--- a/Methanol/Methanol_Bio_Brownfield_Memmingen/Datenbank.xlsx
+++ b/Methanol/Methanol_Bio_Brownfield_Memmingen/Datenbank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methanol\Methanol_Brownfield_Memmingen_Bio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methanol\Methanol_Bio_Brownfield_Memmingen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB321755-11A9-4296-B9D2-67D4CB6B7F97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D4EC0B4-62BD-43D4-B3AF-DC6BF6D3DDA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="23520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -1348,7 +1348,7 @@
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1392,38 +1392,18 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF00B050"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF00B050"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="8">
@@ -1508,105 +1488,158 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1933,1277 +1966,1277 @@
   <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" style="22" customWidth="1"/>
-    <col min="3" max="3" width="36.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="40.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.77734375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="10.88671875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="27" customWidth="1"/>
+    <col min="3" max="3" width="36.21875" style="28" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21" style="28" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19" style="33" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.77734375" style="28" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.77734375" style="28" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.77734375" style="28" customWidth="1"/>
+    <col min="9" max="9" width="13.88671875" style="28" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14" style="28" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.77734375" style="28" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="28"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="22"/>
+      <c r="G1" s="27"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="57" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="30">
         <v>0.66600000000000004</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="29" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="46"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="1" t="s">
+      <c r="A3" s="58"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="31">
         <v>50</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="28" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="46"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="1" t="s">
+      <c r="A4" s="58"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="32">
         <v>1000</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="28" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="46"/>
-      <c r="B5" s="54"/>
-      <c r="C5" s="1" t="s">
+      <c r="A5" s="58"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="33">
         <v>0.03</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="28" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="46"/>
-      <c r="B6" s="54"/>
-      <c r="C6" s="1" t="s">
+      <c r="A6" s="58"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="34">
         <v>20</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="28" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="46"/>
-      <c r="B7" s="54"/>
-      <c r="C7" s="1" t="s">
+      <c r="A7" s="58"/>
+      <c r="B7" s="66"/>
+      <c r="C7" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="33">
         <v>0.08</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="28" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="46"/>
-      <c r="B8" s="57" t="s">
+      <c r="A8" s="58"/>
+      <c r="B8" s="69" t="s">
         <v>231</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="35" t="s">
         <v>233</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="36">
         <v>1.5</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="35" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="46"/>
-      <c r="B9" s="54"/>
-      <c r="C9" s="1" t="s">
+      <c r="A9" s="58"/>
+      <c r="B9" s="66"/>
+      <c r="C9" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="28" t="s">
         <v>234</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="31">
         <v>285.39999999999998</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="28" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="46"/>
-      <c r="B10" s="54"/>
-      <c r="C10" s="1" t="s">
+      <c r="A10" s="58"/>
+      <c r="B10" s="66"/>
+      <c r="C10" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="28" t="s">
         <v>235</v>
       </c>
-      <c r="E10" s="7">
-        <v>5000</v>
-      </c>
-      <c r="F10" s="7" t="s">
+      <c r="E10" s="31">
+        <v>5110</v>
+      </c>
+      <c r="F10" s="31" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="46"/>
-      <c r="B11" s="54"/>
-      <c r="C11" s="1" t="s">
+      <c r="A11" s="58"/>
+      <c r="B11" s="66"/>
+      <c r="C11" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="28" t="s">
         <v>236</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="33">
         <v>0.05</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="28" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="46"/>
-      <c r="B12" s="54"/>
-      <c r="C12" s="1" t="s">
+      <c r="A12" s="58"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="28" t="s">
         <v>237</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="31">
         <v>0.189</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="28" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="46"/>
-      <c r="B13" s="54"/>
-      <c r="C13" s="1" t="s">
+      <c r="A13" s="58"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="28" t="s">
         <v>246</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="28" t="s">
         <v>242</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="31">
         <v>1.375</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="28" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="46"/>
-      <c r="B14" s="54"/>
-      <c r="C14" s="1" t="s">
+      <c r="A14" s="58"/>
+      <c r="B14" s="66"/>
+      <c r="C14" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="28" t="s">
         <v>238</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="34">
         <v>25</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="28" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="46"/>
-      <c r="B15" s="58"/>
-      <c r="C15" s="13" t="s">
+      <c r="A15" s="58"/>
+      <c r="B15" s="70"/>
+      <c r="C15" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="37" t="s">
         <v>239</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="38">
         <v>0.08</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="F15" s="37" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="46"/>
-      <c r="B16" s="57" t="s">
+      <c r="A16" s="58"/>
+      <c r="B16" s="69" t="s">
         <v>273</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="35" t="s">
         <v>276</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="39">
         <v>3.7</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="46"/>
-      <c r="B17" s="54"/>
-      <c r="C17" s="1" t="s">
+      <c r="A17" s="58"/>
+      <c r="B17" s="66"/>
+      <c r="C17" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="28" t="s">
         <v>277</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="33">
         <v>0.27</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="28" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="46"/>
-      <c r="B18" s="54"/>
-      <c r="C18" s="1" t="s">
+      <c r="A18" s="58"/>
+      <c r="B18" s="66"/>
+      <c r="C18" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="28" t="s">
         <v>278</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="33">
         <v>700</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" s="28" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="46"/>
-      <c r="B19" s="54"/>
-      <c r="C19" s="1" t="s">
+      <c r="A19" s="58"/>
+      <c r="B19" s="66"/>
+      <c r="C19" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="28" t="s">
         <v>279</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="33">
         <v>0.02</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="28" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="46"/>
-      <c r="B20" s="54"/>
-      <c r="C20" s="1" t="s">
+      <c r="A20" s="58"/>
+      <c r="B20" s="66"/>
+      <c r="C20" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="28" t="s">
         <v>280</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="33">
         <v>20</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="28" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="46"/>
-      <c r="B21" s="58"/>
-      <c r="C21" s="13" t="s">
+      <c r="A21" s="58"/>
+      <c r="B21" s="70"/>
+      <c r="C21" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="37" t="s">
         <v>281</v>
       </c>
-      <c r="E21" s="14">
+      <c r="E21" s="38">
         <v>0.05</v>
       </c>
-      <c r="F21" s="13" t="s">
+      <c r="F21" s="37" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="46"/>
-      <c r="B22" s="59" t="s">
+      <c r="A22" s="58"/>
+      <c r="B22" s="62" t="s">
         <v>342</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="D22" s="40" t="s">
+      <c r="D22" s="28" t="s">
         <v>351</v>
       </c>
-      <c r="E22" s="39">
+      <c r="E22" s="31">
         <v>0.2</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" s="28" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="46"/>
-      <c r="B23" s="59"/>
-      <c r="C23" s="1" t="s">
+      <c r="A23" s="58"/>
+      <c r="B23" s="62"/>
+      <c r="C23" s="28" t="s">
         <v>283</v>
       </c>
-      <c r="D23" s="40" t="s">
+      <c r="D23" s="28" t="s">
         <v>352</v>
       </c>
-      <c r="E23" s="39">
+      <c r="E23" s="31">
         <v>0.92800000000000005</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="28" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="46"/>
-      <c r="B24" s="59"/>
-      <c r="C24" s="1" t="s">
+      <c r="A24" s="58"/>
+      <c r="B24" s="62"/>
+      <c r="C24" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="D24" s="40" t="s">
+      <c r="D24" s="28" t="s">
         <v>353</v>
       </c>
-      <c r="E24" s="39">
+      <c r="E24" s="31">
         <v>1640</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" s="28" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="46"/>
-      <c r="B25" s="59"/>
-      <c r="C25" s="1" t="s">
+      <c r="A25" s="58"/>
+      <c r="B25" s="62"/>
+      <c r="C25" s="28" t="s">
         <v>379</v>
       </c>
-      <c r="D25" s="40" t="s">
+      <c r="D25" s="28" t="s">
         <v>354</v>
       </c>
-      <c r="E25" s="41">
+      <c r="E25" s="33">
         <v>0.04</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" s="28" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="46"/>
-      <c r="B26" s="59"/>
-      <c r="C26" s="1" t="s">
+      <c r="A26" s="58"/>
+      <c r="B26" s="62"/>
+      <c r="C26" s="28" t="s">
         <v>372</v>
       </c>
-      <c r="D26" s="40" t="s">
+      <c r="D26" s="28" t="s">
         <v>373</v>
       </c>
-      <c r="E26" s="41">
+      <c r="E26" s="33">
         <v>2.5</v>
       </c>
-      <c r="F26" s="40" t="s">
+      <c r="F26" s="28" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="46"/>
-      <c r="B27" s="59"/>
-      <c r="C27" s="1" t="s">
+      <c r="A27" s="58"/>
+      <c r="B27" s="62"/>
+      <c r="C27" s="28" t="s">
         <v>355</v>
       </c>
-      <c r="D27" s="42" t="s">
+      <c r="D27" s="28" t="s">
         <v>356</v>
       </c>
-      <c r="E27" s="43">
+      <c r="E27" s="33">
         <v>1.5</v>
       </c>
-      <c r="F27" s="42" t="s">
+      <c r="F27" s="28" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="46"/>
-      <c r="B28" s="59"/>
-      <c r="C28" s="1" t="s">
+      <c r="A28" s="58"/>
+      <c r="B28" s="62"/>
+      <c r="C28" s="28" t="s">
         <v>380</v>
       </c>
-      <c r="D28" s="42" t="s">
+      <c r="D28" s="28" t="s">
         <v>377</v>
       </c>
-      <c r="E28" s="43">
+      <c r="E28" s="33">
         <v>1.5E-3</v>
       </c>
-      <c r="F28" s="42" t="s">
+      <c r="F28" s="28" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="46"/>
-      <c r="B29" s="59"/>
-      <c r="C29" s="1" t="s">
+      <c r="A29" s="58"/>
+      <c r="B29" s="62"/>
+      <c r="C29" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="D29" s="40" t="s">
+      <c r="D29" s="28" t="s">
         <v>358</v>
       </c>
-      <c r="E29" s="44">
+      <c r="E29" s="34">
         <v>25</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" s="28" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="46"/>
-      <c r="B30" s="59"/>
-      <c r="C30" s="1" t="s">
+      <c r="A30" s="58"/>
+      <c r="B30" s="62"/>
+      <c r="C30" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="D30" s="40" t="s">
+      <c r="D30" s="28" t="s">
         <v>359</v>
       </c>
-      <c r="E30" s="41">
+      <c r="E30" s="33">
         <v>0.08</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" s="28" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="45" t="s">
+      <c r="A31" s="57" t="s">
         <v>71</v>
       </c>
-      <c r="B31" s="49" t="s">
+      <c r="B31" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="E31" s="15">
+      <c r="E31" s="40">
         <v>490</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="F31" s="29" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="46"/>
-      <c r="B32" s="50"/>
-      <c r="C32" s="1" t="s">
+      <c r="A32" s="58"/>
+      <c r="B32" s="62"/>
+      <c r="C32" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="E32" s="9">
+      <c r="E32" s="33">
         <v>0.01</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" s="28" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="46"/>
-      <c r="B33" s="50"/>
-      <c r="C33" s="1" t="s">
+      <c r="A33" s="58"/>
+      <c r="B33" s="62"/>
+      <c r="C33" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="E33" s="10">
+      <c r="E33" s="34">
         <v>20</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" s="28" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="46"/>
-      <c r="B34" s="50"/>
-      <c r="C34" s="1" t="s">
+      <c r="A34" s="58"/>
+      <c r="B34" s="62"/>
+      <c r="C34" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="E34" s="23">
+      <c r="E34" s="41">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" s="28" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="46"/>
-      <c r="B35" s="50"/>
-      <c r="C35" s="1" t="s">
+      <c r="A35" s="58"/>
+      <c r="B35" s="62"/>
+      <c r="C35" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="E35" s="9">
+      <c r="E35" s="33">
         <v>0.83299999999999996</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F35" s="28" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="46"/>
-      <c r="B36" s="50"/>
-      <c r="C36" s="1" t="s">
+      <c r="A36" s="58"/>
+      <c r="B36" s="62"/>
+      <c r="C36" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="E36" s="9">
+      <c r="E36" s="33">
         <v>0.83299999999999996</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F36" s="28" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="46"/>
-      <c r="B37" s="50"/>
-      <c r="C37" s="1" t="s">
+      <c r="A37" s="58"/>
+      <c r="B37" s="62"/>
+      <c r="C37" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="E37" s="9">
+      <c r="E37" s="33">
         <v>0.05</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F37" s="28" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="46"/>
-      <c r="B38" s="51"/>
-      <c r="C38" s="13" t="s">
+      <c r="A38" s="58"/>
+      <c r="B38" s="63"/>
+      <c r="C38" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="D38" s="13" t="s">
+      <c r="D38" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="E38" s="14">
+      <c r="E38" s="38">
         <v>0</v>
       </c>
-      <c r="F38" s="13" t="s">
+      <c r="F38" s="37" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="46"/>
-      <c r="B39" s="52" t="s">
+      <c r="A39" s="58"/>
+      <c r="B39" s="64" t="s">
         <v>317</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" s="29" t="s">
         <v>318</v>
       </c>
-      <c r="E39" s="15">
+      <c r="E39" s="40">
         <v>2.83</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="F39" s="29" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="46"/>
-      <c r="B40" s="50"/>
-      <c r="C40" s="1" t="s">
+      <c r="A40" s="58"/>
+      <c r="B40" s="62"/>
+      <c r="C40" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D40" s="28" t="s">
         <v>319</v>
       </c>
-      <c r="E40" s="9">
+      <c r="E40" s="33">
         <v>0.03</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="F40" s="28" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="46"/>
-      <c r="B41" s="50"/>
-      <c r="C41" s="1" t="s">
+      <c r="A41" s="58"/>
+      <c r="B41" s="62"/>
+      <c r="C41" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" s="28" t="s">
         <v>320</v>
       </c>
-      <c r="E41" s="10">
+      <c r="E41" s="34">
         <v>30</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F41" s="28" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="46"/>
-      <c r="B42" s="50"/>
-      <c r="C42" s="1" t="s">
+      <c r="A42" s="58"/>
+      <c r="B42" s="62"/>
+      <c r="C42" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D42" s="28" t="s">
         <v>321</v>
       </c>
-      <c r="E42" s="9">
+      <c r="E42" s="33">
         <v>7.3999999999999999E-4</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="F42" s="28" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="46"/>
-      <c r="B43" s="50"/>
-      <c r="C43" s="1" t="s">
+      <c r="A43" s="58"/>
+      <c r="B43" s="62"/>
+      <c r="C43" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D43" s="28" t="s">
         <v>322</v>
       </c>
-      <c r="E43" s="9">
+      <c r="E43" s="33">
         <v>0.98</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="F43" s="28" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="46"/>
-      <c r="B44" s="50"/>
-      <c r="C44" s="1" t="s">
+      <c r="A44" s="58"/>
+      <c r="B44" s="62"/>
+      <c r="C44" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D44" s="28" t="s">
         <v>323</v>
       </c>
-      <c r="E44" s="9">
+      <c r="E44" s="33">
         <v>0.98</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="F44" s="28" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="46"/>
-      <c r="B45" s="50"/>
-      <c r="C45" s="1" t="s">
+      <c r="A45" s="58"/>
+      <c r="B45" s="62"/>
+      <c r="C45" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D45" s="28" t="s">
         <v>324</v>
       </c>
-      <c r="E45" s="9">
+      <c r="E45" s="33">
         <v>0.05</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="F45" s="28" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="46"/>
-      <c r="B46" s="50"/>
-      <c r="C46" s="13" t="s">
+      <c r="A46" s="58"/>
+      <c r="B46" s="62"/>
+      <c r="C46" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="D46" s="13" t="s">
+      <c r="D46" s="37" t="s">
         <v>325</v>
       </c>
-      <c r="E46" s="14">
+      <c r="E46" s="38">
         <v>0</v>
       </c>
-      <c r="F46" s="13" t="s">
+      <c r="F46" s="37" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="46"/>
-      <c r="B47" s="52" t="s">
+      <c r="A47" s="58"/>
+      <c r="B47" s="64" t="s">
         <v>203</v>
       </c>
-      <c r="C47" s="11" t="s">
+      <c r="C47" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="D47" s="11" t="s">
+      <c r="D47" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="E47" s="16">
+      <c r="E47" s="39">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="F47" s="11" t="s">
+      <c r="F47" s="35" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="46"/>
-      <c r="B48" s="54"/>
-      <c r="C48" s="1" t="s">
+      <c r="A48" s="58"/>
+      <c r="B48" s="66"/>
+      <c r="C48" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D48" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="E48" s="7">
+      <c r="E48" s="31">
         <f>E49*4</f>
         <v>424</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="F48" s="28" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="46"/>
-      <c r="B49" s="54"/>
-      <c r="C49" s="1" t="s">
+      <c r="A49" s="58"/>
+      <c r="B49" s="66"/>
+      <c r="C49" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D49" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="E49" s="7">
+      <c r="E49" s="31">
         <v>106</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="F49" s="28" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="46"/>
-      <c r="B50" s="54"/>
-      <c r="C50" s="1" t="s">
+      <c r="A50" s="58"/>
+      <c r="B50" s="66"/>
+      <c r="C50" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D50" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="E50" s="9">
+      <c r="E50" s="33">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="F50" s="28" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="46"/>
-      <c r="B51" s="54"/>
-      <c r="C51" s="1" t="s">
+      <c r="A51" s="58"/>
+      <c r="B51" s="66"/>
+      <c r="C51" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D51" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="E51" s="9">
+      <c r="E51" s="33">
         <v>0.93500000000000005</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="F51" s="28" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="46"/>
-      <c r="B52" s="54"/>
-      <c r="C52" s="1" t="s">
+      <c r="A52" s="58"/>
+      <c r="B52" s="66"/>
+      <c r="C52" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D52" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="E52" s="9">
+      <c r="E52" s="33">
         <v>0.93500000000000005</v>
       </c>
-      <c r="F52" s="1" t="s">
+      <c r="F52" s="28" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="46"/>
-      <c r="B53" s="54"/>
-      <c r="C53" s="1" t="s">
+      <c r="A53" s="58"/>
+      <c r="B53" s="66"/>
+      <c r="C53" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="D53" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="E53" s="7">
+      <c r="E53" s="31">
         <v>0.25</v>
       </c>
-      <c r="F53" s="1" t="s">
+      <c r="F53" s="28" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="46"/>
-      <c r="B54" s="54"/>
-      <c r="C54" s="1" t="s">
+      <c r="A54" s="58"/>
+      <c r="B54" s="66"/>
+      <c r="C54" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D54" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="E54" s="9">
+      <c r="E54" s="33">
         <v>0</v>
       </c>
-      <c r="F54" s="1" t="s">
+      <c r="F54" s="28" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="46"/>
-      <c r="B55" s="54"/>
-      <c r="C55" s="1" t="s">
+      <c r="A55" s="58"/>
+      <c r="B55" s="66"/>
+      <c r="C55" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="D55" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="E55" s="10">
+      <c r="E55" s="34">
         <v>15</v>
       </c>
-      <c r="F55" s="1" t="s">
+      <c r="F55" s="28" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="47"/>
-      <c r="B56" s="55"/>
-      <c r="C56" s="17" t="s">
+      <c r="A56" s="59"/>
+      <c r="B56" s="67"/>
+      <c r="C56" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="D56" s="17" t="s">
+      <c r="D56" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="E56" s="18">
+      <c r="E56" s="43">
         <v>0.1</v>
       </c>
-      <c r="F56" s="17" t="s">
+      <c r="F56" s="42" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="45" t="s">
+      <c r="A57" s="57" t="s">
         <v>72</v>
       </c>
-      <c r="B57" s="30" t="s">
+      <c r="B57" s="44" t="s">
         <v>73</v>
       </c>
-      <c r="C57" s="31" t="s">
+      <c r="C57" s="45" t="s">
         <v>74</v>
       </c>
-      <c r="D57" s="31" t="s">
+      <c r="D57" s="45" t="s">
         <v>75</v>
       </c>
-      <c r="E57" s="32">
+      <c r="E57" s="46">
         <v>0.1699</v>
       </c>
-      <c r="F57" s="31" t="s">
+      <c r="F57" s="45" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="48"/>
-      <c r="B58" s="27" t="s">
+      <c r="A58" s="60"/>
+      <c r="B58" s="47" t="s">
         <v>343</v>
       </c>
-      <c r="C58" s="28" t="s">
+      <c r="C58" s="48" t="s">
         <v>344</v>
       </c>
-      <c r="D58" s="28" t="s">
+      <c r="D58" s="48" t="s">
         <v>345</v>
       </c>
-      <c r="E58" s="29">
+      <c r="E58" s="49">
         <v>0</v>
       </c>
-      <c r="F58" s="28" t="s">
+      <c r="F58" s="48" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="46"/>
-      <c r="B59" s="52" t="s">
+      <c r="A59" s="58"/>
+      <c r="B59" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="C59" s="11" t="s">
+      <c r="C59" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="D59" s="11" t="s">
+      <c r="D59" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="E59" s="16">
+      <c r="E59" s="39">
         <v>0.99</v>
       </c>
-      <c r="F59" s="11" t="s">
+      <c r="F59" s="35" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="46"/>
-      <c r="B60" s="50"/>
-      <c r="C60" s="1" t="s">
+      <c r="A60" s="58"/>
+      <c r="B60" s="62"/>
+      <c r="C60" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="D60" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="E60" s="19">
+      <c r="E60" s="50">
         <v>1100</v>
       </c>
-      <c r="F60" s="1" t="s">
+      <c r="F60" s="28" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="46"/>
-      <c r="B61" s="50"/>
-      <c r="C61" s="1" t="s">
+      <c r="A61" s="58"/>
+      <c r="B61" s="62"/>
+      <c r="C61" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="D61" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="E61" s="19">
+      <c r="E61" s="50">
         <v>17.84</v>
       </c>
-      <c r="F61" s="1" t="s">
+      <c r="F61" s="28" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="46"/>
-      <c r="B62" s="50"/>
-      <c r="C62" s="1" t="s">
+      <c r="A62" s="58"/>
+      <c r="B62" s="62"/>
+      <c r="C62" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="D62" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="E62" s="7">
+      <c r="E62" s="31">
         <v>0</v>
       </c>
-      <c r="F62" s="1" t="s">
+      <c r="F62" s="28" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="46"/>
-      <c r="B63" s="50"/>
-      <c r="C63" s="1" t="s">
+      <c r="A63" s="58"/>
+      <c r="B63" s="62"/>
+      <c r="C63" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="D63" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="E63" s="10">
+      <c r="E63" s="34">
         <v>25</v>
       </c>
-      <c r="F63" s="1" t="s">
+      <c r="F63" s="28" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="46"/>
-      <c r="B64" s="50"/>
-      <c r="C64" s="1" t="s">
+      <c r="A64" s="58"/>
+      <c r="B64" s="62"/>
+      <c r="C64" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="D64" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="E64" s="7">
+      <c r="E64" s="31">
         <v>1000000</v>
       </c>
-      <c r="F64" s="1" t="s">
+      <c r="F64" s="28" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="46"/>
-      <c r="B65" s="51"/>
-      <c r="C65" s="13" t="s">
+      <c r="A65" s="58"/>
+      <c r="B65" s="63"/>
+      <c r="C65" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="D65" s="13" t="s">
+      <c r="D65" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="E65" s="14">
+      <c r="E65" s="38">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="F65" s="13" t="s">
+      <c r="F65" s="37" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="46"/>
-      <c r="B66" s="52" t="s">
+      <c r="A66" s="58"/>
+      <c r="B66" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="C66" s="11" t="s">
+      <c r="C66" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="D66" s="11" t="s">
+      <c r="D66" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="E66" s="16">
+      <c r="E66" s="39">
         <v>0.997</v>
       </c>
-      <c r="F66" s="11" t="s">
+      <c r="F66" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="46"/>
-      <c r="B67" s="50"/>
-      <c r="C67" s="1" t="s">
+      <c r="A67" s="58"/>
+      <c r="B67" s="62"/>
+      <c r="C67" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="D67" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="E67" s="19">
+      <c r="E67" s="50">
         <v>1080</v>
       </c>
-      <c r="F67" s="1" t="s">
+      <c r="F67" s="28" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="46"/>
-      <c r="B68" s="50"/>
-      <c r="C68" s="1" t="s">
+      <c r="A68" s="58"/>
+      <c r="B68" s="62"/>
+      <c r="C68" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="D68" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="E68" s="19">
+      <c r="E68" s="50">
         <v>12.68</v>
       </c>
-      <c r="F68" s="1" t="s">
+      <c r="F68" s="28" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="46"/>
-      <c r="B69" s="50"/>
-      <c r="C69" s="1" t="s">
+      <c r="A69" s="58"/>
+      <c r="B69" s="62"/>
+      <c r="C69" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="D69" s="1" t="s">
+      <c r="D69" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="E69" s="21">
+      <c r="E69" s="51">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F69" s="1" t="s">
+      <c r="F69" s="28" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="46"/>
-      <c r="B70" s="50"/>
-      <c r="C70" s="1" t="s">
+      <c r="A70" s="58"/>
+      <c r="B70" s="62"/>
+      <c r="C70" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="D70" s="1" t="s">
+      <c r="D70" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="E70" s="10">
+      <c r="E70" s="34">
         <v>25</v>
       </c>
-      <c r="F70" s="1" t="s">
+      <c r="F70" s="28" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="46"/>
-      <c r="B71" s="50"/>
-      <c r="C71" s="1" t="s">
+      <c r="A71" s="58"/>
+      <c r="B71" s="62"/>
+      <c r="C71" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="D71" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="E71" s="20">
+      <c r="E71" s="52">
         <v>1000000</v>
       </c>
-      <c r="F71" s="1" t="s">
+      <c r="F71" s="28" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="47"/>
-      <c r="B72" s="53"/>
-      <c r="C72" s="17" t="s">
+      <c r="A72" s="59"/>
+      <c r="B72" s="65"/>
+      <c r="C72" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="D72" s="17" t="s">
+      <c r="D72" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="E72" s="18">
+      <c r="E72" s="43">
         <v>5.8000000000000003E-2</v>
       </c>
-      <c r="F72" s="17" t="s">
+      <c r="F72" s="42" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="45" t="s">
+      <c r="A73" s="57" t="s">
         <v>76</v>
       </c>
-      <c r="B73" s="33" t="s">
+      <c r="B73" s="53" t="s">
         <v>73</v>
       </c>
-      <c r="C73" s="34" t="s">
+      <c r="C73" s="45" t="s">
         <v>77</v>
       </c>
-      <c r="D73" s="34" t="s">
+      <c r="D73" s="45" t="s">
         <v>78</v>
       </c>
-      <c r="E73" s="35">
+      <c r="E73" s="46">
         <v>-1E-4</v>
       </c>
-      <c r="F73" s="34" t="s">
+      <c r="F73" s="45" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="46"/>
-      <c r="B74" s="22" t="s">
+      <c r="A74" s="58"/>
+      <c r="B74" s="27" t="s">
         <v>299</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C74" s="28" t="s">
         <v>300</v>
       </c>
-      <c r="D74" s="1" t="s">
+      <c r="D74" s="28" t="s">
         <v>301</v>
       </c>
-      <c r="E74" s="9">
+      <c r="E74" s="33">
         <v>-1E-4</v>
       </c>
-      <c r="F74" s="1" t="s">
+      <c r="F74" s="28" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="46"/>
-      <c r="B75" s="24" t="s">
+      <c r="A75" s="58"/>
+      <c r="B75" s="54" t="s">
         <v>79</v>
       </c>
-      <c r="C75" s="25" t="s">
+      <c r="C75" s="55" t="s">
         <v>80</v>
       </c>
-      <c r="D75" s="25" t="s">
+      <c r="D75" s="55" t="s">
         <v>81</v>
       </c>
-      <c r="E75" s="26">
+      <c r="E75" s="56">
         <v>-1.5</v>
       </c>
-      <c r="F75" s="25" t="s">
+      <c r="F75" s="55" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="47"/>
-      <c r="B76" s="4" t="s">
+      <c r="A76" s="59"/>
+      <c r="B76" s="25" t="s">
         <v>262</v>
       </c>
-      <c r="C76" s="17" t="s">
+      <c r="C76" s="42" t="s">
         <v>274</v>
       </c>
-      <c r="D76" s="17" t="s">
+      <c r="D76" s="42" t="s">
         <v>272</v>
       </c>
-      <c r="E76" s="18">
+      <c r="E76" s="43">
         <v>-0.6</v>
       </c>
-      <c r="F76" s="17" t="s">
+      <c r="F76" s="42" t="s">
         <v>275</v>
       </c>
     </row>
@@ -3234,1973 +3267,1973 @@
   <dimension ref="A1:F149"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="50.77734375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="46.109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="37.5546875" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="11.5546875" style="1"/>
+    <col min="1" max="1" width="14.5546875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.77734375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="46.109375" style="5" customWidth="1"/>
+    <col min="6" max="6" width="37.5546875" style="5" customWidth="1"/>
+    <col min="7" max="16384" width="11.5546875" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="75" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="78" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="E2" s="6"/>
-      <c r="F2" s="2" t="s">
+      <c r="E2" s="7"/>
+      <c r="F2" s="6" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="46"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="1" t="s">
+      <c r="A3" s="77"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="1" t="s">
+      <c r="E3" s="8"/>
+      <c r="F3" s="5" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="46"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="1" t="s">
+      <c r="A4" s="77"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="E4" s="8"/>
-      <c r="F4" s="1" t="s">
+      <c r="E4" s="9"/>
+      <c r="F4" s="5" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="46"/>
-      <c r="B5" s="54"/>
-      <c r="C5" s="1" t="s">
+      <c r="A5" s="77"/>
+      <c r="B5" s="72"/>
+      <c r="C5" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="1" t="s">
+      <c r="E5" s="10"/>
+      <c r="F5" s="5" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="46"/>
-      <c r="B6" s="54"/>
-      <c r="C6" s="1" t="s">
+      <c r="A6" s="77"/>
+      <c r="B6" s="72"/>
+      <c r="C6" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="1" t="s">
+      <c r="E6" s="11"/>
+      <c r="F6" s="5" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="46"/>
-      <c r="B7" s="54"/>
-      <c r="C7" s="1" t="s">
+      <c r="A7" s="77"/>
+      <c r="B7" s="72"/>
+      <c r="C7" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="1" t="s">
+      <c r="E7" s="11"/>
+      <c r="F7" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="46"/>
-      <c r="B8" s="54"/>
-      <c r="C8" s="1" t="s">
+      <c r="A8" s="77"/>
+      <c r="B8" s="72"/>
+      <c r="C8" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="1" t="s">
+      <c r="E8" s="11"/>
+      <c r="F8" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="46"/>
-      <c r="B9" s="54"/>
-      <c r="C9" s="1" t="s">
+      <c r="A9" s="77"/>
+      <c r="B9" s="72"/>
+      <c r="C9" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="E9" s="10"/>
-      <c r="F9" s="1" t="s">
+      <c r="E9" s="11"/>
+      <c r="F9" s="5" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="46"/>
-      <c r="B10" s="54"/>
-      <c r="C10" s="1" t="s">
+      <c r="A10" s="77"/>
+      <c r="B10" s="72"/>
+      <c r="C10" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="1" t="s">
+      <c r="E10" s="11"/>
+      <c r="F10" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="46"/>
-      <c r="B11" s="54"/>
-      <c r="E11" s="9"/>
+      <c r="A11" s="77"/>
+      <c r="B11" s="72"/>
+      <c r="E11" s="10"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="46"/>
-      <c r="B12" s="57" t="s">
+      <c r="A12" s="77"/>
+      <c r="B12" s="71" t="s">
         <v>231</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="E12" s="12"/>
-      <c r="F12" s="11" t="s">
+      <c r="E12" s="13"/>
+      <c r="F12" s="12" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="46"/>
-      <c r="B13" s="54"/>
-      <c r="C13" s="1" t="s">
+      <c r="A13" s="77"/>
+      <c r="B13" s="72"/>
+      <c r="C13" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="E13" s="7"/>
-      <c r="F13" s="1" t="s">
+      <c r="E13" s="8"/>
+      <c r="F13" s="5" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="46"/>
-      <c r="B14" s="54"/>
-      <c r="C14" s="1" t="s">
+      <c r="A14" s="77"/>
+      <c r="B14" s="72"/>
+      <c r="C14" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7" t="s">
+      <c r="E14" s="8"/>
+      <c r="F14" s="8" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="46"/>
-      <c r="B15" s="54"/>
-      <c r="C15" s="1" t="s">
+      <c r="A15" s="77"/>
+      <c r="B15" s="72"/>
+      <c r="C15" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="E15" s="9"/>
-      <c r="F15" s="1" t="s">
+      <c r="E15" s="10"/>
+      <c r="F15" s="5" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="46"/>
-      <c r="B16" s="54"/>
-      <c r="C16" s="1" t="s">
+      <c r="A16" s="77"/>
+      <c r="B16" s="72"/>
+      <c r="C16" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="E16" s="7"/>
-      <c r="F16" s="1" t="s">
+      <c r="E16" s="8"/>
+      <c r="F16" s="5" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="46"/>
-      <c r="B17" s="54"/>
-      <c r="C17" s="1" t="s">
+      <c r="A17" s="77"/>
+      <c r="B17" s="72"/>
+      <c r="C17" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="E17" s="7"/>
-      <c r="F17" s="1" t="s">
+      <c r="E17" s="8"/>
+      <c r="F17" s="5" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="46"/>
-      <c r="B18" s="54"/>
-      <c r="C18" s="1" t="s">
+      <c r="A18" s="77"/>
+      <c r="B18" s="72"/>
+      <c r="C18" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="E18" s="10"/>
-      <c r="F18" s="1" t="s">
+      <c r="E18" s="11"/>
+      <c r="F18" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="46"/>
-      <c r="B19" s="54"/>
-      <c r="C19" s="1" t="s">
+      <c r="A19" s="77"/>
+      <c r="B19" s="72"/>
+      <c r="C19" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="E19" s="10"/>
-      <c r="F19" s="1" t="s">
+      <c r="E19" s="11"/>
+      <c r="F19" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="46"/>
-      <c r="B20" s="54"/>
-      <c r="C20" s="1" t="s">
+      <c r="A20" s="77"/>
+      <c r="B20" s="72"/>
+      <c r="C20" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="E20" s="10"/>
-      <c r="F20" s="1" t="s">
+      <c r="E20" s="11"/>
+      <c r="F20" s="5" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="46"/>
-      <c r="B21" s="54"/>
-      <c r="C21" s="1" t="s">
+      <c r="A21" s="77"/>
+      <c r="B21" s="72"/>
+      <c r="C21" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="E21" s="10"/>
-      <c r="F21" s="1" t="s">
+      <c r="E21" s="11"/>
+      <c r="F21" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="46"/>
-      <c r="B22" s="58"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="13"/>
+      <c r="A22" s="77"/>
+      <c r="B22" s="74"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="14"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="46"/>
-      <c r="B23" s="57" t="s">
+      <c r="A23" s="77"/>
+      <c r="B23" s="71" t="s">
         <v>273</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="E23" s="7"/>
-      <c r="F23" s="1" t="s">
+      <c r="E23" s="8"/>
+      <c r="F23" s="5" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="46"/>
-      <c r="B24" s="54"/>
-      <c r="C24" s="1" t="s">
+      <c r="A24" s="77"/>
+      <c r="B24" s="72"/>
+      <c r="C24" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="E24" s="7"/>
-      <c r="F24" s="1" t="s">
+      <c r="E24" s="8"/>
+      <c r="F24" s="5" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="46"/>
-      <c r="B25" s="54"/>
-      <c r="C25" s="1" t="s">
+      <c r="A25" s="77"/>
+      <c r="B25" s="72"/>
+      <c r="C25" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="E25" s="9"/>
-      <c r="F25" s="1" t="s">
+      <c r="E25" s="10"/>
+      <c r="F25" s="5" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="46"/>
-      <c r="B26" s="54"/>
-      <c r="C26" s="1" t="s">
+      <c r="A26" s="77"/>
+      <c r="B26" s="72"/>
+      <c r="C26" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="E26" s="10"/>
-      <c r="F26" s="1" t="s">
+      <c r="E26" s="11"/>
+      <c r="F26" s="5" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="46"/>
-      <c r="B27" s="54"/>
-      <c r="C27" s="1" t="s">
+      <c r="A27" s="77"/>
+      <c r="B27" s="72"/>
+      <c r="C27" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="E27" s="10"/>
-      <c r="F27" s="1" t="s">
+      <c r="E27" s="11"/>
+      <c r="F27" s="5" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="46"/>
-      <c r="B28" s="54"/>
-      <c r="C28" s="1" t="s">
+      <c r="A28" s="77"/>
+      <c r="B28" s="72"/>
+      <c r="C28" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="E28" s="10"/>
-      <c r="F28" s="1" t="s">
+      <c r="E28" s="11"/>
+      <c r="F28" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="46"/>
-      <c r="B29" s="54"/>
-      <c r="C29" s="1" t="s">
+      <c r="A29" s="77"/>
+      <c r="B29" s="72"/>
+      <c r="C29" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="E29" s="10"/>
-      <c r="F29" s="1" t="s">
+      <c r="E29" s="11"/>
+      <c r="F29" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="46"/>
-      <c r="B30" s="54"/>
-      <c r="C30" s="1" t="s">
+      <c r="A30" s="77"/>
+      <c r="B30" s="72"/>
+      <c r="C30" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="E30" s="9"/>
-      <c r="F30" s="1" t="s">
+      <c r="E30" s="10"/>
+      <c r="F30" s="5" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="46"/>
-      <c r="B31" s="54"/>
-      <c r="C31" s="1" t="s">
+      <c r="A31" s="77"/>
+      <c r="B31" s="72"/>
+      <c r="C31" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="E31" s="9"/>
-      <c r="F31" s="1" t="s">
+      <c r="E31" s="10"/>
+      <c r="F31" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="46"/>
-      <c r="B32" s="58"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="13"/>
+      <c r="A32" s="77"/>
+      <c r="B32" s="74"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="14"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="46"/>
-      <c r="B33" s="59" t="s">
+      <c r="A33" s="77"/>
+      <c r="B33" s="79" t="s">
         <v>360</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="E33" s="7"/>
-      <c r="F33" s="1" t="s">
+      <c r="E33" s="8"/>
+      <c r="F33" s="5" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="46"/>
-      <c r="B34" s="59"/>
-      <c r="C34" s="1" t="s">
+      <c r="A34" s="77"/>
+      <c r="B34" s="79"/>
+      <c r="C34" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="E34" s="7"/>
-      <c r="F34" s="1" t="s">
+      <c r="E34" s="8"/>
+      <c r="F34" s="5" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="46"/>
-      <c r="B35" s="59"/>
-      <c r="C35" s="1" t="s">
+      <c r="A35" s="77"/>
+      <c r="B35" s="79"/>
+      <c r="C35" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="E35" s="9"/>
-      <c r="F35" s="1" t="s">
+      <c r="E35" s="10"/>
+      <c r="F35" s="5" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="46"/>
-      <c r="B36" s="59"/>
-      <c r="C36" s="1" t="s">
+      <c r="A36" s="77"/>
+      <c r="B36" s="79"/>
+      <c r="C36" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" s="5" t="s">
         <v>365</v>
       </c>
-      <c r="E36" s="9"/>
-      <c r="F36" s="1" t="s">
+      <c r="E36" s="10"/>
+      <c r="F36" s="5" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="46"/>
-      <c r="B37" s="59"/>
-      <c r="C37" s="1" t="s">
+      <c r="A37" s="77"/>
+      <c r="B37" s="79"/>
+      <c r="C37" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="E37" s="9"/>
-      <c r="F37" s="1" t="s">
+      <c r="E37" s="10"/>
+      <c r="F37" s="5" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="46"/>
-      <c r="B38" s="59"/>
-      <c r="C38" s="1" t="s">
+      <c r="A38" s="77"/>
+      <c r="B38" s="79"/>
+      <c r="C38" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" s="5" t="s">
         <v>364</v>
       </c>
-      <c r="E38" s="10"/>
-      <c r="F38" s="1" t="s">
+      <c r="E38" s="11"/>
+      <c r="F38" s="5" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="46"/>
-      <c r="B39" s="59"/>
-      <c r="C39" s="1" t="s">
+      <c r="A39" s="77"/>
+      <c r="B39" s="79"/>
+      <c r="C39" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D39" s="5" t="s">
         <v>366</v>
       </c>
-      <c r="E39" s="10"/>
-      <c r="F39" s="1" t="s">
+      <c r="E39" s="11"/>
+      <c r="F39" s="5" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="46"/>
-      <c r="B40" s="59"/>
-      <c r="C40" s="1" t="s">
+      <c r="A40" s="77"/>
+      <c r="B40" s="79"/>
+      <c r="C40" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D40" s="5" t="s">
         <v>369</v>
       </c>
-      <c r="E40" s="10"/>
-      <c r="F40" s="1" t="s">
+      <c r="E40" s="11"/>
+      <c r="F40" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="46"/>
-      <c r="B41" s="59"/>
-      <c r="C41" s="1" t="s">
+      <c r="A41" s="77"/>
+      <c r="B41" s="79"/>
+      <c r="C41" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="E41" s="10"/>
-      <c r="F41" s="1" t="s">
+      <c r="E41" s="11"/>
+      <c r="F41" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="46"/>
-      <c r="B42" s="59"/>
-      <c r="C42" s="1" t="s">
+      <c r="A42" s="77"/>
+      <c r="B42" s="79"/>
+      <c r="C42" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D42" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="E42" s="10"/>
-      <c r="F42" s="1" t="s">
+      <c r="E42" s="11"/>
+      <c r="F42" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="46"/>
-      <c r="B43" s="59"/>
-      <c r="C43" s="1" t="s">
+      <c r="A43" s="77"/>
+      <c r="B43" s="79"/>
+      <c r="C43" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D43" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="E43" s="9"/>
-      <c r="F43" s="1" t="s">
+      <c r="E43" s="10"/>
+      <c r="F43" s="5" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="46"/>
-      <c r="B44" s="59"/>
-      <c r="C44" s="1" t="s">
+      <c r="A44" s="77"/>
+      <c r="B44" s="79"/>
+      <c r="C44" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D44" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="E44" s="9"/>
-      <c r="F44" s="1" t="s">
+      <c r="E44" s="10"/>
+      <c r="F44" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="46"/>
-      <c r="B45" s="59"/>
-      <c r="E45" s="9"/>
+      <c r="A45" s="77"/>
+      <c r="B45" s="79"/>
+      <c r="E45" s="10"/>
     </row>
     <row r="46" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="45" t="s">
+      <c r="A46" s="75" t="s">
         <v>71</v>
       </c>
-      <c r="B46" s="49" t="s">
+      <c r="B46" s="83" t="s">
         <v>3</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D46" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="E46" s="15"/>
-      <c r="F46" s="2" t="s">
+      <c r="E46" s="16"/>
+      <c r="F46" s="6" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="46"/>
-      <c r="B47" s="50"/>
-      <c r="C47" s="1" t="s">
+      <c r="A47" s="77"/>
+      <c r="B47" s="79"/>
+      <c r="C47" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D47" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="E47" s="9"/>
-      <c r="F47" s="1" t="s">
+      <c r="E47" s="10"/>
+      <c r="F47" s="5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="46"/>
-      <c r="B48" s="50"/>
-      <c r="C48" s="1" t="s">
+      <c r="A48" s="77"/>
+      <c r="B48" s="79"/>
+      <c r="C48" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D48" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="E48" s="10"/>
-      <c r="F48" s="1" t="s">
+      <c r="E48" s="11"/>
+      <c r="F48" s="5" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="46"/>
-      <c r="B49" s="50"/>
-      <c r="C49" s="1" t="s">
+      <c r="A49" s="77"/>
+      <c r="B49" s="79"/>
+      <c r="C49" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D49" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="E49" s="9"/>
-      <c r="F49" s="1" t="s">
+      <c r="E49" s="10"/>
+      <c r="F49" s="5" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="46"/>
-      <c r="B50" s="50"/>
-      <c r="C50" s="1" t="s">
+      <c r="A50" s="77"/>
+      <c r="B50" s="79"/>
+      <c r="C50" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D50" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="E50" s="9"/>
-      <c r="F50" s="1" t="s">
+      <c r="E50" s="10"/>
+      <c r="F50" s="5" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="46"/>
-      <c r="B51" s="50"/>
-      <c r="C51" s="1" t="s">
+      <c r="A51" s="77"/>
+      <c r="B51" s="79"/>
+      <c r="C51" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D51" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="E51" s="9"/>
-      <c r="F51" s="1" t="s">
+      <c r="E51" s="10"/>
+      <c r="F51" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="46"/>
-      <c r="B52" s="50"/>
-      <c r="C52" s="1" t="s">
+      <c r="A52" s="77"/>
+      <c r="B52" s="79"/>
+      <c r="C52" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D52" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="E52" s="9"/>
-      <c r="F52" s="1" t="s">
+      <c r="E52" s="10"/>
+      <c r="F52" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="46"/>
-      <c r="B53" s="50"/>
-      <c r="C53" s="1" t="s">
+      <c r="A53" s="77"/>
+      <c r="B53" s="79"/>
+      <c r="C53" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="D53" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="E53" s="9"/>
-      <c r="F53" s="1" t="s">
+      <c r="E53" s="10"/>
+      <c r="F53" s="5" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="46"/>
-      <c r="B54" s="50"/>
-      <c r="C54" s="1" t="s">
+      <c r="A54" s="77"/>
+      <c r="B54" s="79"/>
+      <c r="C54" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D54" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="E54" s="9"/>
-      <c r="F54" s="1" t="s">
+      <c r="E54" s="10"/>
+      <c r="F54" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="46"/>
-      <c r="B55" s="51"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="13"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="13"/>
+      <c r="A55" s="77"/>
+      <c r="B55" s="84"/>
+      <c r="C55" s="14"/>
+      <c r="D55" s="14"/>
+      <c r="E55" s="15"/>
+      <c r="F55" s="14"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="46"/>
-      <c r="B56" s="50" t="s">
+      <c r="A56" s="77"/>
+      <c r="B56" s="79" t="s">
         <v>317</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="D56" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="E56" s="7"/>
-      <c r="F56" s="1" t="s">
+      <c r="E56" s="8"/>
+      <c r="F56" s="5" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="46"/>
-      <c r="B57" s="50"/>
-      <c r="C57" s="1" t="s">
+      <c r="A57" s="77"/>
+      <c r="B57" s="79"/>
+      <c r="C57" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="D57" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="E57" s="9"/>
-      <c r="F57" s="1" t="s">
+      <c r="E57" s="10"/>
+      <c r="F57" s="5" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="46"/>
-      <c r="B58" s="50"/>
-      <c r="C58" s="1" t="s">
+      <c r="A58" s="77"/>
+      <c r="B58" s="79"/>
+      <c r="C58" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="D58" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="E58" s="10"/>
-      <c r="F58" s="1" t="s">
+      <c r="E58" s="11"/>
+      <c r="F58" s="5" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="46"/>
-      <c r="B59" s="50"/>
-      <c r="C59" s="1" t="s">
+      <c r="A59" s="77"/>
+      <c r="B59" s="79"/>
+      <c r="C59" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="D59" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="E59" s="9"/>
-      <c r="F59" s="1" t="s">
+      <c r="E59" s="10"/>
+      <c r="F59" s="5" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="46"/>
-      <c r="B60" s="50"/>
-      <c r="C60" s="1" t="s">
+      <c r="A60" s="77"/>
+      <c r="B60" s="79"/>
+      <c r="C60" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="D60" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="E60" s="9"/>
-      <c r="F60" s="1" t="s">
+      <c r="E60" s="10"/>
+      <c r="F60" s="5" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="46"/>
-      <c r="B61" s="50"/>
-      <c r="C61" s="1" t="s">
+      <c r="A61" s="77"/>
+      <c r="B61" s="79"/>
+      <c r="C61" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="D61" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="E61" s="9"/>
-      <c r="F61" s="1" t="s">
+      <c r="E61" s="10"/>
+      <c r="F61" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="46"/>
-      <c r="B62" s="50"/>
-      <c r="C62" s="1" t="s">
+      <c r="A62" s="77"/>
+      <c r="B62" s="79"/>
+      <c r="C62" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="D62" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="E62" s="9"/>
-      <c r="F62" s="1" t="s">
+      <c r="E62" s="10"/>
+      <c r="F62" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="46"/>
-      <c r="B63" s="50"/>
-      <c r="C63" s="1" t="s">
+      <c r="A63" s="77"/>
+      <c r="B63" s="79"/>
+      <c r="C63" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="D63" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="E63" s="9"/>
-      <c r="F63" s="1" t="s">
+      <c r="E63" s="10"/>
+      <c r="F63" s="5" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="46"/>
-      <c r="B64" s="50"/>
-      <c r="C64" s="1" t="s">
+      <c r="A64" s="77"/>
+      <c r="B64" s="79"/>
+      <c r="C64" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="D64" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="E64" s="9"/>
-      <c r="F64" s="1" t="s">
+      <c r="E64" s="10"/>
+      <c r="F64" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="46"/>
-      <c r="B65" s="51"/>
-      <c r="E65" s="9"/>
+      <c r="A65" s="77"/>
+      <c r="B65" s="84"/>
+      <c r="E65" s="10"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="46"/>
-      <c r="B66" s="52" t="s">
+      <c r="A66" s="77"/>
+      <c r="B66" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="C66" s="11" t="s">
+      <c r="C66" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="D66" s="11" t="s">
+      <c r="D66" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="E66" s="16"/>
-      <c r="F66" s="11" t="s">
+      <c r="E66" s="17"/>
+      <c r="F66" s="12" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="46"/>
-      <c r="B67" s="50"/>
-      <c r="C67" s="1" t="s">
+      <c r="A67" s="77"/>
+      <c r="B67" s="79"/>
+      <c r="C67" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="D67" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="E67" s="9"/>
-      <c r="F67" s="1" t="s">
+      <c r="E67" s="10"/>
+      <c r="F67" s="5" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="46"/>
-      <c r="B68" s="54"/>
-      <c r="C68" s="1" t="s">
+      <c r="A68" s="77"/>
+      <c r="B68" s="72"/>
+      <c r="C68" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="D68" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="E68" s="7"/>
-      <c r="F68" s="1" t="s">
+      <c r="E68" s="8"/>
+      <c r="F68" s="5" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="46"/>
-      <c r="B69" s="54"/>
-      <c r="C69" s="1" t="s">
+      <c r="A69" s="77"/>
+      <c r="B69" s="72"/>
+      <c r="C69" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="D69" s="1" t="s">
+      <c r="D69" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="E69" s="7"/>
-      <c r="F69" s="1" t="s">
+      <c r="E69" s="8"/>
+      <c r="F69" s="5" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="46"/>
-      <c r="B70" s="54"/>
-      <c r="C70" s="1" t="s">
+      <c r="A70" s="77"/>
+      <c r="B70" s="72"/>
+      <c r="C70" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D70" s="1" t="s">
+      <c r="D70" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="E70" s="7"/>
-      <c r="F70" s="1" t="s">
+      <c r="E70" s="8"/>
+      <c r="F70" s="5" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="46"/>
-      <c r="B71" s="54"/>
-      <c r="C71" s="1" t="s">
+      <c r="A71" s="77"/>
+      <c r="B71" s="72"/>
+      <c r="C71" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="D71" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="E71" s="9"/>
-      <c r="F71" s="1" t="s">
+      <c r="E71" s="10"/>
+      <c r="F71" s="5" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="46"/>
-      <c r="B72" s="54"/>
-      <c r="C72" s="1" t="s">
+      <c r="A72" s="77"/>
+      <c r="B72" s="72"/>
+      <c r="C72" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="D72" s="1" t="s">
+      <c r="D72" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="E72" s="7"/>
-      <c r="F72" s="1" t="s">
+      <c r="E72" s="8"/>
+      <c r="F72" s="5" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="46"/>
-      <c r="B73" s="54"/>
-      <c r="C73" s="1" t="s">
+      <c r="A73" s="77"/>
+      <c r="B73" s="72"/>
+      <c r="C73" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="D73" s="1" t="s">
+      <c r="D73" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="E73" s="9"/>
-      <c r="F73" s="1" t="s">
+      <c r="E73" s="10"/>
+      <c r="F73" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="46"/>
-      <c r="B74" s="54"/>
-      <c r="C74" s="1" t="s">
+      <c r="A74" s="77"/>
+      <c r="B74" s="72"/>
+      <c r="C74" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="D74" s="1" t="s">
+      <c r="D74" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="E74" s="9"/>
-      <c r="F74" s="1" t="s">
+      <c r="E74" s="10"/>
+      <c r="F74" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="46"/>
-      <c r="B75" s="54"/>
-      <c r="C75" s="1" t="s">
+      <c r="A75" s="77"/>
+      <c r="B75" s="72"/>
+      <c r="C75" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="D75" s="1" t="s">
+      <c r="D75" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="E75" s="9"/>
-      <c r="F75" s="1" t="s">
+      <c r="E75" s="10"/>
+      <c r="F75" s="5" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="46"/>
-      <c r="B76" s="54"/>
-      <c r="C76" s="1" t="s">
+      <c r="A76" s="77"/>
+      <c r="B76" s="72"/>
+      <c r="C76" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="D76" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="E76" s="9"/>
-      <c r="F76" s="1" t="s">
+      <c r="E76" s="10"/>
+      <c r="F76" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="47"/>
-      <c r="B77" s="55"/>
-      <c r="C77" s="17"/>
-      <c r="D77" s="17"/>
-      <c r="E77" s="18"/>
-      <c r="F77" s="17"/>
+      <c r="A77" s="80"/>
+      <c r="B77" s="82"/>
+      <c r="C77" s="18"/>
+      <c r="D77" s="18"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="18"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="45" t="s">
+      <c r="A78" s="75" t="s">
         <v>72</v>
       </c>
-      <c r="B78" s="56" t="s">
+      <c r="B78" s="78" t="s">
         <v>73</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C78" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="D78" s="2" t="s">
+      <c r="D78" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="E78" s="15"/>
-      <c r="F78" s="2" t="s">
+      <c r="E78" s="16"/>
+      <c r="F78" s="6" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="46"/>
-      <c r="B79" s="60"/>
-      <c r="C79" s="36" t="s">
+      <c r="A79" s="77"/>
+      <c r="B79" s="73"/>
+      <c r="C79" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="D79" s="36" t="s">
+      <c r="D79" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="E79" s="37"/>
-      <c r="F79" s="36" t="s">
+      <c r="E79" s="21"/>
+      <c r="F79" s="20" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="46"/>
-      <c r="B80" s="58"/>
-      <c r="C80" s="13"/>
-      <c r="D80" s="13"/>
-      <c r="E80" s="38"/>
-      <c r="F80" s="13"/>
+      <c r="A80" s="77"/>
+      <c r="B80" s="74"/>
+      <c r="C80" s="14"/>
+      <c r="D80" s="14"/>
+      <c r="E80" s="22"/>
+      <c r="F80" s="14"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="46"/>
-      <c r="B81" s="60" t="s">
+      <c r="A81" s="77"/>
+      <c r="B81" s="73" t="s">
         <v>343</v>
       </c>
-      <c r="C81" s="36" t="s">
+      <c r="C81" s="20" t="s">
         <v>346</v>
       </c>
-      <c r="D81" s="36" t="s">
+      <c r="D81" s="20" t="s">
         <v>349</v>
       </c>
-      <c r="E81" s="37"/>
-      <c r="F81" s="36" t="s">
+      <c r="E81" s="21"/>
+      <c r="F81" s="20" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="46"/>
-      <c r="B82" s="60"/>
-      <c r="C82" s="1" t="s">
+      <c r="A82" s="77"/>
+      <c r="B82" s="73"/>
+      <c r="C82" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="D82" s="1" t="s">
+      <c r="D82" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="E82" s="7"/>
-      <c r="F82" s="1" t="s">
+      <c r="E82" s="8"/>
+      <c r="F82" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="46"/>
-      <c r="B83" s="60"/>
-      <c r="E83" s="7"/>
+      <c r="A83" s="77"/>
+      <c r="B83" s="73"/>
+      <c r="E83" s="8"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="46"/>
-      <c r="B84" s="52" t="s">
+      <c r="A84" s="77"/>
+      <c r="B84" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="C84" s="11" t="s">
+      <c r="C84" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="D84" s="11" t="s">
+      <c r="D84" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="E84" s="16"/>
-      <c r="F84" s="11" t="s">
+      <c r="E84" s="17"/>
+      <c r="F84" s="12" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="46"/>
-      <c r="B85" s="50"/>
-      <c r="C85" s="1" t="s">
+      <c r="A85" s="77"/>
+      <c r="B85" s="79"/>
+      <c r="C85" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="D85" s="1" t="s">
+      <c r="D85" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="E85" s="19"/>
-      <c r="F85" s="1" t="s">
+      <c r="E85" s="1"/>
+      <c r="F85" s="5" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="46"/>
-      <c r="B86" s="50"/>
-      <c r="C86" s="1" t="s">
+      <c r="A86" s="77"/>
+      <c r="B86" s="79"/>
+      <c r="C86" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D86" s="1" t="s">
+      <c r="D86" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="E86" s="19"/>
-      <c r="F86" s="1" t="s">
+      <c r="E86" s="1"/>
+      <c r="F86" s="5" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="46"/>
-      <c r="B87" s="50"/>
-      <c r="C87" s="1" t="s">
+      <c r="A87" s="77"/>
+      <c r="B87" s="79"/>
+      <c r="C87" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="D87" s="1" t="s">
+      <c r="D87" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="E87" s="7"/>
-      <c r="F87" s="1" t="s">
+      <c r="E87" s="8"/>
+      <c r="F87" s="5" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="46"/>
-      <c r="B88" s="50"/>
-      <c r="C88" s="1" t="s">
+      <c r="A88" s="77"/>
+      <c r="B88" s="79"/>
+      <c r="C88" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="D88" s="1" t="s">
+      <c r="D88" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="E88" s="10"/>
-      <c r="F88" s="1" t="s">
+      <c r="E88" s="11"/>
+      <c r="F88" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="46"/>
-      <c r="B89" s="50"/>
-      <c r="C89" s="1" t="s">
+      <c r="A89" s="77"/>
+      <c r="B89" s="79"/>
+      <c r="C89" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="D89" s="1" t="s">
+      <c r="D89" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="E89" s="7"/>
-      <c r="F89" s="1" t="s">
+      <c r="E89" s="8"/>
+      <c r="F89" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="46"/>
-      <c r="B90" s="50"/>
-      <c r="C90" s="1" t="s">
+      <c r="A90" s="77"/>
+      <c r="B90" s="79"/>
+      <c r="C90" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="D90" s="1" t="s">
+      <c r="D90" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="E90" s="7"/>
-      <c r="F90" s="1" t="s">
+      <c r="E90" s="8"/>
+      <c r="F90" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="46"/>
-      <c r="B91" s="50"/>
-      <c r="C91" s="1" t="s">
+      <c r="A91" s="77"/>
+      <c r="B91" s="79"/>
+      <c r="C91" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="D91" s="1" t="s">
+      <c r="D91" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="E91" s="9"/>
-      <c r="F91" s="1" t="s">
+      <c r="E91" s="10"/>
+      <c r="F91" s="5" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="46"/>
-      <c r="B92" s="50"/>
-      <c r="C92" s="1" t="s">
+      <c r="A92" s="77"/>
+      <c r="B92" s="79"/>
+      <c r="C92" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="D92" s="1" t="s">
+      <c r="D92" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="E92" s="9"/>
-      <c r="F92" s="1" t="s">
+      <c r="E92" s="10"/>
+      <c r="F92" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="46"/>
-      <c r="B93" s="51"/>
+      <c r="A93" s="77"/>
+      <c r="B93" s="84"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="46"/>
-      <c r="B94" s="52" t="s">
+      <c r="A94" s="77"/>
+      <c r="B94" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="C94" s="11" t="s">
+      <c r="C94" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="D94" s="11" t="s">
+      <c r="D94" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="E94" s="16"/>
-      <c r="F94" s="11" t="s">
+      <c r="E94" s="17"/>
+      <c r="F94" s="12" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="46"/>
-      <c r="B95" s="50"/>
-      <c r="C95" s="1" t="s">
+      <c r="A95" s="77"/>
+      <c r="B95" s="79"/>
+      <c r="C95" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="D95" s="1" t="s">
+      <c r="D95" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="E95" s="19"/>
-      <c r="F95" s="1" t="s">
+      <c r="E95" s="1"/>
+      <c r="F95" s="5" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="46"/>
-      <c r="B96" s="50"/>
-      <c r="C96" s="1" t="s">
+      <c r="A96" s="77"/>
+      <c r="B96" s="79"/>
+      <c r="C96" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="D96" s="1" t="s">
+      <c r="D96" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="E96" s="19"/>
-      <c r="F96" s="1" t="s">
+      <c r="E96" s="1"/>
+      <c r="F96" s="5" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="46"/>
-      <c r="B97" s="50"/>
-      <c r="C97" s="1" t="s">
+      <c r="A97" s="77"/>
+      <c r="B97" s="79"/>
+      <c r="C97" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="D97" s="1" t="s">
+      <c r="D97" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="E97" s="19"/>
-      <c r="F97" s="1" t="s">
+      <c r="E97" s="1"/>
+      <c r="F97" s="5" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="46"/>
-      <c r="B98" s="50"/>
-      <c r="C98" s="1" t="s">
+      <c r="A98" s="77"/>
+      <c r="B98" s="79"/>
+      <c r="C98" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="D98" s="1" t="s">
+      <c r="D98" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="E98" s="10"/>
-      <c r="F98" s="1" t="s">
+      <c r="E98" s="11"/>
+      <c r="F98" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="46"/>
-      <c r="B99" s="50"/>
-      <c r="C99" s="1" t="s">
+      <c r="A99" s="77"/>
+      <c r="B99" s="79"/>
+      <c r="C99" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="D99" s="1" t="s">
+      <c r="D99" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="E99" s="20"/>
-      <c r="F99" s="1" t="s">
+      <c r="E99" s="23"/>
+      <c r="F99" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="46"/>
-      <c r="B100" s="50"/>
-      <c r="C100" s="1" t="s">
+      <c r="A100" s="77"/>
+      <c r="B100" s="79"/>
+      <c r="C100" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="D100" s="1" t="s">
+      <c r="D100" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="E100" s="20"/>
-      <c r="F100" s="1" t="s">
+      <c r="E100" s="23"/>
+      <c r="F100" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="46"/>
-      <c r="B101" s="50"/>
-      <c r="C101" s="1" t="s">
+      <c r="A101" s="77"/>
+      <c r="B101" s="79"/>
+      <c r="C101" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="D101" s="1" t="s">
+      <c r="D101" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="E101" s="9"/>
-      <c r="F101" s="1" t="s">
+      <c r="E101" s="10"/>
+      <c r="F101" s="5" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="46"/>
-      <c r="B102" s="50"/>
-      <c r="C102" s="1" t="s">
+      <c r="A102" s="77"/>
+      <c r="B102" s="79"/>
+      <c r="C102" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="D102" s="1" t="s">
+      <c r="D102" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="E102" s="9"/>
-      <c r="F102" s="1" t="s">
+      <c r="E102" s="10"/>
+      <c r="F102" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="47"/>
-      <c r="B103" s="53"/>
+      <c r="A103" s="80"/>
+      <c r="B103" s="85"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="45" t="s">
+      <c r="A104" s="75" t="s">
         <v>76</v>
       </c>
-      <c r="B104" s="56" t="s">
+      <c r="B104" s="78" t="s">
         <v>73</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="C104" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="D104" s="2" t="s">
+      <c r="D104" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="E104" s="6"/>
-      <c r="F104" s="2" t="s">
+      <c r="E104" s="7"/>
+      <c r="F104" s="6" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="46"/>
-      <c r="B105" s="54"/>
-      <c r="C105" s="1" t="s">
+      <c r="A105" s="77"/>
+      <c r="B105" s="72"/>
+      <c r="C105" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="D105" s="1" t="s">
+      <c r="D105" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="E105" s="9"/>
-      <c r="F105" s="1" t="s">
+      <c r="E105" s="10"/>
+      <c r="F105" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="46"/>
-      <c r="B106" s="54"/>
-      <c r="C106" s="1" t="s">
+      <c r="A106" s="77"/>
+      <c r="B106" s="72"/>
+      <c r="C106" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="D106" s="1" t="s">
+      <c r="D106" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="E106" s="9"/>
-      <c r="F106" s="1" t="s">
+      <c r="E106" s="10"/>
+      <c r="F106" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="46"/>
-      <c r="B107" s="58"/>
-      <c r="C107" s="13"/>
-      <c r="D107" s="13"/>
-      <c r="E107" s="14"/>
-      <c r="F107" s="13"/>
+      <c r="A107" s="77"/>
+      <c r="B107" s="74"/>
+      <c r="C107" s="14"/>
+      <c r="D107" s="14"/>
+      <c r="E107" s="15"/>
+      <c r="F107" s="14"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="46"/>
-      <c r="B108" s="57" t="s">
+      <c r="A108" s="77"/>
+      <c r="B108" s="71" t="s">
         <v>303</v>
       </c>
-      <c r="C108" s="1" t="s">
+      <c r="C108" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="D108" s="1" t="s">
+      <c r="D108" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="E108" s="9"/>
-      <c r="F108" s="1" t="s">
+      <c r="E108" s="10"/>
+      <c r="F108" s="5" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="46"/>
-      <c r="B109" s="54"/>
-      <c r="C109" s="1" t="s">
+      <c r="A109" s="77"/>
+      <c r="B109" s="72"/>
+      <c r="C109" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="D109" s="1" t="s">
+      <c r="D109" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="E109" s="9"/>
-      <c r="F109" s="1" t="s">
+      <c r="E109" s="10"/>
+      <c r="F109" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="46"/>
-      <c r="B110" s="54"/>
-      <c r="C110" s="1" t="s">
+      <c r="A110" s="77"/>
+      <c r="B110" s="72"/>
+      <c r="C110" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="D110" s="1" t="s">
+      <c r="D110" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="E110" s="9"/>
-      <c r="F110" s="1" t="s">
+      <c r="E110" s="10"/>
+      <c r="F110" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="46"/>
-      <c r="B111" s="58"/>
-      <c r="E111" s="9"/>
+      <c r="A111" s="77"/>
+      <c r="B111" s="74"/>
+      <c r="E111" s="10"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="46"/>
-      <c r="B112" s="57" t="s">
+      <c r="A112" s="77"/>
+      <c r="B112" s="71" t="s">
         <v>79</v>
       </c>
-      <c r="C112" s="11" t="s">
+      <c r="C112" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="D112" s="11" t="s">
+      <c r="D112" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="E112" s="16"/>
-      <c r="F112" s="11" t="s">
+      <c r="E112" s="17"/>
+      <c r="F112" s="12" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="46"/>
-      <c r="B113" s="54"/>
-      <c r="C113" s="1" t="s">
+      <c r="A113" s="77"/>
+      <c r="B113" s="72"/>
+      <c r="C113" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="D113" s="1" t="s">
+      <c r="D113" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="E113" s="9"/>
-      <c r="F113" s="1" t="s">
+      <c r="E113" s="10"/>
+      <c r="F113" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="46"/>
-      <c r="B114" s="58"/>
-      <c r="C114" s="13"/>
-      <c r="D114" s="13"/>
-      <c r="E114" s="14"/>
-      <c r="F114" s="13"/>
+      <c r="A114" s="77"/>
+      <c r="B114" s="74"/>
+      <c r="C114" s="14"/>
+      <c r="D114" s="14"/>
+      <c r="E114" s="15"/>
+      <c r="F114" s="14"/>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="46"/>
-      <c r="B115" s="57" t="s">
+      <c r="A115" s="77"/>
+      <c r="B115" s="71" t="s">
         <v>262</v>
       </c>
-      <c r="C115" s="1" t="s">
+      <c r="C115" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="D115" s="1" t="s">
+      <c r="D115" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="E115" s="9"/>
-      <c r="F115" s="1" t="s">
+      <c r="E115" s="10"/>
+      <c r="F115" s="5" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="46"/>
-      <c r="B116" s="54"/>
-      <c r="C116" s="1" t="s">
+      <c r="A116" s="77"/>
+      <c r="B116" s="72"/>
+      <c r="C116" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="D116" s="1" t="s">
+      <c r="D116" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="E116" s="9"/>
-      <c r="F116" s="1" t="s">
+      <c r="E116" s="10"/>
+      <c r="F116" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="47"/>
-      <c r="B117" s="55"/>
-      <c r="C117" s="17"/>
-      <c r="D117" s="17"/>
-      <c r="E117" s="18"/>
-      <c r="F117" s="17"/>
+      <c r="A117" s="80"/>
+      <c r="B117" s="82"/>
+      <c r="C117" s="18"/>
+      <c r="D117" s="18"/>
+      <c r="E117" s="19"/>
+      <c r="F117" s="18"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="45" t="s">
+      <c r="A118" s="75" t="s">
         <v>164</v>
       </c>
-      <c r="B118" s="56" t="s">
+      <c r="B118" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="C118" s="2" t="s">
+      <c r="C118" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D118" s="2" t="s">
+      <c r="D118" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="E118" s="2"/>
-      <c r="F118" s="2" t="s">
+      <c r="E118" s="6"/>
+      <c r="F118" s="6" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="48"/>
-      <c r="B119" s="54"/>
-      <c r="C119" s="1" t="s">
+      <c r="A119" s="76"/>
+      <c r="B119" s="72"/>
+      <c r="C119" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="D119" s="1" t="s">
+      <c r="D119" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="F119" s="1" t="s">
+      <c r="F119" s="5" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="48"/>
-      <c r="B120" s="58"/>
-      <c r="C120" s="13"/>
-      <c r="D120" s="13"/>
-      <c r="E120" s="13"/>
-      <c r="F120" s="13"/>
+      <c r="A120" s="76"/>
+      <c r="B120" s="74"/>
+      <c r="C120" s="14"/>
+      <c r="D120" s="14"/>
+      <c r="E120" s="14"/>
+      <c r="F120" s="14"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="48"/>
-      <c r="B121" s="57" t="s">
+      <c r="A121" s="76"/>
+      <c r="B121" s="71" t="s">
         <v>184</v>
       </c>
-      <c r="C121" s="1" t="s">
+      <c r="C121" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="D121" s="1" t="s">
+      <c r="D121" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="F121" s="1" t="s">
+      <c r="F121" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="48"/>
-      <c r="B122" s="54"/>
-      <c r="C122" s="1" t="s">
+      <c r="A122" s="76"/>
+      <c r="B122" s="72"/>
+      <c r="C122" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="D122" s="1" t="s">
+      <c r="D122" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="F122" s="1" t="s">
+      <c r="F122" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="48"/>
-      <c r="B123" s="54"/>
-      <c r="C123" s="1" t="s">
+      <c r="A123" s="76"/>
+      <c r="B123" s="72"/>
+      <c r="C123" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="D123" s="1" t="s">
+      <c r="D123" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="F123" s="1" t="s">
+      <c r="F123" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="48"/>
-      <c r="B124" s="54"/>
-      <c r="C124" s="1" t="s">
+      <c r="A124" s="76"/>
+      <c r="B124" s="72"/>
+      <c r="C124" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="D124" s="1" t="s">
+      <c r="D124" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="F124" s="1" t="s">
+      <c r="F124" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="48"/>
-      <c r="B125" s="54"/>
-      <c r="C125" s="1" t="s">
+      <c r="A125" s="76"/>
+      <c r="B125" s="72"/>
+      <c r="C125" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="D125" s="1" t="s">
+      <c r="D125" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="F125" s="1" t="s">
+      <c r="F125" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="48"/>
-      <c r="B126" s="54"/>
-      <c r="C126" s="1" t="s">
+      <c r="A126" s="76"/>
+      <c r="B126" s="72"/>
+      <c r="C126" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="D126" s="1" t="s">
+      <c r="D126" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="F126" s="1" t="s">
+      <c r="F126" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="48"/>
-      <c r="B127" s="54"/>
+      <c r="A127" s="76"/>
+      <c r="B127" s="72"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="48"/>
-      <c r="B128" s="57" t="s">
+      <c r="A128" s="76"/>
+      <c r="B128" s="71" t="s">
         <v>208</v>
       </c>
-      <c r="C128" s="11" t="s">
+      <c r="C128" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="D128" s="11" t="s">
+      <c r="D128" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="E128" s="11"/>
-      <c r="F128" s="11" t="s">
+      <c r="E128" s="12"/>
+      <c r="F128" s="12" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="48"/>
-      <c r="B129" s="54"/>
-      <c r="C129" s="1" t="s">
+      <c r="A129" s="76"/>
+      <c r="B129" s="72"/>
+      <c r="C129" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="D129" s="1" t="s">
+      <c r="D129" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="F129" s="1" t="s">
+      <c r="F129" s="5" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="48"/>
-      <c r="B130" s="54"/>
-      <c r="C130" s="1" t="s">
+      <c r="A130" s="76"/>
+      <c r="B130" s="72"/>
+      <c r="C130" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="D130" s="1" t="s">
+      <c r="D130" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="F130" s="1" t="s">
+      <c r="F130" s="5" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="48"/>
-      <c r="B131" s="54"/>
-      <c r="C131" s="1" t="s">
+      <c r="A131" s="76"/>
+      <c r="B131" s="72"/>
+      <c r="C131" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="D131" s="1" t="s">
+      <c r="D131" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="F131" s="1" t="s">
+      <c r="F131" s="5" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="48"/>
-      <c r="B132" s="54"/>
-      <c r="C132" s="1" t="s">
+      <c r="A132" s="76"/>
+      <c r="B132" s="72"/>
+      <c r="C132" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="D132" s="1" t="s">
+      <c r="D132" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="F132" s="1" t="s">
+      <c r="F132" s="5" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="48"/>
-      <c r="B133" s="54"/>
-      <c r="C133" s="1" t="s">
+      <c r="A133" s="76"/>
+      <c r="B133" s="72"/>
+      <c r="C133" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="D133" s="1" t="s">
+      <c r="D133" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="F133" s="1" t="s">
+      <c r="F133" s="5" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="48"/>
-      <c r="B134" s="54"/>
-      <c r="C134" s="1" t="s">
+      <c r="A134" s="76"/>
+      <c r="B134" s="72"/>
+      <c r="C134" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="D134" s="1" t="s">
+      <c r="D134" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="F134" s="1" t="s">
+      <c r="F134" s="5" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="48"/>
-      <c r="B135" s="54"/>
-      <c r="C135" s="1" t="s">
+      <c r="A135" s="76"/>
+      <c r="B135" s="72"/>
+      <c r="C135" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="D135" s="1" t="s">
+      <c r="D135" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="F135" s="1" t="s">
+      <c r="F135" s="5" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="48"/>
-      <c r="B136" s="54"/>
-      <c r="C136" s="1" t="s">
+      <c r="A136" s="76"/>
+      <c r="B136" s="72"/>
+      <c r="C136" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D136" s="1" t="s">
+      <c r="D136" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="F136" s="1" t="s">
+      <c r="F136" s="5" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="48"/>
-      <c r="B137" s="54"/>
-      <c r="C137" s="1" t="s">
+      <c r="A137" s="76"/>
+      <c r="B137" s="72"/>
+      <c r="C137" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="D137" s="1" t="s">
+      <c r="D137" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="F137" s="1" t="s">
+      <c r="F137" s="5" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="48"/>
-      <c r="B138" s="54"/>
-      <c r="C138" s="1" t="s">
+      <c r="A138" s="76"/>
+      <c r="B138" s="72"/>
+      <c r="C138" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="D138" s="1" t="s">
+      <c r="D138" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="F138" s="1" t="s">
+      <c r="F138" s="5" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="48"/>
-      <c r="B139" s="54"/>
-      <c r="C139" s="1" t="s">
+      <c r="A139" s="76"/>
+      <c r="B139" s="72"/>
+      <c r="C139" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="D139" s="1" t="s">
+      <c r="D139" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="F139" s="1" t="s">
+      <c r="F139" s="5" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="48"/>
-      <c r="B140" s="54"/>
+      <c r="A140" s="76"/>
+      <c r="B140" s="72"/>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="48"/>
-      <c r="B141" s="57" t="s">
+      <c r="A141" s="76"/>
+      <c r="B141" s="71" t="s">
         <v>224</v>
       </c>
-      <c r="C141" s="11" t="s">
+      <c r="C141" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="D141" s="11" t="s">
+      <c r="D141" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="E141" s="11"/>
-      <c r="F141" s="11" t="s">
+      <c r="E141" s="12"/>
+      <c r="F141" s="12" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="48"/>
-      <c r="B142" s="60"/>
-      <c r="C142" s="1" t="s">
+      <c r="A142" s="76"/>
+      <c r="B142" s="73"/>
+      <c r="C142" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="D142" s="1" t="s">
+      <c r="D142" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="F142" s="1" t="s">
+      <c r="F142" s="5" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="48"/>
-      <c r="B143" s="60"/>
-      <c r="C143" s="1" t="s">
+      <c r="A143" s="76"/>
+      <c r="B143" s="73"/>
+      <c r="C143" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="D143" s="1" t="s">
+      <c r="D143" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="F143" s="1" t="s">
+      <c r="F143" s="5" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="48"/>
-      <c r="B144" s="60"/>
-      <c r="C144" s="1" t="s">
+      <c r="A144" s="76"/>
+      <c r="B144" s="73"/>
+      <c r="C144" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D144" s="1" t="s">
+      <c r="D144" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="F144" s="1" t="s">
+      <c r="F144" s="5" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A145" s="48"/>
-      <c r="B145" s="60"/>
-      <c r="C145" s="1" t="s">
+      <c r="A145" s="76"/>
+      <c r="B145" s="73"/>
+      <c r="C145" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="D145" s="1" t="s">
+      <c r="D145" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="F145" s="1" t="s">
+      <c r="F145" s="5" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A146" s="48"/>
-      <c r="B146" s="58"/>
+      <c r="A146" s="76"/>
+      <c r="B146" s="74"/>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A147" s="48"/>
-      <c r="B147" s="57" t="s">
+      <c r="A147" s="76"/>
+      <c r="B147" s="71" t="s">
         <v>382</v>
       </c>
-      <c r="C147" s="11" t="s">
+      <c r="C147" s="12" t="s">
         <v>383</v>
       </c>
-      <c r="D147" s="11" t="s">
+      <c r="D147" s="12" t="s">
         <v>384</v>
       </c>
-      <c r="E147" s="11"/>
-      <c r="F147" s="11" t="s">
+      <c r="E147" s="12"/>
+      <c r="F147" s="12" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A148" s="48"/>
-      <c r="B148" s="54"/>
-      <c r="C148" s="1" t="s">
+      <c r="A148" s="76"/>
+      <c r="B148" s="72"/>
+      <c r="C148" s="5" t="s">
         <v>385</v>
       </c>
-      <c r="D148" s="1" t="s">
+      <c r="D148" s="5" t="s">
         <v>386</v>
       </c>
-      <c r="F148" s="1" t="s">
+      <c r="F148" s="5" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A149" s="48"/>
+      <c r="A149" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="25">

--- a/Methanol/Methanol_Bio_Brownfield_Memmingen/Datenbank.xlsx
+++ b/Methanol/Methanol_Bio_Brownfield_Memmingen/Datenbank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methanol\Methanol_Bio_Brownfield_Memmingen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D4EC0B4-62BD-43D4-B3AF-DC6BF6D3DDA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21507B0B-967E-42C4-8888-FBDEF8EFE66B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -453,9 +453,6 @@
     <t>€/kWa</t>
   </si>
   <si>
-    <t>€/kg_H2 * h</t>
-  </si>
-  <si>
     <t>(%_Kapa)/h</t>
   </si>
   <si>
@@ -738,9 +735,6 @@
     <t>kW_el</t>
   </si>
   <si>
-    <t>€ h / kg a</t>
-  </si>
-  <si>
     <t>calc_cost_gesamt</t>
   </si>
   <si>
@@ -1336,6 +1330,12 @@
   </si>
   <si>
     <t>kWh_th/a</t>
+  </si>
+  <si>
+    <t>€ / kg a</t>
+  </si>
+  <si>
+    <t>kg</t>
   </si>
 </sst>
 </file>
@@ -1596,13 +1596,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1611,17 +1608,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1629,16 +1617,28 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2034,7 +2034,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="28" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -2104,19 +2104,19 @@
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="58"/>
       <c r="B8" s="69" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C8" s="35" t="s">
         <v>84</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E8" s="36">
         <v>1.5</v>
       </c>
       <c r="F8" s="35" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -2126,7 +2126,7 @@
         <v>85</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E9" s="31">
         <v>285.39999999999998</v>
@@ -2142,13 +2142,13 @@
         <v>10</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E10" s="31">
         <v>5110</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -2158,7 +2158,7 @@
         <v>11</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E11" s="33">
         <v>0.05</v>
@@ -2174,29 +2174,29 @@
         <v>86</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E12" s="31">
         <v>0.189</v>
       </c>
       <c r="F12" s="28" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="58"/>
       <c r="B13" s="66"/>
       <c r="C13" s="28" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D13" s="28" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E13" s="31">
         <v>1.375</v>
       </c>
       <c r="F13" s="28" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -2206,7 +2206,7 @@
         <v>13</v>
       </c>
       <c r="D14" s="28" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E14" s="34">
         <v>25</v>
@@ -2222,7 +2222,7 @@
         <v>15</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E15" s="38">
         <v>0.08</v>
@@ -2234,13 +2234,13 @@
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="58"/>
       <c r="B16" s="69" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C16" s="35" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="35" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E16" s="39">
         <v>3.7</v>
@@ -2256,13 +2256,13 @@
         <v>84</v>
       </c>
       <c r="D17" s="28" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E17" s="33">
         <v>0.27</v>
       </c>
       <c r="F17" s="28" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -2272,13 +2272,13 @@
         <v>10</v>
       </c>
       <c r="D18" s="28" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E18" s="33">
         <v>700</v>
       </c>
       <c r="F18" s="28" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -2288,7 +2288,7 @@
         <v>11</v>
       </c>
       <c r="D19" s="28" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E19" s="33">
         <v>0.02</v>
@@ -2304,7 +2304,7 @@
         <v>13</v>
       </c>
       <c r="D20" s="28" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E20" s="33">
         <v>20</v>
@@ -2320,7 +2320,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="37" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E21" s="38">
         <v>0.05</v>
@@ -2332,35 +2332,35 @@
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="58"/>
       <c r="B22" s="62" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C22" s="28" t="s">
         <v>84</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E22" s="31">
         <v>0.2</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="58"/>
       <c r="B23" s="62"/>
       <c r="C23" s="28" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D23" s="28" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E23" s="31">
         <v>0.92800000000000005</v>
       </c>
       <c r="F23" s="28" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -2370,23 +2370,23 @@
         <v>10</v>
       </c>
       <c r="D24" s="28" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E24" s="31">
         <v>1640</v>
       </c>
       <c r="F24" s="28" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="58"/>
       <c r="B25" s="62"/>
       <c r="C25" s="28" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D25" s="28" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E25" s="33">
         <v>0.04</v>
@@ -2399,48 +2399,48 @@
       <c r="A26" s="58"/>
       <c r="B26" s="62"/>
       <c r="C26" s="28" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D26" s="28" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E26" s="33">
         <v>2.5</v>
       </c>
       <c r="F26" s="28" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="58"/>
       <c r="B27" s="62"/>
       <c r="C27" s="28" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D27" s="28" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E27" s="33">
         <v>1.5</v>
       </c>
       <c r="F27" s="28" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="58"/>
       <c r="B28" s="62"/>
       <c r="C28" s="28" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D28" s="28" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E28" s="33">
         <v>1.5E-3</v>
       </c>
       <c r="F28" s="28" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -2450,7 +2450,7 @@
         <v>13</v>
       </c>
       <c r="D29" s="28" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E29" s="34">
         <v>25</v>
@@ -2466,7 +2466,7 @@
         <v>15</v>
       </c>
       <c r="D30" s="28" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E30" s="33">
         <v>0.08</v>
@@ -2492,7 +2492,7 @@
         <v>490</v>
       </c>
       <c r="F31" s="29" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -2540,7 +2540,7 @@
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="F34" s="28" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -2604,25 +2604,25 @@
         <v>0</v>
       </c>
       <c r="F38" s="37" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="58"/>
       <c r="B39" s="64" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C39" s="29" t="s">
         <v>87</v>
       </c>
       <c r="D39" s="29" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E39" s="40">
         <v>2.83</v>
       </c>
       <c r="F39" s="29" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -2632,7 +2632,7 @@
         <v>11</v>
       </c>
       <c r="D40" s="28" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E40" s="33">
         <v>0.03</v>
@@ -2648,7 +2648,7 @@
         <v>13</v>
       </c>
       <c r="D41" s="28" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E41" s="34">
         <v>30</v>
@@ -2664,13 +2664,13 @@
         <v>20</v>
       </c>
       <c r="D42" s="28" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E42" s="33">
         <v>7.3999999999999999E-4</v>
       </c>
       <c r="F42" s="28" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -2680,7 +2680,7 @@
         <v>35</v>
       </c>
       <c r="D43" s="28" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E43" s="33">
         <v>0.98</v>
@@ -2696,7 +2696,7 @@
         <v>36</v>
       </c>
       <c r="D44" s="28" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E44" s="33">
         <v>0.98</v>
@@ -2712,7 +2712,7 @@
         <v>15</v>
       </c>
       <c r="D45" s="28" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E45" s="33">
         <v>0.05</v>
@@ -2728,19 +2728,19 @@
         <v>88</v>
       </c>
       <c r="D46" s="37" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E46" s="38">
         <v>0</v>
       </c>
       <c r="F46" s="37" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="58"/>
       <c r="B47" s="64" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C47" s="35" t="s">
         <v>91</v>
@@ -2752,7 +2752,7 @@
         <v>1.6999999999999999E-3</v>
       </c>
       <c r="F47" s="35" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -2865,7 +2865,7 @@
         <v>0</v>
       </c>
       <c r="F54" s="28" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -2923,19 +2923,19 @@
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="60"/>
       <c r="B58" s="47" t="s">
+        <v>341</v>
+      </c>
+      <c r="C58" s="48" t="s">
+        <v>342</v>
+      </c>
+      <c r="D58" s="48" t="s">
         <v>343</v>
-      </c>
-      <c r="C58" s="48" t="s">
-        <v>344</v>
-      </c>
-      <c r="D58" s="48" t="s">
-        <v>345</v>
       </c>
       <c r="E58" s="49">
         <v>0</v>
       </c>
       <c r="F58" s="48" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
@@ -3189,19 +3189,19 @@
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="58"/>
       <c r="B74" s="27" t="s">
+        <v>297</v>
+      </c>
+      <c r="C74" s="28" t="s">
+        <v>298</v>
+      </c>
+      <c r="D74" s="28" t="s">
         <v>299</v>
-      </c>
-      <c r="C74" s="28" t="s">
-        <v>300</v>
-      </c>
-      <c r="D74" s="28" t="s">
-        <v>301</v>
       </c>
       <c r="E74" s="33">
         <v>-1E-4</v>
       </c>
       <c r="F74" s="28" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
@@ -3225,19 +3225,19 @@
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="59"/>
       <c r="B76" s="25" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C76" s="42" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D76" s="42" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E76" s="43">
         <v>-0.6</v>
       </c>
       <c r="F76" s="42" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
   </sheetData>
@@ -3297,31 +3297,31 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="75" t="s">
+      <c r="A2" s="74" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="78" t="s">
+      <c r="B2" s="71" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="E2" s="7"/>
       <c r="F2" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="77"/>
+      <c r="A3" s="75"/>
       <c r="B3" s="72"/>
       <c r="C3" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="5" t="s">
@@ -3329,892 +3329,892 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="77"/>
+      <c r="A4" s="75"/>
       <c r="B4" s="72"/>
       <c r="C4" s="5" t="s">
         <v>84</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E4" s="9"/>
       <c r="F4" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="77"/>
+      <c r="A5" s="75"/>
       <c r="B5" s="72"/>
       <c r="C5" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E5" s="10"/>
       <c r="F5" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="77"/>
+      <c r="A6" s="75"/>
       <c r="B6" s="72"/>
       <c r="C6" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="77"/>
+      <c r="A7" s="75"/>
       <c r="B7" s="72"/>
       <c r="C7" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="77"/>
+      <c r="A8" s="75"/>
       <c r="B8" s="72"/>
       <c r="C8" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="77"/>
+      <c r="A9" s="75"/>
       <c r="B9" s="72"/>
       <c r="C9" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E9" s="11"/>
       <c r="F9" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="77"/>
+      <c r="A10" s="75"/>
       <c r="B10" s="72"/>
       <c r="C10" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="77"/>
+      <c r="A11" s="75"/>
       <c r="B11" s="72"/>
       <c r="E11" s="10"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="77"/>
-      <c r="B12" s="71" t="s">
-        <v>231</v>
+      <c r="A12" s="75"/>
+      <c r="B12" s="81" t="s">
+        <v>229</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E12" s="13"/>
       <c r="F12" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="77"/>
+      <c r="A13" s="75"/>
       <c r="B13" s="72"/>
       <c r="C13" s="5" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E13" s="8"/>
       <c r="F13" s="5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="77"/>
+      <c r="A14" s="75"/>
       <c r="B14" s="72"/>
       <c r="C14" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E14" s="8"/>
       <c r="F14" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="77"/>
+      <c r="A15" s="75"/>
       <c r="B15" s="72"/>
       <c r="C15" s="5" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E15" s="10"/>
       <c r="F15" s="5" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="77"/>
+      <c r="A16" s="75"/>
       <c r="B16" s="72"/>
       <c r="C16" s="5" t="s">
         <v>84</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E16" s="8"/>
       <c r="F16" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="77"/>
+      <c r="A17" s="75"/>
       <c r="B17" s="72"/>
       <c r="C17" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E17" s="8"/>
       <c r="F17" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="77"/>
+      <c r="A18" s="75"/>
       <c r="B18" s="72"/>
       <c r="C18" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E18" s="11"/>
       <c r="F18" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="77"/>
+      <c r="A19" s="75"/>
       <c r="B19" s="72"/>
       <c r="C19" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E19" s="11"/>
       <c r="F19" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="77"/>
+      <c r="A20" s="75"/>
       <c r="B20" s="72"/>
       <c r="C20" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E20" s="11"/>
       <c r="F20" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="77"/>
+      <c r="A21" s="75"/>
       <c r="B21" s="72"/>
       <c r="C21" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E21" s="11"/>
       <c r="F21" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="77"/>
-      <c r="B22" s="74"/>
+      <c r="A22" s="75"/>
+      <c r="B22" s="73"/>
       <c r="C22" s="14"/>
       <c r="D22" s="14"/>
       <c r="E22" s="15"/>
       <c r="F22" s="14"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="77"/>
-      <c r="B23" s="71" t="s">
-        <v>273</v>
+      <c r="A23" s="75"/>
+      <c r="B23" s="81" t="s">
+        <v>271</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E23" s="8"/>
       <c r="F23" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="77"/>
+      <c r="A24" s="75"/>
       <c r="B24" s="72"/>
       <c r="C24" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E24" s="8"/>
       <c r="F24" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="77"/>
+      <c r="A25" s="75"/>
       <c r="B25" s="72"/>
       <c r="C25" s="5" t="s">
         <v>84</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E25" s="10"/>
       <c r="F25" s="5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="77"/>
+      <c r="A26" s="75"/>
       <c r="B26" s="72"/>
       <c r="C26" s="5" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E26" s="11"/>
       <c r="F26" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="77"/>
+      <c r="A27" s="75"/>
       <c r="B27" s="72"/>
       <c r="C27" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E27" s="11"/>
       <c r="F27" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="77"/>
+      <c r="A28" s="75"/>
       <c r="B28" s="72"/>
       <c r="C28" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E28" s="11"/>
       <c r="F28" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="77"/>
+      <c r="A29" s="75"/>
       <c r="B29" s="72"/>
       <c r="C29" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E29" s="11"/>
       <c r="F29" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="77"/>
+      <c r="A30" s="75"/>
       <c r="B30" s="72"/>
       <c r="C30" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E30" s="10"/>
       <c r="F30" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="77"/>
+      <c r="A31" s="75"/>
       <c r="B31" s="72"/>
       <c r="C31" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E31" s="10"/>
       <c r="F31" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="77"/>
-      <c r="B32" s="74"/>
+      <c r="A32" s="75"/>
+      <c r="B32" s="73"/>
       <c r="C32" s="14"/>
       <c r="D32" s="14"/>
       <c r="E32" s="15"/>
       <c r="F32" s="14"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="77"/>
-      <c r="B33" s="79" t="s">
-        <v>360</v>
+      <c r="A33" s="75"/>
+      <c r="B33" s="78" t="s">
+        <v>358</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E33" s="8"/>
       <c r="F33" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="77"/>
-      <c r="B34" s="79"/>
+      <c r="A34" s="75"/>
+      <c r="B34" s="78"/>
       <c r="C34" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E34" s="8"/>
       <c r="F34" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="77"/>
-      <c r="B35" s="79"/>
+      <c r="A35" s="75"/>
+      <c r="B35" s="78"/>
       <c r="C35" s="5" t="s">
         <v>84</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E35" s="10"/>
       <c r="F35" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="77"/>
-      <c r="B36" s="79"/>
+      <c r="A36" s="75"/>
+      <c r="B36" s="78"/>
       <c r="C36" s="5" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E36" s="10"/>
       <c r="F36" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="77"/>
-      <c r="B37" s="79"/>
+      <c r="A37" s="75"/>
+      <c r="B37" s="78"/>
       <c r="C37" s="5" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E37" s="10"/>
       <c r="F37" s="5" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="77"/>
-      <c r="B38" s="79"/>
+      <c r="A38" s="75"/>
+      <c r="B38" s="78"/>
       <c r="C38" s="5" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E38" s="11"/>
       <c r="F38" s="5" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="77"/>
-      <c r="B39" s="79"/>
+      <c r="A39" s="75"/>
+      <c r="B39" s="78"/>
       <c r="C39" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E39" s="11"/>
       <c r="F39" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="77"/>
-      <c r="B40" s="79"/>
+      <c r="A40" s="75"/>
+      <c r="B40" s="78"/>
       <c r="C40" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E40" s="11"/>
       <c r="F40" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="77"/>
-      <c r="B41" s="79"/>
+      <c r="A41" s="75"/>
+      <c r="B41" s="78"/>
       <c r="C41" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E41" s="11"/>
       <c r="F41" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="77"/>
-      <c r="B42" s="79"/>
+      <c r="A42" s="75"/>
+      <c r="B42" s="78"/>
       <c r="C42" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E42" s="11"/>
       <c r="F42" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="77"/>
-      <c r="B43" s="79"/>
+      <c r="A43" s="75"/>
+      <c r="B43" s="78"/>
       <c r="C43" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E43" s="10"/>
       <c r="F43" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="77"/>
-      <c r="B44" s="79"/>
+      <c r="A44" s="75"/>
+      <c r="B44" s="78"/>
       <c r="C44" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E44" s="10"/>
       <c r="F44" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="77"/>
-      <c r="B45" s="79"/>
+      <c r="A45" s="75"/>
+      <c r="B45" s="78"/>
       <c r="E45" s="10"/>
     </row>
     <row r="46" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="75" t="s">
+      <c r="A46" s="74" t="s">
         <v>71</v>
       </c>
-      <c r="B46" s="83" t="s">
+      <c r="B46" s="85" t="s">
         <v>3</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E46" s="16"/>
       <c r="F46" s="6" t="s">
-        <v>188</v>
+        <v>386</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="77"/>
-      <c r="B47" s="79"/>
+      <c r="A47" s="75"/>
+      <c r="B47" s="78"/>
       <c r="C47" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E47" s="10"/>
       <c r="F47" s="5" t="s">
-        <v>30</v>
+        <v>387</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="77"/>
-      <c r="B48" s="79"/>
+      <c r="A48" s="75"/>
+      <c r="B48" s="78"/>
       <c r="C48" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E48" s="11"/>
       <c r="F48" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="77"/>
-      <c r="B49" s="79"/>
+      <c r="A49" s="75"/>
+      <c r="B49" s="78"/>
       <c r="C49" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E49" s="10"/>
       <c r="F49" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="77"/>
-      <c r="B50" s="79"/>
+      <c r="A50" s="75"/>
+      <c r="B50" s="78"/>
       <c r="C50" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E50" s="10"/>
       <c r="F50" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="77"/>
-      <c r="B51" s="79"/>
+      <c r="A51" s="75"/>
+      <c r="B51" s="78"/>
       <c r="C51" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E51" s="10"/>
       <c r="F51" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="77"/>
-      <c r="B52" s="79"/>
+      <c r="A52" s="75"/>
+      <c r="B52" s="78"/>
       <c r="C52" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E52" s="10"/>
       <c r="F52" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="77"/>
-      <c r="B53" s="79"/>
+      <c r="A53" s="75"/>
+      <c r="B53" s="78"/>
       <c r="C53" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E53" s="10"/>
       <c r="F53" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="77"/>
-      <c r="B54" s="79"/>
+      <c r="A54" s="75"/>
+      <c r="B54" s="78"/>
       <c r="C54" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E54" s="10"/>
       <c r="F54" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="77"/>
-      <c r="B55" s="84"/>
+      <c r="A55" s="75"/>
+      <c r="B55" s="79"/>
       <c r="C55" s="14"/>
       <c r="D55" s="14"/>
       <c r="E55" s="15"/>
       <c r="F55" s="14"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="77"/>
-      <c r="B56" s="79" t="s">
-        <v>317</v>
+      <c r="A56" s="75"/>
+      <c r="B56" s="78" t="s">
+        <v>315</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E56" s="8"/>
       <c r="F56" s="5" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="77"/>
-      <c r="B57" s="79"/>
+      <c r="A57" s="75"/>
+      <c r="B57" s="78"/>
       <c r="C57" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E57" s="10"/>
       <c r="F57" s="5" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="77"/>
-      <c r="B58" s="79"/>
+      <c r="A58" s="75"/>
+      <c r="B58" s="78"/>
       <c r="C58" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E58" s="11"/>
       <c r="F58" s="5" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="77"/>
-      <c r="B59" s="79"/>
+      <c r="A59" s="75"/>
+      <c r="B59" s="78"/>
       <c r="C59" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E59" s="10"/>
       <c r="F59" s="5" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="77"/>
-      <c r="B60" s="79"/>
+      <c r="A60" s="75"/>
+      <c r="B60" s="78"/>
       <c r="C60" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E60" s="10"/>
       <c r="F60" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="77"/>
-      <c r="B61" s="79"/>
+      <c r="A61" s="75"/>
+      <c r="B61" s="78"/>
       <c r="C61" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E61" s="10"/>
       <c r="F61" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="77"/>
-      <c r="B62" s="79"/>
+      <c r="A62" s="75"/>
+      <c r="B62" s="78"/>
       <c r="C62" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E62" s="10"/>
       <c r="F62" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="77"/>
-      <c r="B63" s="79"/>
+      <c r="A63" s="75"/>
+      <c r="B63" s="78"/>
       <c r="C63" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E63" s="10"/>
       <c r="F63" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="77"/>
-      <c r="B64" s="79"/>
+      <c r="A64" s="75"/>
+      <c r="B64" s="78"/>
       <c r="C64" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E64" s="10"/>
       <c r="F64" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="77"/>
-      <c r="B65" s="84"/>
+      <c r="A65" s="75"/>
+      <c r="B65" s="79"/>
       <c r="E65" s="10"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="77"/>
-      <c r="B66" s="81" t="s">
+      <c r="A66" s="75"/>
+      <c r="B66" s="77" t="s">
         <v>6</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E66" s="17"/>
       <c r="F66" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="77"/>
-      <c r="B67" s="79"/>
+      <c r="A67" s="75"/>
+      <c r="B67" s="78"/>
       <c r="C67" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E67" s="10"/>
       <c r="F67" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="77"/>
+      <c r="A68" s="75"/>
       <c r="B68" s="72"/>
       <c r="C68" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D68" s="5" t="s">
         <v>112</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>113</v>
       </c>
       <c r="E68" s="8"/>
       <c r="F68" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="77"/>
+      <c r="A69" s="75"/>
       <c r="B69" s="72"/>
       <c r="C69" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E69" s="8"/>
       <c r="F69" s="5" t="s">
@@ -4222,210 +4222,210 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="77"/>
+      <c r="A70" s="75"/>
       <c r="B70" s="72"/>
       <c r="C70" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E70" s="8"/>
       <c r="F70" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="77"/>
+      <c r="A71" s="75"/>
       <c r="B71" s="72"/>
       <c r="C71" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E71" s="10"/>
       <c r="F71" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="77"/>
+      <c r="A72" s="75"/>
       <c r="B72" s="72"/>
       <c r="C72" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E72" s="8"/>
       <c r="F72" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="77"/>
+      <c r="A73" s="75"/>
       <c r="B73" s="72"/>
       <c r="C73" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E73" s="10"/>
       <c r="F73" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="77"/>
+      <c r="A74" s="75"/>
       <c r="B74" s="72"/>
       <c r="C74" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E74" s="10"/>
       <c r="F74" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="77"/>
+      <c r="A75" s="75"/>
       <c r="B75" s="72"/>
       <c r="C75" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E75" s="10"/>
       <c r="F75" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="77"/>
+      <c r="A76" s="75"/>
       <c r="B76" s="72"/>
       <c r="C76" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E76" s="10"/>
       <c r="F76" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="80"/>
-      <c r="B77" s="82"/>
+      <c r="A77" s="76"/>
+      <c r="B77" s="84"/>
       <c r="C77" s="18"/>
       <c r="D77" s="18"/>
       <c r="E77" s="19"/>
       <c r="F77" s="18"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="75" t="s">
+      <c r="A78" s="74" t="s">
         <v>72</v>
       </c>
-      <c r="B78" s="78" t="s">
+      <c r="B78" s="71" t="s">
         <v>73</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E78" s="16"/>
       <c r="F78" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="77"/>
-      <c r="B79" s="73"/>
+      <c r="A79" s="75"/>
+      <c r="B79" s="82"/>
       <c r="C79" s="20" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D79" s="20" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E79" s="21"/>
       <c r="F79" s="20" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="77"/>
-      <c r="B80" s="74"/>
+      <c r="A80" s="75"/>
+      <c r="B80" s="73"/>
       <c r="C80" s="14"/>
       <c r="D80" s="14"/>
       <c r="E80" s="22"/>
       <c r="F80" s="14"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="77"/>
-      <c r="B81" s="73" t="s">
-        <v>343</v>
+      <c r="A81" s="75"/>
+      <c r="B81" s="82" t="s">
+        <v>341</v>
       </c>
       <c r="C81" s="20" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D81" s="20" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E81" s="21"/>
       <c r="F81" s="20" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" s="75"/>
+      <c r="B82" s="82"/>
+      <c r="C82" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="D82" s="5" t="s">
         <v>348</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="77"/>
-      <c r="B82" s="73"/>
-      <c r="C82" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="D82" s="5" t="s">
-        <v>350</v>
       </c>
       <c r="E82" s="8"/>
       <c r="F82" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="77"/>
-      <c r="B83" s="73"/>
+      <c r="A83" s="75"/>
+      <c r="B83" s="82"/>
       <c r="E83" s="8"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="77"/>
-      <c r="B84" s="81" t="s">
+      <c r="A84" s="75"/>
+      <c r="B84" s="77" t="s">
         <v>4</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D84" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E84" s="17"/>
       <c r="F84" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="77"/>
-      <c r="B85" s="79"/>
+      <c r="A85" s="75"/>
+      <c r="B85" s="78"/>
       <c r="C85" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E85" s="1"/>
       <c r="F85" s="5" t="s">
@@ -4433,131 +4433,131 @@
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="77"/>
-      <c r="B86" s="79"/>
+      <c r="A86" s="75"/>
+      <c r="B86" s="78"/>
       <c r="C86" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E86" s="1"/>
       <c r="F86" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="77"/>
-      <c r="B87" s="79"/>
+      <c r="A87" s="75"/>
+      <c r="B87" s="78"/>
       <c r="C87" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E87" s="8"/>
       <c r="F87" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="77"/>
-      <c r="B88" s="79"/>
+      <c r="A88" s="75"/>
+      <c r="B88" s="78"/>
       <c r="C88" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D88" s="5" t="s">
         <v>156</v>
-      </c>
-      <c r="D88" s="5" t="s">
-        <v>157</v>
       </c>
       <c r="E88" s="11"/>
       <c r="F88" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="77"/>
-      <c r="B89" s="79"/>
+      <c r="A89" s="75"/>
+      <c r="B89" s="78"/>
       <c r="C89" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="D89" s="5" t="s">
         <v>162</v>
-      </c>
-      <c r="D89" s="5" t="s">
-        <v>163</v>
       </c>
       <c r="E89" s="8"/>
       <c r="F89" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="77"/>
-      <c r="B90" s="79"/>
+      <c r="A90" s="75"/>
+      <c r="B90" s="78"/>
       <c r="C90" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="D90" s="5" t="s">
         <v>198</v>
-      </c>
-      <c r="D90" s="5" t="s">
-        <v>200</v>
       </c>
       <c r="E90" s="8"/>
       <c r="F90" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="77"/>
-      <c r="B91" s="79"/>
+      <c r="A91" s="75"/>
+      <c r="B91" s="78"/>
       <c r="C91" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E91" s="10"/>
       <c r="F91" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="77"/>
-      <c r="B92" s="79"/>
+      <c r="A92" s="75"/>
+      <c r="B92" s="78"/>
       <c r="C92" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="D92" s="5" t="s">
         <v>190</v>
-      </c>
-      <c r="D92" s="5" t="s">
-        <v>192</v>
       </c>
       <c r="E92" s="10"/>
       <c r="F92" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="77"/>
-      <c r="B93" s="84"/>
+      <c r="A93" s="75"/>
+      <c r="B93" s="79"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="77"/>
-      <c r="B94" s="81" t="s">
+      <c r="A94" s="75"/>
+      <c r="B94" s="77" t="s">
         <v>5</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D94" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E94" s="17"/>
       <c r="F94" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="77"/>
-      <c r="B95" s="79"/>
+      <c r="A95" s="75"/>
+      <c r="B95" s="78"/>
       <c r="C95" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E95" s="1"/>
       <c r="F95" s="5" t="s">
@@ -4565,687 +4565,678 @@
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="77"/>
-      <c r="B96" s="79"/>
+      <c r="A96" s="75"/>
+      <c r="B96" s="78"/>
       <c r="C96" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E96" s="1"/>
       <c r="F96" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="77"/>
-      <c r="B97" s="79"/>
+      <c r="A97" s="75"/>
+      <c r="B97" s="78"/>
       <c r="C97" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D97" s="5" t="s">
         <v>142</v>
-      </c>
-      <c r="D97" s="5" t="s">
-        <v>143</v>
       </c>
       <c r="E97" s="1"/>
       <c r="F97" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="77"/>
-      <c r="B98" s="79"/>
+      <c r="A98" s="75"/>
+      <c r="B98" s="78"/>
       <c r="C98" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E98" s="11"/>
       <c r="F98" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="77"/>
-      <c r="B99" s="79"/>
+      <c r="A99" s="75"/>
+      <c r="B99" s="78"/>
       <c r="C99" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E99" s="23"/>
       <c r="F99" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="77"/>
-      <c r="B100" s="79"/>
+      <c r="A100" s="75"/>
+      <c r="B100" s="78"/>
       <c r="C100" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E100" s="23"/>
       <c r="F100" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="77"/>
-      <c r="B101" s="79"/>
+      <c r="A101" s="75"/>
+      <c r="B101" s="78"/>
       <c r="C101" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D101" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="D101" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="E101" s="10"/>
       <c r="F101" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="77"/>
-      <c r="B102" s="79"/>
+      <c r="A102" s="75"/>
+      <c r="B102" s="78"/>
       <c r="C102" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E102" s="10"/>
       <c r="F102" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="80"/>
-      <c r="B103" s="85"/>
+      <c r="A103" s="76"/>
+      <c r="B103" s="80"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="75" t="s">
+      <c r="A104" s="74" t="s">
         <v>76</v>
       </c>
-      <c r="B104" s="78" t="s">
+      <c r="B104" s="71" t="s">
         <v>73</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E104" s="7"/>
       <c r="F104" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="77"/>
+      <c r="A105" s="75"/>
       <c r="B105" s="72"/>
       <c r="C105" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E105" s="10"/>
       <c r="F105" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="77"/>
+      <c r="A106" s="75"/>
       <c r="B106" s="72"/>
       <c r="C106" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E106" s="10"/>
       <c r="F106" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="77"/>
-      <c r="B107" s="74"/>
+      <c r="A107" s="75"/>
+      <c r="B107" s="73"/>
       <c r="C107" s="14"/>
       <c r="D107" s="14"/>
       <c r="E107" s="15"/>
       <c r="F107" s="14"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="77"/>
-      <c r="B108" s="71" t="s">
+      <c r="A108" s="75"/>
+      <c r="B108" s="81" t="s">
+        <v>301</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="D108" s="5" t="s">
         <v>303</v>
-      </c>
-      <c r="C108" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="D108" s="5" t="s">
-        <v>305</v>
       </c>
       <c r="E108" s="10"/>
       <c r="F108" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="77"/>
+      <c r="A109" s="75"/>
       <c r="B109" s="72"/>
       <c r="C109" s="5" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E109" s="10"/>
       <c r="F109" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="77"/>
+      <c r="A110" s="75"/>
       <c r="B110" s="72"/>
       <c r="C110" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E110" s="10"/>
       <c r="F110" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="77"/>
-      <c r="B111" s="74"/>
+      <c r="A111" s="75"/>
+      <c r="B111" s="73"/>
       <c r="E111" s="10"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="77"/>
-      <c r="B112" s="71" t="s">
+      <c r="A112" s="75"/>
+      <c r="B112" s="81" t="s">
         <v>79</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D112" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E112" s="17"/>
       <c r="F112" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="77"/>
+      <c r="A113" s="75"/>
       <c r="B113" s="72"/>
       <c r="C113" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E113" s="10"/>
       <c r="F113" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="77"/>
-      <c r="B114" s="74"/>
+      <c r="A114" s="75"/>
+      <c r="B114" s="73"/>
       <c r="C114" s="14"/>
       <c r="D114" s="14"/>
       <c r="E114" s="15"/>
       <c r="F114" s="14"/>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="77"/>
-      <c r="B115" s="71" t="s">
+      <c r="A115" s="75"/>
+      <c r="B115" s="81" t="s">
+        <v>260</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="D115" s="5" t="s">
         <v>262</v>
-      </c>
-      <c r="C115" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="D115" s="5" t="s">
-        <v>264</v>
       </c>
       <c r="E115" s="10"/>
       <c r="F115" s="5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="77"/>
+      <c r="A116" s="75"/>
       <c r="B116" s="72"/>
       <c r="C116" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="D116" s="5" t="s">
         <v>263</v>
-      </c>
-      <c r="D116" s="5" t="s">
-        <v>265</v>
       </c>
       <c r="E116" s="10"/>
       <c r="F116" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="80"/>
-      <c r="B117" s="82"/>
+      <c r="A117" s="76"/>
+      <c r="B117" s="84"/>
       <c r="C117" s="18"/>
       <c r="D117" s="18"/>
       <c r="E117" s="19"/>
       <c r="F117" s="18"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="75" t="s">
-        <v>164</v>
-      </c>
-      <c r="B118" s="78" t="s">
+      <c r="A118" s="74" t="s">
+        <v>163</v>
+      </c>
+      <c r="B118" s="71" t="s">
         <v>13</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E118" s="6"/>
       <c r="F118" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="76"/>
+      <c r="A119" s="83"/>
       <c r="B119" s="72"/>
       <c r="C119" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D119" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="D119" s="5" t="s">
-        <v>176</v>
-      </c>
       <c r="F119" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="76"/>
-      <c r="B120" s="74"/>
+      <c r="A120" s="83"/>
+      <c r="B120" s="73"/>
       <c r="C120" s="14"/>
       <c r="D120" s="14"/>
       <c r="E120" s="14"/>
       <c r="F120" s="14"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="76"/>
-      <c r="B121" s="71" t="s">
-        <v>184</v>
+      <c r="A121" s="83"/>
+      <c r="B121" s="81" t="s">
+        <v>183</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="76"/>
+      <c r="A122" s="83"/>
       <c r="B122" s="72"/>
       <c r="C122" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="76"/>
+      <c r="A123" s="83"/>
       <c r="B123" s="72"/>
       <c r="C123" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="76"/>
+      <c r="A124" s="83"/>
       <c r="B124" s="72"/>
       <c r="C124" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="76"/>
+      <c r="A125" s="83"/>
       <c r="B125" s="72"/>
       <c r="C125" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="76"/>
+      <c r="A126" s="83"/>
       <c r="B126" s="72"/>
       <c r="C126" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="76"/>
+      <c r="A127" s="83"/>
       <c r="B127" s="72"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="76"/>
-      <c r="B128" s="71" t="s">
-        <v>208</v>
+      <c r="A128" s="83"/>
+      <c r="B128" s="81" t="s">
+        <v>206</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D128" s="12" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E128" s="12"/>
       <c r="F128" s="12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="76"/>
+      <c r="A129" s="83"/>
       <c r="B129" s="72"/>
       <c r="C129" s="5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="76"/>
+      <c r="A130" s="83"/>
       <c r="B130" s="72"/>
       <c r="C130" s="5" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="76"/>
+      <c r="A131" s="83"/>
       <c r="B131" s="72"/>
       <c r="C131" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="76"/>
+      <c r="A132" s="83"/>
       <c r="B132" s="72"/>
       <c r="C132" s="5" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="76"/>
+      <c r="A133" s="83"/>
       <c r="B133" s="72"/>
       <c r="C133" s="5" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="76"/>
+      <c r="A134" s="83"/>
       <c r="B134" s="72"/>
       <c r="C134" s="5" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="76"/>
+      <c r="A135" s="83"/>
       <c r="B135" s="72"/>
       <c r="C135" s="5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D135" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="F135" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="F135" s="5" t="s">
-        <v>220</v>
-      </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="76"/>
+      <c r="A136" s="83"/>
       <c r="B136" s="72"/>
       <c r="C136" s="5" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="76"/>
+      <c r="A137" s="83"/>
       <c r="B137" s="72"/>
       <c r="C137" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="76"/>
+      <c r="A138" s="83"/>
       <c r="B138" s="72"/>
       <c r="C138" s="5" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="76"/>
+      <c r="A139" s="83"/>
       <c r="B139" s="72"/>
       <c r="C139" s="5" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="76"/>
+      <c r="A140" s="83"/>
       <c r="B140" s="72"/>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="76"/>
-      <c r="B141" s="71" t="s">
+      <c r="A141" s="83"/>
+      <c r="B141" s="81" t="s">
+        <v>222</v>
+      </c>
+      <c r="C141" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="C141" s="12" t="s">
-        <v>226</v>
-      </c>
       <c r="D141" s="12" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E141" s="12"/>
       <c r="F141" s="12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="76"/>
-      <c r="B142" s="73"/>
+      <c r="A142" s="83"/>
+      <c r="B142" s="82"/>
       <c r="C142" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="D142" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="F142" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="D142" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="F142" s="5" t="s">
-        <v>316</v>
-      </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="76"/>
-      <c r="B143" s="73"/>
+      <c r="A143" s="83"/>
+      <c r="B143" s="82"/>
       <c r="C143" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="76"/>
-      <c r="B144" s="73"/>
+      <c r="A144" s="83"/>
+      <c r="B144" s="82"/>
       <c r="C144" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="D144" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="F144" s="5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A145" s="83"/>
+      <c r="B145" s="82"/>
+      <c r="C145" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D144" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="F144" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A145" s="76"/>
-      <c r="B145" s="73"/>
-      <c r="C145" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="D145" s="5" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A146" s="76"/>
-      <c r="B146" s="74"/>
+      <c r="A146" s="83"/>
+      <c r="B146" s="73"/>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A147" s="76"/>
-      <c r="B147" s="71" t="s">
+      <c r="A147" s="83"/>
+      <c r="B147" s="81" t="s">
+        <v>380</v>
+      </c>
+      <c r="C147" s="12" t="s">
+        <v>381</v>
+      </c>
+      <c r="D147" s="12" t="s">
         <v>382</v>
-      </c>
-      <c r="C147" s="12" t="s">
-        <v>383</v>
-      </c>
-      <c r="D147" s="12" t="s">
-        <v>384</v>
       </c>
       <c r="E147" s="12"/>
       <c r="F147" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A148" s="76"/>
+      <c r="A148" s="83"/>
       <c r="B148" s="72"/>
       <c r="C148" s="5" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A149" s="76"/>
+      <c r="A149" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="B118:B120"/>
-    <mergeCell ref="A78:A103"/>
-    <mergeCell ref="B84:B93"/>
-    <mergeCell ref="B94:B103"/>
-    <mergeCell ref="A104:A117"/>
-    <mergeCell ref="B112:B114"/>
-    <mergeCell ref="B104:B107"/>
-    <mergeCell ref="B108:B111"/>
-    <mergeCell ref="B78:B80"/>
     <mergeCell ref="B147:B148"/>
     <mergeCell ref="B141:B146"/>
     <mergeCell ref="A118:A149"/>
@@ -5262,6 +5253,15 @@
     <mergeCell ref="B115:B117"/>
     <mergeCell ref="B121:B127"/>
     <mergeCell ref="B128:B140"/>
+    <mergeCell ref="B118:B120"/>
+    <mergeCell ref="A78:A103"/>
+    <mergeCell ref="B84:B93"/>
+    <mergeCell ref="B94:B103"/>
+    <mergeCell ref="A104:A117"/>
+    <mergeCell ref="B112:B114"/>
+    <mergeCell ref="B104:B107"/>
+    <mergeCell ref="B108:B111"/>
+    <mergeCell ref="B78:B80"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Methanol/Methanol_Bio_Brownfield_Memmingen/Datenbank.xlsx
+++ b/Methanol/Methanol_Bio_Brownfield_Memmingen/Datenbank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methanol\Methanol_Bio_Brownfield_Memmingen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Methanol\Methanol_Bio_Brownfield_Memmingen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21507B0B-967E-42C4-8888-FBDEF8EFE66B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E10240A4-A514-4B48-A4F3-A3CD58B98EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -1343,10 +1343,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -1486,159 +1486,145 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1966,1277 +1952,1276 @@
   <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" style="28" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" style="27" customWidth="1"/>
-    <col min="3" max="3" width="36.21875" style="28" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21" style="28" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19" style="33" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="40.77734375" style="28" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.77734375" style="28" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.77734375" style="28" customWidth="1"/>
-    <col min="9" max="9" width="13.88671875" style="28" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14" style="28" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" style="28" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="28"/>
+    <col min="1" max="1" width="10.88671875" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="25" customWidth="1"/>
+    <col min="3" max="3" width="36.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19" style="30" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.77734375" customWidth="1"/>
+    <col min="9" max="9" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="F1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="27"/>
+      <c r="G1" s="25"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="30">
+      <c r="E2" s="27">
         <v>0.66600000000000004</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="F2" s="26" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="58"/>
-      <c r="B3" s="66"/>
-      <c r="C3" s="28" t="s">
+      <c r="A3" s="53"/>
+      <c r="B3" s="60"/>
+      <c r="C3" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="D3" t="s">
         <v>63</v>
       </c>
-      <c r="E3" s="31">
+      <c r="E3" s="28">
         <v>50</v>
       </c>
-      <c r="F3" s="28" t="s">
+      <c r="F3" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="58"/>
-      <c r="B4" s="66"/>
-      <c r="C4" s="28" t="s">
+      <c r="A4" s="53"/>
+      <c r="B4" s="60"/>
+      <c r="C4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="32">
-        <v>1000</v>
-      </c>
-      <c r="F4" s="28" t="s">
+      <c r="E4" s="29">
+        <v>1500</v>
+      </c>
+      <c r="F4" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="58"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="28" t="s">
+      <c r="A5" s="53"/>
+      <c r="B5" s="60"/>
+      <c r="C5" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="33">
+      <c r="E5" s="30">
         <v>0.03</v>
       </c>
-      <c r="F5" s="28" t="s">
+      <c r="F5" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="58"/>
-      <c r="B6" s="66"/>
-      <c r="C6" s="28" t="s">
+      <c r="A6" s="53"/>
+      <c r="B6" s="60"/>
+      <c r="C6" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="D6" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="34">
+      <c r="E6" s="31">
         <v>20</v>
       </c>
-      <c r="F6" s="28" t="s">
+      <c r="F6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="58"/>
-      <c r="B7" s="66"/>
-      <c r="C7" s="28" t="s">
+      <c r="A7" s="53"/>
+      <c r="B7" s="60"/>
+      <c r="C7" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="28" t="s">
+      <c r="D7" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="33">
+      <c r="E7" s="30">
         <v>0.08</v>
       </c>
-      <c r="F7" s="28" t="s">
+      <c r="F7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="58"/>
-      <c r="B8" s="69" t="s">
+      <c r="A8" s="53"/>
+      <c r="B8" s="63" t="s">
         <v>229</v>
       </c>
-      <c r="C8" s="35" t="s">
+      <c r="C8" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="D8" s="35" t="s">
+      <c r="D8" s="32" t="s">
         <v>231</v>
       </c>
-      <c r="E8" s="36">
+      <c r="E8" s="33">
         <v>1.5</v>
       </c>
-      <c r="F8" s="35" t="s">
+      <c r="F8" s="32" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="58"/>
-      <c r="B9" s="66"/>
-      <c r="C9" s="28" t="s">
+      <c r="A9" s="53"/>
+      <c r="B9" s="60"/>
+      <c r="C9" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="28" t="s">
+      <c r="D9" t="s">
         <v>232</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="28">
         <v>285.39999999999998</v>
       </c>
-      <c r="F9" s="28" t="s">
+      <c r="F9" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="58"/>
-      <c r="B10" s="66"/>
-      <c r="C10" s="28" t="s">
+      <c r="A10" s="53"/>
+      <c r="B10" s="60"/>
+      <c r="C10" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="28" t="s">
+      <c r="D10" t="s">
         <v>233</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="28">
         <v>5110</v>
       </c>
-      <c r="F10" s="31" t="s">
+      <c r="F10" s="28" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="58"/>
-      <c r="B11" s="66"/>
-      <c r="C11" s="28" t="s">
+      <c r="A11" s="53"/>
+      <c r="B11" s="60"/>
+      <c r="C11" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="28" t="s">
+      <c r="D11" t="s">
         <v>234</v>
       </c>
-      <c r="E11" s="33">
+      <c r="E11" s="30">
         <v>0.05</v>
       </c>
-      <c r="F11" s="28" t="s">
+      <c r="F11" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="58"/>
-      <c r="B12" s="66"/>
-      <c r="C12" s="28" t="s">
+      <c r="A12" s="53"/>
+      <c r="B12" s="60"/>
+      <c r="C12" t="s">
         <v>86</v>
       </c>
-      <c r="D12" s="28" t="s">
+      <c r="D12" t="s">
         <v>235</v>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="28">
         <v>0.189</v>
       </c>
-      <c r="F12" s="28" t="s">
+      <c r="F12" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="58"/>
-      <c r="B13" s="66"/>
-      <c r="C13" s="28" t="s">
+      <c r="A13" s="53"/>
+      <c r="B13" s="60"/>
+      <c r="C13" t="s">
         <v>244</v>
       </c>
-      <c r="D13" s="28" t="s">
+      <c r="D13" t="s">
         <v>240</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="28">
         <v>1.375</v>
       </c>
-      <c r="F13" s="28" t="s">
+      <c r="F13" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="58"/>
-      <c r="B14" s="66"/>
-      <c r="C14" s="28" t="s">
+      <c r="A14" s="53"/>
+      <c r="B14" s="60"/>
+      <c r="C14" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="28" t="s">
+      <c r="D14" t="s">
         <v>236</v>
       </c>
-      <c r="E14" s="34">
+      <c r="E14" s="31">
         <v>25</v>
       </c>
-      <c r="F14" s="28" t="s">
+      <c r="F14" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="58"/>
-      <c r="B15" s="70"/>
-      <c r="C15" s="37" t="s">
+      <c r="A15" s="53"/>
+      <c r="B15" s="64"/>
+      <c r="C15" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="37" t="s">
+      <c r="D15" s="34" t="s">
         <v>237</v>
       </c>
-      <c r="E15" s="38">
+      <c r="E15" s="35">
         <v>0.08</v>
       </c>
-      <c r="F15" s="37" t="s">
+      <c r="F15" s="34" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="58"/>
-      <c r="B16" s="69" t="s">
+      <c r="A16" s="53"/>
+      <c r="B16" s="63" t="s">
         <v>271</v>
       </c>
-      <c r="C16" s="35" t="s">
+      <c r="C16" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="35" t="s">
+      <c r="D16" s="32" t="s">
         <v>274</v>
       </c>
-      <c r="E16" s="39">
+      <c r="E16" s="36">
         <v>3.7</v>
       </c>
-      <c r="F16" s="35" t="s">
+      <c r="F16" s="32" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="58"/>
-      <c r="B17" s="66"/>
-      <c r="C17" s="28" t="s">
+      <c r="A17" s="53"/>
+      <c r="B17" s="60"/>
+      <c r="C17" t="s">
         <v>84</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D17" t="s">
         <v>275</v>
       </c>
-      <c r="E17" s="33">
+      <c r="E17" s="30">
         <v>0.27</v>
       </c>
-      <c r="F17" s="28" t="s">
+      <c r="F17" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="58"/>
-      <c r="B18" s="66"/>
-      <c r="C18" s="28" t="s">
+      <c r="A18" s="53"/>
+      <c r="B18" s="60"/>
+      <c r="C18" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="28" t="s">
+      <c r="D18" t="s">
         <v>276</v>
       </c>
-      <c r="E18" s="33">
+      <c r="E18" s="30">
         <v>700</v>
       </c>
-      <c r="F18" s="28" t="s">
+      <c r="F18" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="58"/>
-      <c r="B19" s="66"/>
-      <c r="C19" s="28" t="s">
+      <c r="A19" s="53"/>
+      <c r="B19" s="60"/>
+      <c r="C19" t="s">
         <v>11</v>
       </c>
-      <c r="D19" s="28" t="s">
+      <c r="D19" t="s">
         <v>277</v>
       </c>
-      <c r="E19" s="33">
+      <c r="E19" s="30">
         <v>0.02</v>
       </c>
-      <c r="F19" s="28" t="s">
+      <c r="F19" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="58"/>
-      <c r="B20" s="66"/>
-      <c r="C20" s="28" t="s">
+      <c r="A20" s="53"/>
+      <c r="B20" s="60"/>
+      <c r="C20" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="28" t="s">
+      <c r="D20" t="s">
         <v>278</v>
       </c>
-      <c r="E20" s="33">
+      <c r="E20" s="30">
         <v>20</v>
       </c>
-      <c r="F20" s="28" t="s">
+      <c r="F20" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="58"/>
-      <c r="B21" s="70"/>
-      <c r="C21" s="37" t="s">
+      <c r="A21" s="53"/>
+      <c r="B21" s="64"/>
+      <c r="C21" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="37" t="s">
+      <c r="D21" s="34" t="s">
         <v>279</v>
       </c>
-      <c r="E21" s="38">
+      <c r="E21" s="35">
         <v>0.05</v>
       </c>
-      <c r="F21" s="37" t="s">
+      <c r="F21" s="34" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="58"/>
-      <c r="B22" s="62" t="s">
+      <c r="A22" s="53"/>
+      <c r="B22" s="56" t="s">
         <v>340</v>
       </c>
-      <c r="C22" s="28" t="s">
+      <c r="C22" t="s">
         <v>84</v>
       </c>
-      <c r="D22" s="28" t="s">
+      <c r="D22" t="s">
         <v>349</v>
       </c>
-      <c r="E22" s="31">
+      <c r="E22" s="28">
         <v>0.2</v>
       </c>
-      <c r="F22" s="28" t="s">
+      <c r="F22" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="58"/>
-      <c r="B23" s="62"/>
-      <c r="C23" s="28" t="s">
+      <c r="A23" s="53"/>
+      <c r="B23" s="56"/>
+      <c r="C23" t="s">
         <v>281</v>
       </c>
-      <c r="D23" s="28" t="s">
+      <c r="D23" t="s">
         <v>350</v>
       </c>
-      <c r="E23" s="31">
+      <c r="E23" s="28">
         <v>0.92800000000000005</v>
       </c>
-      <c r="F23" s="28" t="s">
+      <c r="F23" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="58"/>
-      <c r="B24" s="62"/>
-      <c r="C24" s="28" t="s">
+      <c r="A24" s="53"/>
+      <c r="B24" s="56"/>
+      <c r="C24" t="s">
         <v>10</v>
       </c>
-      <c r="D24" s="28" t="s">
+      <c r="D24" t="s">
         <v>351</v>
       </c>
-      <c r="E24" s="31">
+      <c r="E24" s="28">
         <v>1640</v>
       </c>
-      <c r="F24" s="28" t="s">
+      <c r="F24" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="58"/>
-      <c r="B25" s="62"/>
-      <c r="C25" s="28" t="s">
+      <c r="A25" s="53"/>
+      <c r="B25" s="56"/>
+      <c r="C25" t="s">
         <v>377</v>
       </c>
-      <c r="D25" s="28" t="s">
+      <c r="D25" t="s">
         <v>352</v>
       </c>
-      <c r="E25" s="33">
+      <c r="E25" s="30">
         <v>0.04</v>
       </c>
-      <c r="F25" s="28" t="s">
+      <c r="F25" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="58"/>
-      <c r="B26" s="62"/>
-      <c r="C26" s="28" t="s">
+      <c r="A26" s="53"/>
+      <c r="B26" s="56"/>
+      <c r="C26" t="s">
         <v>370</v>
       </c>
-      <c r="D26" s="28" t="s">
+      <c r="D26" t="s">
         <v>371</v>
       </c>
-      <c r="E26" s="33">
+      <c r="E26" s="30">
         <v>2.5</v>
       </c>
-      <c r="F26" s="28" t="s">
+      <c r="F26" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="58"/>
-      <c r="B27" s="62"/>
-      <c r="C27" s="28" t="s">
+      <c r="A27" s="53"/>
+      <c r="B27" s="56"/>
+      <c r="C27" t="s">
         <v>353</v>
       </c>
-      <c r="D27" s="28" t="s">
+      <c r="D27" t="s">
         <v>354</v>
       </c>
-      <c r="E27" s="33">
+      <c r="E27" s="30">
         <v>1.5</v>
       </c>
-      <c r="F27" s="28" t="s">
+      <c r="F27" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="58"/>
-      <c r="B28" s="62"/>
-      <c r="C28" s="28" t="s">
+      <c r="A28" s="53"/>
+      <c r="B28" s="56"/>
+      <c r="C28" t="s">
         <v>378</v>
       </c>
-      <c r="D28" s="28" t="s">
+      <c r="D28" t="s">
         <v>375</v>
       </c>
-      <c r="E28" s="33">
+      <c r="E28" s="30">
         <v>1.5E-3</v>
       </c>
-      <c r="F28" s="28" t="s">
+      <c r="F28" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="58"/>
-      <c r="B29" s="62"/>
-      <c r="C29" s="28" t="s">
+      <c r="A29" s="53"/>
+      <c r="B29" s="56"/>
+      <c r="C29" t="s">
         <v>13</v>
       </c>
-      <c r="D29" s="28" t="s">
+      <c r="D29" t="s">
         <v>356</v>
       </c>
-      <c r="E29" s="34">
+      <c r="E29" s="31">
         <v>25</v>
       </c>
-      <c r="F29" s="28" t="s">
+      <c r="F29" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="58"/>
-      <c r="B30" s="62"/>
-      <c r="C30" s="28" t="s">
+      <c r="A30" s="53"/>
+      <c r="B30" s="56"/>
+      <c r="C30" t="s">
         <v>15</v>
       </c>
-      <c r="D30" s="28" t="s">
+      <c r="D30" t="s">
         <v>357</v>
       </c>
-      <c r="E30" s="33">
+      <c r="E30" s="30">
         <v>0.08</v>
       </c>
-      <c r="F30" s="28" t="s">
+      <c r="F30" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="57" t="s">
+      <c r="A31" s="52" t="s">
         <v>71</v>
       </c>
-      <c r="B31" s="61" t="s">
+      <c r="B31" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="C31" s="29" t="s">
+      <c r="C31" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="D31" s="29" t="s">
+      <c r="D31" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="E31" s="40">
+      <c r="E31" s="37">
         <v>490</v>
       </c>
-      <c r="F31" s="29" t="s">
+      <c r="F31" s="26" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="58"/>
-      <c r="B32" s="62"/>
-      <c r="C32" s="28" t="s">
+      <c r="A32" s="53"/>
+      <c r="B32" s="56"/>
+      <c r="C32" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="28" t="s">
+      <c r="D32" t="s">
         <v>40</v>
       </c>
-      <c r="E32" s="33">
+      <c r="E32" s="30">
         <v>0.01</v>
       </c>
-      <c r="F32" s="28" t="s">
+      <c r="F32" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="58"/>
-      <c r="B33" s="62"/>
-      <c r="C33" s="28" t="s">
+      <c r="A33" s="53"/>
+      <c r="B33" s="56"/>
+      <c r="C33" t="s">
         <v>13</v>
       </c>
-      <c r="D33" s="28" t="s">
+      <c r="D33" t="s">
         <v>32</v>
       </c>
-      <c r="E33" s="34">
+      <c r="E33" s="31">
         <v>20</v>
       </c>
-      <c r="F33" s="28" t="s">
+      <c r="F33" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="58"/>
-      <c r="B34" s="62"/>
-      <c r="C34" s="28" t="s">
+      <c r="A34" s="53"/>
+      <c r="B34" s="56"/>
+      <c r="C34" t="s">
         <v>20</v>
       </c>
-      <c r="D34" s="28" t="s">
+      <c r="D34" t="s">
         <v>34</v>
       </c>
-      <c r="E34" s="41">
+      <c r="E34" s="38">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="F34" s="28" t="s">
+      <c r="F34" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="58"/>
-      <c r="B35" s="62"/>
-      <c r="C35" s="28" t="s">
+      <c r="A35" s="53"/>
+      <c r="B35" s="56"/>
+      <c r="C35" t="s">
         <v>35</v>
       </c>
-      <c r="D35" s="28" t="s">
+      <c r="D35" t="s">
         <v>37</v>
       </c>
-      <c r="E35" s="33">
+      <c r="E35" s="30">
         <v>0.83299999999999996</v>
       </c>
-      <c r="F35" s="28" t="s">
+      <c r="F35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="58"/>
-      <c r="B36" s="62"/>
-      <c r="C36" s="28" t="s">
+      <c r="A36" s="53"/>
+      <c r="B36" s="56"/>
+      <c r="C36" t="s">
         <v>36</v>
       </c>
-      <c r="D36" s="28" t="s">
+      <c r="D36" t="s">
         <v>38</v>
       </c>
-      <c r="E36" s="33">
+      <c r="E36" s="30">
         <v>0.83299999999999996</v>
       </c>
-      <c r="F36" s="28" t="s">
+      <c r="F36" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="58"/>
-      <c r="B37" s="62"/>
-      <c r="C37" s="28" t="s">
+      <c r="A37" s="53"/>
+      <c r="B37" s="56"/>
+      <c r="C37" t="s">
         <v>15</v>
       </c>
-      <c r="D37" s="28" t="s">
+      <c r="D37" t="s">
         <v>31</v>
       </c>
-      <c r="E37" s="33">
+      <c r="E37" s="30">
         <v>0.05</v>
       </c>
-      <c r="F37" s="28" t="s">
+      <c r="F37" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="58"/>
-      <c r="B38" s="63"/>
-      <c r="C38" s="37" t="s">
+      <c r="A38" s="53"/>
+      <c r="B38" s="57"/>
+      <c r="C38" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="D38" s="37" t="s">
+      <c r="D38" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="E38" s="38">
+      <c r="E38" s="35">
         <v>0</v>
       </c>
-      <c r="F38" s="37" t="s">
+      <c r="F38" s="34" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="58"/>
-      <c r="B39" s="64" t="s">
+      <c r="A39" s="53"/>
+      <c r="B39" s="58" t="s">
         <v>315</v>
       </c>
-      <c r="C39" s="29" t="s">
+      <c r="C39" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="D39" s="29" t="s">
+      <c r="D39" s="26" t="s">
         <v>316</v>
       </c>
-      <c r="E39" s="40">
+      <c r="E39" s="37">
         <v>2.83</v>
       </c>
-      <c r="F39" s="29" t="s">
+      <c r="F39" s="26" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="58"/>
-      <c r="B40" s="62"/>
-      <c r="C40" s="28" t="s">
+      <c r="A40" s="53"/>
+      <c r="B40" s="56"/>
+      <c r="C40" t="s">
         <v>11</v>
       </c>
-      <c r="D40" s="28" t="s">
+      <c r="D40" t="s">
         <v>317</v>
       </c>
-      <c r="E40" s="33">
+      <c r="E40" s="30">
         <v>0.03</v>
       </c>
-      <c r="F40" s="28" t="s">
+      <c r="F40" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="58"/>
-      <c r="B41" s="62"/>
-      <c r="C41" s="28" t="s">
+      <c r="A41" s="53"/>
+      <c r="B41" s="56"/>
+      <c r="C41" t="s">
         <v>13</v>
       </c>
-      <c r="D41" s="28" t="s">
+      <c r="D41" t="s">
         <v>318</v>
       </c>
-      <c r="E41" s="34">
+      <c r="E41" s="31">
         <v>30</v>
       </c>
-      <c r="F41" s="28" t="s">
+      <c r="F41" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="58"/>
-      <c r="B42" s="62"/>
-      <c r="C42" s="28" t="s">
+      <c r="A42" s="53"/>
+      <c r="B42" s="56"/>
+      <c r="C42" t="s">
         <v>20</v>
       </c>
-      <c r="D42" s="28" t="s">
+      <c r="D42" t="s">
         <v>319</v>
       </c>
-      <c r="E42" s="33">
+      <c r="E42" s="30">
         <v>7.3999999999999999E-4</v>
       </c>
-      <c r="F42" s="28" t="s">
+      <c r="F42" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="58"/>
-      <c r="B43" s="62"/>
-      <c r="C43" s="28" t="s">
+      <c r="A43" s="53"/>
+      <c r="B43" s="56"/>
+      <c r="C43" t="s">
         <v>35</v>
       </c>
-      <c r="D43" s="28" t="s">
+      <c r="D43" t="s">
         <v>320</v>
       </c>
-      <c r="E43" s="33">
+      <c r="E43" s="30">
         <v>0.98</v>
       </c>
-      <c r="F43" s="28" t="s">
+      <c r="F43" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="58"/>
-      <c r="B44" s="62"/>
-      <c r="C44" s="28" t="s">
+      <c r="A44" s="53"/>
+      <c r="B44" s="56"/>
+      <c r="C44" t="s">
         <v>36</v>
       </c>
-      <c r="D44" s="28" t="s">
+      <c r="D44" t="s">
         <v>321</v>
       </c>
-      <c r="E44" s="33">
+      <c r="E44" s="30">
         <v>0.98</v>
       </c>
-      <c r="F44" s="28" t="s">
+      <c r="F44" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="58"/>
-      <c r="B45" s="62"/>
-      <c r="C45" s="28" t="s">
+      <c r="A45" s="53"/>
+      <c r="B45" s="56"/>
+      <c r="C45" t="s">
         <v>15</v>
       </c>
-      <c r="D45" s="28" t="s">
+      <c r="D45" t="s">
         <v>322</v>
       </c>
-      <c r="E45" s="33">
+      <c r="E45" s="30">
         <v>0.05</v>
       </c>
-      <c r="F45" s="28" t="s">
+      <c r="F45" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="58"/>
-      <c r="B46" s="62"/>
-      <c r="C46" s="37" t="s">
+      <c r="A46" s="53"/>
+      <c r="B46" s="56"/>
+      <c r="C46" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="D46" s="37" t="s">
+      <c r="D46" s="34" t="s">
         <v>323</v>
       </c>
-      <c r="E46" s="38">
+      <c r="E46" s="35">
         <v>0</v>
       </c>
-      <c r="F46" s="37" t="s">
+      <c r="F46" s="34" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="58"/>
-      <c r="B47" s="64" t="s">
+      <c r="A47" s="53"/>
+      <c r="B47" s="58" t="s">
         <v>201</v>
       </c>
-      <c r="C47" s="35" t="s">
+      <c r="C47" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="D47" s="35" t="s">
+      <c r="D47" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="E47" s="39">
+      <c r="E47" s="36">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="F47" s="35" t="s">
+      <c r="F47" s="32" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="58"/>
-      <c r="B48" s="66"/>
-      <c r="C48" s="28" t="s">
+      <c r="A48" s="53"/>
+      <c r="B48" s="60"/>
+      <c r="C48" t="s">
         <v>21</v>
       </c>
-      <c r="D48" s="28" t="s">
+      <c r="D48" t="s">
         <v>55</v>
       </c>
-      <c r="E48" s="31">
+      <c r="E48" s="28">
         <f>E49*4</f>
         <v>424</v>
       </c>
-      <c r="F48" s="28" t="s">
+      <c r="F48" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="58"/>
-      <c r="B49" s="66"/>
-      <c r="C49" s="28" t="s">
+      <c r="A49" s="53"/>
+      <c r="B49" s="60"/>
+      <c r="C49" t="s">
         <v>16</v>
       </c>
-      <c r="D49" s="28" t="s">
+      <c r="D49" t="s">
         <v>56</v>
       </c>
-      <c r="E49" s="31">
+      <c r="E49" s="28">
         <v>106</v>
       </c>
-      <c r="F49" s="28" t="s">
+      <c r="F49" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="58"/>
-      <c r="B50" s="66"/>
-      <c r="C50" s="28" t="s">
+      <c r="A50" s="53"/>
+      <c r="B50" s="60"/>
+      <c r="C50" t="s">
         <v>17</v>
       </c>
-      <c r="D50" s="28" t="s">
+      <c r="D50" t="s">
         <v>57</v>
       </c>
-      <c r="E50" s="33">
+      <c r="E50" s="30">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F50" s="28" t="s">
+      <c r="F50" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="58"/>
-      <c r="B51" s="66"/>
-      <c r="C51" s="28" t="s">
+      <c r="A51" s="53"/>
+      <c r="B51" s="60"/>
+      <c r="C51" t="s">
         <v>35</v>
       </c>
-      <c r="D51" s="28" t="s">
+      <c r="D51" t="s">
         <v>59</v>
       </c>
-      <c r="E51" s="33">
+      <c r="E51" s="30">
         <v>0.93500000000000005</v>
       </c>
-      <c r="F51" s="28" t="s">
+      <c r="F51" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="58"/>
-      <c r="B52" s="66"/>
-      <c r="C52" s="28" t="s">
+      <c r="A52" s="53"/>
+      <c r="B52" s="60"/>
+      <c r="C52" t="s">
         <v>36</v>
       </c>
-      <c r="D52" s="28" t="s">
+      <c r="D52" t="s">
         <v>60</v>
       </c>
-      <c r="E52" s="33">
+      <c r="E52" s="30">
         <v>0.93500000000000005</v>
       </c>
-      <c r="F52" s="28" t="s">
+      <c r="F52" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="58"/>
-      <c r="B53" s="66"/>
-      <c r="C53" s="28" t="s">
+      <c r="A53" s="53"/>
+      <c r="B53" s="60"/>
+      <c r="C53" t="s">
         <v>89</v>
       </c>
-      <c r="D53" s="28" t="s">
+      <c r="D53" t="s">
         <v>58</v>
       </c>
-      <c r="E53" s="31">
+      <c r="E53" s="28">
         <v>0.25</v>
       </c>
-      <c r="F53" s="28" t="s">
+      <c r="F53" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="58"/>
-      <c r="B54" s="66"/>
-      <c r="C54" s="28" t="s">
+      <c r="A54" s="53"/>
+      <c r="B54" s="60"/>
+      <c r="C54" t="s">
         <v>88</v>
       </c>
-      <c r="D54" s="28" t="s">
+      <c r="D54" t="s">
         <v>61</v>
       </c>
-      <c r="E54" s="33">
+      <c r="E54" s="30">
         <v>0</v>
       </c>
-      <c r="F54" s="28" t="s">
+      <c r="F54" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="58"/>
-      <c r="B55" s="66"/>
-      <c r="C55" s="28" t="s">
+      <c r="A55" s="53"/>
+      <c r="B55" s="60"/>
+      <c r="C55" t="s">
         <v>13</v>
       </c>
-      <c r="D55" s="28" t="s">
+      <c r="D55" t="s">
         <v>54</v>
       </c>
-      <c r="E55" s="34">
+      <c r="E55" s="31">
         <v>15</v>
       </c>
-      <c r="F55" s="28" t="s">
+      <c r="F55" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="59"/>
-      <c r="B56" s="67"/>
-      <c r="C56" s="42" t="s">
+      <c r="A56" s="54"/>
+      <c r="B56" s="61"/>
+      <c r="C56" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="D56" s="42" t="s">
+      <c r="D56" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="E56" s="43">
+      <c r="E56" s="40">
         <v>0.1</v>
       </c>
-      <c r="F56" s="42" t="s">
+      <c r="F56" s="39" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="57" t="s">
+      <c r="A57" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="B57" s="44" t="s">
+      <c r="B57" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="C57" s="45" t="s">
+      <c r="C57" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="D57" s="45" t="s">
+      <c r="D57" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="E57" s="46">
+      <c r="E57" s="43">
         <v>0.1699</v>
       </c>
-      <c r="F57" s="45" t="s">
+      <c r="F57" s="42" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="60"/>
-      <c r="B58" s="47" t="s">
+      <c r="A58" s="53"/>
+      <c r="B58" s="44" t="s">
         <v>341</v>
       </c>
-      <c r="C58" s="48" t="s">
+      <c r="C58" t="s">
         <v>342</v>
       </c>
-      <c r="D58" s="48" t="s">
+      <c r="D58" t="s">
         <v>343</v>
       </c>
-      <c r="E58" s="49">
+      <c r="E58" s="30">
         <v>0</v>
       </c>
-      <c r="F58" s="48" t="s">
+      <c r="F58" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="58"/>
-      <c r="B59" s="64" t="s">
+      <c r="A59" s="53"/>
+      <c r="B59" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="C59" s="35" t="s">
+      <c r="C59" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="D59" s="35" t="s">
+      <c r="D59" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="E59" s="39">
+      <c r="E59" s="36">
         <v>0.99</v>
       </c>
-      <c r="F59" s="35" t="s">
+      <c r="F59" s="32" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="58"/>
-      <c r="B60" s="62"/>
-      <c r="C60" s="28" t="s">
+      <c r="A60" s="53"/>
+      <c r="B60" s="56"/>
+      <c r="C60" t="s">
         <v>10</v>
       </c>
-      <c r="D60" s="28" t="s">
+      <c r="D60" t="s">
         <v>43</v>
       </c>
-      <c r="E60" s="50">
+      <c r="E60" s="45">
         <v>1100</v>
       </c>
-      <c r="F60" s="28" t="s">
+      <c r="F60" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="58"/>
-      <c r="B61" s="62"/>
-      <c r="C61" s="28" t="s">
+      <c r="A61" s="53"/>
+      <c r="B61" s="56"/>
+      <c r="C61" t="s">
         <v>17</v>
       </c>
-      <c r="D61" s="28" t="s">
+      <c r="D61" t="s">
         <v>44</v>
       </c>
-      <c r="E61" s="50">
+      <c r="E61" s="45">
         <v>17.84</v>
       </c>
-      <c r="F61" s="28" t="s">
+      <c r="F61" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="58"/>
-      <c r="B62" s="62"/>
-      <c r="C62" s="28" t="s">
+      <c r="A62" s="53"/>
+      <c r="B62" s="56"/>
+      <c r="C62" t="s">
         <v>18</v>
       </c>
-      <c r="D62" s="28" t="s">
+      <c r="D62" t="s">
         <v>45</v>
       </c>
-      <c r="E62" s="31">
+      <c r="E62" s="28">
         <v>0</v>
       </c>
-      <c r="F62" s="28" t="s">
+      <c r="F62" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="58"/>
-      <c r="B63" s="62"/>
-      <c r="C63" s="28" t="s">
+      <c r="A63" s="53"/>
+      <c r="B63" s="56"/>
+      <c r="C63" t="s">
         <v>13</v>
       </c>
-      <c r="D63" s="28" t="s">
+      <c r="D63" t="s">
         <v>42</v>
       </c>
-      <c r="E63" s="34">
+      <c r="E63" s="31">
         <v>25</v>
       </c>
-      <c r="F63" s="28" t="s">
+      <c r="F63" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="58"/>
-      <c r="B64" s="62"/>
-      <c r="C64" s="28" t="s">
+      <c r="A64" s="53"/>
+      <c r="B64" s="56"/>
+      <c r="C64" t="s">
         <v>68</v>
       </c>
-      <c r="D64" s="28" t="s">
+      <c r="D64" t="s">
         <v>67</v>
       </c>
-      <c r="E64" s="31">
+      <c r="E64" s="28">
         <v>1000000</v>
       </c>
-      <c r="F64" s="28" t="s">
+      <c r="F64" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="58"/>
-      <c r="B65" s="63"/>
-      <c r="C65" s="37" t="s">
+      <c r="A65" s="53"/>
+      <c r="B65" s="57"/>
+      <c r="C65" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="D65" s="37" t="s">
+      <c r="D65" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="E65" s="38">
+      <c r="E65" s="35">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="F65" s="37" t="s">
+      <c r="F65" s="34" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="58"/>
-      <c r="B66" s="64" t="s">
+      <c r="A66" s="53"/>
+      <c r="B66" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="C66" s="35" t="s">
+      <c r="C66" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="D66" s="35" t="s">
+      <c r="D66" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="E66" s="39">
+      <c r="E66" s="36">
         <v>0.997</v>
       </c>
-      <c r="F66" s="35" t="s">
+      <c r="F66" s="32" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="58"/>
-      <c r="B67" s="62"/>
-      <c r="C67" s="28" t="s">
+      <c r="A67" s="53"/>
+      <c r="B67" s="56"/>
+      <c r="C67" t="s">
         <v>10</v>
       </c>
-      <c r="D67" s="28" t="s">
+      <c r="D67" t="s">
         <v>48</v>
       </c>
-      <c r="E67" s="50">
+      <c r="E67" s="45">
         <v>1080</v>
       </c>
-      <c r="F67" s="28" t="s">
+      <c r="F67" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="58"/>
-      <c r="B68" s="62"/>
-      <c r="C68" s="28" t="s">
+      <c r="A68" s="53"/>
+      <c r="B68" s="56"/>
+      <c r="C68" t="s">
         <v>17</v>
       </c>
-      <c r="D68" s="28" t="s">
+      <c r="D68" t="s">
         <v>52</v>
       </c>
-      <c r="E68" s="50">
+      <c r="E68" s="45">
         <v>12.68</v>
       </c>
-      <c r="F68" s="28" t="s">
+      <c r="F68" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="58"/>
-      <c r="B69" s="62"/>
-      <c r="C69" s="28" t="s">
+      <c r="A69" s="53"/>
+      <c r="B69" s="56"/>
+      <c r="C69" t="s">
         <v>18</v>
       </c>
-      <c r="D69" s="28" t="s">
+      <c r="D69" t="s">
         <v>49</v>
       </c>
-      <c r="E69" s="51">
+      <c r="E69" s="46">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F69" s="28" t="s">
+      <c r="F69" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="58"/>
-      <c r="B70" s="62"/>
-      <c r="C70" s="28" t="s">
+      <c r="A70" s="53"/>
+      <c r="B70" s="56"/>
+      <c r="C70" t="s">
         <v>13</v>
       </c>
-      <c r="D70" s="28" t="s">
+      <c r="D70" t="s">
         <v>50</v>
       </c>
-      <c r="E70" s="34">
+      <c r="E70" s="31">
         <v>25</v>
       </c>
-      <c r="F70" s="28" t="s">
+      <c r="F70" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="58"/>
-      <c r="B71" s="62"/>
-      <c r="C71" s="28" t="s">
+      <c r="A71" s="53"/>
+      <c r="B71" s="56"/>
+      <c r="C71" t="s">
         <v>68</v>
       </c>
-      <c r="D71" s="28" t="s">
+      <c r="D71" t="s">
         <v>65</v>
       </c>
-      <c r="E71" s="52">
+      <c r="E71" s="47">
         <v>1000000</v>
       </c>
-      <c r="F71" s="28" t="s">
+      <c r="F71" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="59"/>
-      <c r="B72" s="65"/>
-      <c r="C72" s="42" t="s">
+      <c r="A72" s="54"/>
+      <c r="B72" s="59"/>
+      <c r="C72" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="D72" s="42" t="s">
+      <c r="D72" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="E72" s="43">
+      <c r="E72" s="40">
         <v>5.8000000000000003E-2</v>
       </c>
-      <c r="F72" s="42" t="s">
+      <c r="F72" s="39" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="57" t="s">
+      <c r="A73" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="B73" s="53" t="s">
+      <c r="B73" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="C73" s="45" t="s">
+      <c r="C73" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="D73" s="45" t="s">
+      <c r="D73" s="42" t="s">
         <v>78</v>
       </c>
-      <c r="E73" s="46">
+      <c r="E73" s="43">
         <v>-1E-4</v>
       </c>
-      <c r="F73" s="45" t="s">
+      <c r="F73" s="42" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="58"/>
-      <c r="B74" s="27" t="s">
+      <c r="A74" s="53"/>
+      <c r="B74" s="25" t="s">
         <v>297</v>
       </c>
-      <c r="C74" s="28" t="s">
+      <c r="C74" t="s">
         <v>298</v>
       </c>
-      <c r="D74" s="28" t="s">
+      <c r="D74" t="s">
         <v>299</v>
       </c>
-      <c r="E74" s="33">
+      <c r="E74" s="30">
         <v>-1E-4</v>
       </c>
-      <c r="F74" s="28" t="s">
+      <c r="F74" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="58"/>
-      <c r="B75" s="54" t="s">
+      <c r="A75" s="53"/>
+      <c r="B75" s="49" t="s">
         <v>79</v>
       </c>
-      <c r="C75" s="55" t="s">
+      <c r="C75" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="D75" s="55" t="s">
+      <c r="D75" s="50" t="s">
         <v>81</v>
       </c>
-      <c r="E75" s="56">
+      <c r="E75" s="51">
         <v>-1.5</v>
       </c>
-      <c r="F75" s="55" t="s">
+      <c r="F75" s="50" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="59"/>
-      <c r="B76" s="25" t="s">
+      <c r="A76" s="54"/>
+      <c r="B76" s="23" t="s">
         <v>260</v>
       </c>
-      <c r="C76" s="42" t="s">
+      <c r="C76" s="39" t="s">
         <v>272</v>
       </c>
-      <c r="D76" s="42" t="s">
+      <c r="D76" s="39" t="s">
         <v>270</v>
       </c>
-      <c r="E76" s="43">
+      <c r="E76" s="40">
         <v>-0.6</v>
       </c>
-      <c r="F76" s="42" t="s">
+      <c r="F76" s="39" t="s">
         <v>273</v>
       </c>
     </row>
@@ -3297,10 +3282,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="68" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="71" t="s">
+      <c r="B2" s="70" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="6" t="s">
@@ -3315,8 +3300,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="75"/>
-      <c r="B3" s="72"/>
+      <c r="A3" s="69"/>
+      <c r="B3" s="66"/>
       <c r="C3" s="5" t="s">
         <v>107</v>
       </c>
@@ -3329,8 +3314,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="75"/>
-      <c r="B4" s="72"/>
+      <c r="A4" s="69"/>
+      <c r="B4" s="66"/>
       <c r="C4" s="5" t="s">
         <v>84</v>
       </c>
@@ -3343,8 +3328,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="75"/>
-      <c r="B5" s="72"/>
+      <c r="A5" s="69"/>
+      <c r="B5" s="66"/>
       <c r="C5" s="5" t="s">
         <v>138</v>
       </c>
@@ -3357,8 +3342,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="75"/>
-      <c r="B6" s="72"/>
+      <c r="A6" s="69"/>
+      <c r="B6" s="66"/>
       <c r="C6" s="5" t="s">
         <v>141</v>
       </c>
@@ -3371,8 +3356,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="75"/>
-      <c r="B7" s="72"/>
+      <c r="A7" s="69"/>
+      <c r="B7" s="66"/>
       <c r="C7" s="5" t="s">
         <v>155</v>
       </c>
@@ -3385,8 +3370,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="75"/>
-      <c r="B8" s="72"/>
+      <c r="A8" s="69"/>
+      <c r="B8" s="66"/>
       <c r="C8" s="5" t="s">
         <v>196</v>
       </c>
@@ -3399,8 +3384,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="75"/>
-      <c r="B9" s="72"/>
+      <c r="A9" s="69"/>
+      <c r="B9" s="66"/>
       <c r="C9" s="5" t="s">
         <v>167</v>
       </c>
@@ -3413,8 +3398,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="75"/>
-      <c r="B10" s="72"/>
+      <c r="A10" s="69"/>
+      <c r="B10" s="66"/>
       <c r="C10" s="5" t="s">
         <v>188</v>
       </c>
@@ -3427,13 +3412,13 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="75"/>
-      <c r="B11" s="72"/>
+      <c r="A11" s="69"/>
+      <c r="B11" s="66"/>
       <c r="E11" s="10"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="75"/>
-      <c r="B12" s="81" t="s">
+      <c r="A12" s="69"/>
+      <c r="B12" s="65" t="s">
         <v>229</v>
       </c>
       <c r="C12" s="12" t="s">
@@ -3448,8 +3433,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="75"/>
-      <c r="B13" s="72"/>
+      <c r="A13" s="69"/>
+      <c r="B13" s="66"/>
       <c r="C13" s="5" t="s">
         <v>253</v>
       </c>
@@ -3462,8 +3447,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="75"/>
-      <c r="B14" s="72"/>
+      <c r="A14" s="69"/>
+      <c r="B14" s="66"/>
       <c r="C14" s="5" t="s">
         <v>139</v>
       </c>
@@ -3476,8 +3461,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="75"/>
-      <c r="B15" s="72"/>
+      <c r="A15" s="69"/>
+      <c r="B15" s="66"/>
       <c r="C15" s="5" t="s">
         <v>254</v>
       </c>
@@ -3490,8 +3475,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="75"/>
-      <c r="B16" s="72"/>
+      <c r="A16" s="69"/>
+      <c r="B16" s="66"/>
       <c r="C16" s="5" t="s">
         <v>84</v>
       </c>
@@ -3504,8 +3489,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="75"/>
-      <c r="B17" s="72"/>
+      <c r="A17" s="69"/>
+      <c r="B17" s="66"/>
       <c r="C17" s="5" t="s">
         <v>141</v>
       </c>
@@ -3518,8 +3503,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="75"/>
-      <c r="B18" s="72"/>
+      <c r="A18" s="69"/>
+      <c r="B18" s="66"/>
       <c r="C18" s="5" t="s">
         <v>155</v>
       </c>
@@ -3532,8 +3517,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="75"/>
-      <c r="B19" s="72"/>
+      <c r="A19" s="69"/>
+      <c r="B19" s="66"/>
       <c r="C19" s="5" t="s">
         <v>196</v>
       </c>
@@ -3546,8 +3531,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="75"/>
-      <c r="B20" s="72"/>
+      <c r="A20" s="69"/>
+      <c r="B20" s="66"/>
       <c r="C20" s="5" t="s">
         <v>167</v>
       </c>
@@ -3560,8 +3545,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="75"/>
-      <c r="B21" s="72"/>
+      <c r="A21" s="69"/>
+      <c r="B21" s="66"/>
       <c r="C21" s="5" t="s">
         <v>188</v>
       </c>
@@ -3574,16 +3559,16 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="75"/>
-      <c r="B22" s="73"/>
+      <c r="A22" s="69"/>
+      <c r="B22" s="67"/>
       <c r="C22" s="14"/>
       <c r="D22" s="14"/>
       <c r="E22" s="15"/>
       <c r="F22" s="14"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="75"/>
-      <c r="B23" s="81" t="s">
+      <c r="A23" s="69"/>
+      <c r="B23" s="65" t="s">
         <v>271</v>
       </c>
       <c r="C23" s="5" t="s">
@@ -3598,8 +3583,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="75"/>
-      <c r="B24" s="72"/>
+      <c r="A24" s="69"/>
+      <c r="B24" s="66"/>
       <c r="C24" s="5" t="s">
         <v>107</v>
       </c>
@@ -3612,8 +3597,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="75"/>
-      <c r="B25" s="72"/>
+      <c r="A25" s="69"/>
+      <c r="B25" s="66"/>
       <c r="C25" s="5" t="s">
         <v>84</v>
       </c>
@@ -3626,8 +3611,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="75"/>
-      <c r="B26" s="72"/>
+      <c r="A26" s="69"/>
+      <c r="B26" s="66"/>
       <c r="C26" s="5" t="s">
         <v>293</v>
       </c>
@@ -3640,8 +3625,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="75"/>
-      <c r="B27" s="72"/>
+      <c r="A27" s="69"/>
+      <c r="B27" s="66"/>
       <c r="C27" s="5" t="s">
         <v>141</v>
       </c>
@@ -3654,8 +3639,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="75"/>
-      <c r="B28" s="72"/>
+      <c r="A28" s="69"/>
+      <c r="B28" s="66"/>
       <c r="C28" s="5" t="s">
         <v>155</v>
       </c>
@@ -3668,8 +3653,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="75"/>
-      <c r="B29" s="72"/>
+      <c r="A29" s="69"/>
+      <c r="B29" s="66"/>
       <c r="C29" s="5" t="s">
         <v>196</v>
       </c>
@@ -3682,8 +3667,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="75"/>
-      <c r="B30" s="72"/>
+      <c r="A30" s="69"/>
+      <c r="B30" s="66"/>
       <c r="C30" s="5" t="s">
         <v>167</v>
       </c>
@@ -3696,8 +3681,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="75"/>
-      <c r="B31" s="72"/>
+      <c r="A31" s="69"/>
+      <c r="B31" s="66"/>
       <c r="C31" s="5" t="s">
         <v>188</v>
       </c>
@@ -3710,16 +3695,16 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="75"/>
-      <c r="B32" s="73"/>
+      <c r="A32" s="69"/>
+      <c r="B32" s="67"/>
       <c r="C32" s="14"/>
       <c r="D32" s="14"/>
       <c r="E32" s="15"/>
       <c r="F32" s="14"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="75"/>
-      <c r="B33" s="78" t="s">
+      <c r="A33" s="69"/>
+      <c r="B33" s="71" t="s">
         <v>358</v>
       </c>
       <c r="C33" s="5" t="s">
@@ -3734,8 +3719,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="75"/>
-      <c r="B34" s="78"/>
+      <c r="A34" s="69"/>
+      <c r="B34" s="71"/>
       <c r="C34" s="5" t="s">
         <v>107</v>
       </c>
@@ -3748,8 +3733,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="75"/>
-      <c r="B35" s="78"/>
+      <c r="A35" s="69"/>
+      <c r="B35" s="71"/>
       <c r="C35" s="5" t="s">
         <v>84</v>
       </c>
@@ -3762,8 +3747,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="75"/>
-      <c r="B36" s="78"/>
+      <c r="A36" s="69"/>
+      <c r="B36" s="71"/>
       <c r="C36" s="5" t="s">
         <v>281</v>
       </c>
@@ -3776,8 +3761,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="75"/>
-      <c r="B37" s="78"/>
+      <c r="A37" s="69"/>
+      <c r="B37" s="71"/>
       <c r="C37" s="5" t="s">
         <v>370</v>
       </c>
@@ -3790,8 +3775,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="75"/>
-      <c r="B38" s="78"/>
+      <c r="A38" s="69"/>
+      <c r="B38" s="71"/>
       <c r="C38" s="5" t="s">
         <v>258</v>
       </c>
@@ -3804,8 +3789,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="75"/>
-      <c r="B39" s="78"/>
+      <c r="A39" s="69"/>
+      <c r="B39" s="71"/>
       <c r="C39" s="5" t="s">
         <v>141</v>
       </c>
@@ -3818,8 +3803,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="75"/>
-      <c r="B40" s="78"/>
+      <c r="A40" s="69"/>
+      <c r="B40" s="71"/>
       <c r="C40" s="5" t="s">
         <v>155</v>
       </c>
@@ -3832,8 +3817,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="75"/>
-      <c r="B41" s="78"/>
+      <c r="A41" s="69"/>
+      <c r="B41" s="71"/>
       <c r="C41" s="5" t="s">
         <v>161</v>
       </c>
@@ -3846,8 +3831,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="75"/>
-      <c r="B42" s="78"/>
+      <c r="A42" s="69"/>
+      <c r="B42" s="71"/>
       <c r="C42" s="5" t="s">
         <v>196</v>
       </c>
@@ -3860,8 +3845,8 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="75"/>
-      <c r="B43" s="78"/>
+      <c r="A43" s="69"/>
+      <c r="B43" s="71"/>
       <c r="C43" s="5" t="s">
         <v>167</v>
       </c>
@@ -3874,8 +3859,8 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="75"/>
-      <c r="B44" s="78"/>
+      <c r="A44" s="69"/>
+      <c r="B44" s="71"/>
       <c r="C44" s="5" t="s">
         <v>188</v>
       </c>
@@ -3888,15 +3873,15 @@
       </c>
     </row>
     <row r="45" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="75"/>
-      <c r="B45" s="78"/>
+      <c r="A45" s="69"/>
+      <c r="B45" s="71"/>
       <c r="E45" s="10"/>
     </row>
     <row r="46" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="74" t="s">
+      <c r="A46" s="68" t="s">
         <v>71</v>
       </c>
-      <c r="B46" s="85" t="s">
+      <c r="B46" s="75" t="s">
         <v>3</v>
       </c>
       <c r="C46" s="6" t="s">
@@ -3911,8 +3896,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="75"/>
-      <c r="B47" s="78"/>
+      <c r="A47" s="69"/>
+      <c r="B47" s="71"/>
       <c r="C47" s="5" t="s">
         <v>111</v>
       </c>
@@ -3925,8 +3910,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="75"/>
-      <c r="B48" s="78"/>
+      <c r="A48" s="69"/>
+      <c r="B48" s="71"/>
       <c r="C48" s="5" t="s">
         <v>135</v>
       </c>
@@ -3939,8 +3924,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="75"/>
-      <c r="B49" s="78"/>
+      <c r="A49" s="69"/>
+      <c r="B49" s="71"/>
       <c r="C49" s="5" t="s">
         <v>136</v>
       </c>
@@ -3953,8 +3938,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="75"/>
-      <c r="B50" s="78"/>
+      <c r="A50" s="69"/>
+      <c r="B50" s="71"/>
       <c r="C50" s="5" t="s">
         <v>141</v>
       </c>
@@ -3967,8 +3952,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="75"/>
-      <c r="B51" s="78"/>
+      <c r="A51" s="69"/>
+      <c r="B51" s="71"/>
       <c r="C51" s="5" t="s">
         <v>155</v>
       </c>
@@ -3981,8 +3966,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="75"/>
-      <c r="B52" s="78"/>
+      <c r="A52" s="69"/>
+      <c r="B52" s="71"/>
       <c r="C52" s="5" t="s">
         <v>196</v>
       </c>
@@ -3995,8 +3980,8 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="75"/>
-      <c r="B53" s="78"/>
+      <c r="A53" s="69"/>
+      <c r="B53" s="71"/>
       <c r="C53" s="5" t="s">
         <v>167</v>
       </c>
@@ -4009,8 +3994,8 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="75"/>
-      <c r="B54" s="78"/>
+      <c r="A54" s="69"/>
+      <c r="B54" s="71"/>
       <c r="C54" s="5" t="s">
         <v>188</v>
       </c>
@@ -4023,16 +4008,16 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="75"/>
-      <c r="B55" s="79"/>
+      <c r="A55" s="69"/>
+      <c r="B55" s="76"/>
       <c r="C55" s="14"/>
       <c r="D55" s="14"/>
       <c r="E55" s="15"/>
       <c r="F55" s="14"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="75"/>
-      <c r="B56" s="78" t="s">
+      <c r="A56" s="69"/>
+      <c r="B56" s="71" t="s">
         <v>315</v>
       </c>
       <c r="C56" s="5" t="s">
@@ -4047,8 +4032,8 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="75"/>
-      <c r="B57" s="78"/>
+      <c r="A57" s="69"/>
+      <c r="B57" s="71"/>
       <c r="C57" s="5" t="s">
         <v>111</v>
       </c>
@@ -4061,8 +4046,8 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="75"/>
-      <c r="B58" s="78"/>
+      <c r="A58" s="69"/>
+      <c r="B58" s="71"/>
       <c r="C58" s="5" t="s">
         <v>135</v>
       </c>
@@ -4075,8 +4060,8 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="75"/>
-      <c r="B59" s="78"/>
+      <c r="A59" s="69"/>
+      <c r="B59" s="71"/>
       <c r="C59" s="5" t="s">
         <v>136</v>
       </c>
@@ -4089,8 +4074,8 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="75"/>
-      <c r="B60" s="78"/>
+      <c r="A60" s="69"/>
+      <c r="B60" s="71"/>
       <c r="C60" s="5" t="s">
         <v>141</v>
       </c>
@@ -4103,8 +4088,8 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="75"/>
-      <c r="B61" s="78"/>
+      <c r="A61" s="69"/>
+      <c r="B61" s="71"/>
       <c r="C61" s="5" t="s">
         <v>155</v>
       </c>
@@ -4117,8 +4102,8 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="75"/>
-      <c r="B62" s="78"/>
+      <c r="A62" s="69"/>
+      <c r="B62" s="71"/>
       <c r="C62" s="5" t="s">
         <v>196</v>
       </c>
@@ -4131,8 +4116,8 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="75"/>
-      <c r="B63" s="78"/>
+      <c r="A63" s="69"/>
+      <c r="B63" s="71"/>
       <c r="C63" s="5" t="s">
         <v>167</v>
       </c>
@@ -4145,8 +4130,8 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="75"/>
-      <c r="B64" s="78"/>
+      <c r="A64" s="69"/>
+      <c r="B64" s="71"/>
       <c r="C64" s="5" t="s">
         <v>188</v>
       </c>
@@ -4159,13 +4144,13 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="75"/>
-      <c r="B65" s="79"/>
+      <c r="A65" s="69"/>
+      <c r="B65" s="76"/>
       <c r="E65" s="10"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="75"/>
-      <c r="B66" s="77" t="s">
+      <c r="A66" s="69"/>
+      <c r="B66" s="73" t="s">
         <v>6</v>
       </c>
       <c r="C66" s="12" t="s">
@@ -4180,8 +4165,8 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="75"/>
-      <c r="B67" s="78"/>
+      <c r="A67" s="69"/>
+      <c r="B67" s="71"/>
       <c r="C67" s="5" t="s">
         <v>113</v>
       </c>
@@ -4194,8 +4179,8 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="75"/>
-      <c r="B68" s="72"/>
+      <c r="A68" s="69"/>
+      <c r="B68" s="66"/>
       <c r="C68" s="5" t="s">
         <v>111</v>
       </c>
@@ -4208,8 +4193,8 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="75"/>
-      <c r="B69" s="72"/>
+      <c r="A69" s="69"/>
+      <c r="B69" s="66"/>
       <c r="C69" s="5" t="s">
         <v>107</v>
       </c>
@@ -4222,8 +4207,8 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="75"/>
-      <c r="B70" s="72"/>
+      <c r="A70" s="69"/>
+      <c r="B70" s="66"/>
       <c r="C70" s="5" t="s">
         <v>126</v>
       </c>
@@ -4236,8 +4221,8 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="75"/>
-      <c r="B71" s="72"/>
+      <c r="A71" s="69"/>
+      <c r="B71" s="66"/>
       <c r="C71" s="5" t="s">
         <v>127</v>
       </c>
@@ -4250,8 +4235,8 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="75"/>
-      <c r="B72" s="72"/>
+      <c r="A72" s="69"/>
+      <c r="B72" s="66"/>
       <c r="C72" s="5" t="s">
         <v>141</v>
       </c>
@@ -4264,8 +4249,8 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="75"/>
-      <c r="B73" s="72"/>
+      <c r="A73" s="69"/>
+      <c r="B73" s="66"/>
       <c r="C73" s="5" t="s">
         <v>155</v>
       </c>
@@ -4278,8 +4263,8 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="75"/>
-      <c r="B74" s="72"/>
+      <c r="A74" s="69"/>
+      <c r="B74" s="66"/>
       <c r="C74" s="5" t="s">
         <v>196</v>
       </c>
@@ -4292,8 +4277,8 @@
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="75"/>
-      <c r="B75" s="72"/>
+      <c r="A75" s="69"/>
+      <c r="B75" s="66"/>
       <c r="C75" s="5" t="s">
         <v>167</v>
       </c>
@@ -4306,8 +4291,8 @@
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="75"/>
-      <c r="B76" s="72"/>
+      <c r="A76" s="69"/>
+      <c r="B76" s="66"/>
       <c r="C76" s="5" t="s">
         <v>188</v>
       </c>
@@ -4320,18 +4305,18 @@
       </c>
     </row>
     <row r="77" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="76"/>
-      <c r="B77" s="84"/>
+      <c r="A77" s="72"/>
+      <c r="B77" s="74"/>
       <c r="C77" s="18"/>
       <c r="D77" s="18"/>
       <c r="E77" s="19"/>
       <c r="F77" s="18"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="74" t="s">
+      <c r="A78" s="68" t="s">
         <v>72</v>
       </c>
-      <c r="B78" s="71" t="s">
+      <c r="B78" s="70" t="s">
         <v>73</v>
       </c>
       <c r="C78" s="6" t="s">
@@ -4346,46 +4331,46 @@
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="75"/>
-      <c r="B79" s="82"/>
-      <c r="C79" s="20" t="s">
+      <c r="A79" s="69"/>
+      <c r="B79" s="66"/>
+      <c r="C79" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="D79" s="20" t="s">
+      <c r="D79" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="E79" s="21"/>
-      <c r="F79" s="20" t="s">
+      <c r="E79" s="8"/>
+      <c r="F79" s="5" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="75"/>
-      <c r="B80" s="73"/>
+      <c r="A80" s="69"/>
+      <c r="B80" s="67"/>
       <c r="C80" s="14"/>
       <c r="D80" s="14"/>
-      <c r="E80" s="22"/>
+      <c r="E80" s="20"/>
       <c r="F80" s="14"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="75"/>
-      <c r="B81" s="82" t="s">
+      <c r="A81" s="69"/>
+      <c r="B81" s="66" t="s">
         <v>341</v>
       </c>
-      <c r="C81" s="20" t="s">
+      <c r="C81" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="D81" s="20" t="s">
+      <c r="D81" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="E81" s="21"/>
-      <c r="F81" s="20" t="s">
+      <c r="E81" s="8"/>
+      <c r="F81" s="5" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="75"/>
-      <c r="B82" s="82"/>
+      <c r="A82" s="69"/>
+      <c r="B82" s="66"/>
       <c r="C82" s="5" t="s">
         <v>345</v>
       </c>
@@ -4398,13 +4383,13 @@
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="75"/>
-      <c r="B83" s="82"/>
+      <c r="A83" s="69"/>
+      <c r="B83" s="66"/>
       <c r="E83" s="8"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="75"/>
-      <c r="B84" s="77" t="s">
+      <c r="A84" s="69"/>
+      <c r="B84" s="73" t="s">
         <v>4</v>
       </c>
       <c r="C84" s="12" t="s">
@@ -4419,8 +4404,8 @@
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="75"/>
-      <c r="B85" s="78"/>
+      <c r="A85" s="69"/>
+      <c r="B85" s="71"/>
       <c r="C85" s="5" t="s">
         <v>107</v>
       </c>
@@ -4433,8 +4418,8 @@
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="75"/>
-      <c r="B86" s="78"/>
+      <c r="A86" s="69"/>
+      <c r="B86" s="71"/>
       <c r="C86" s="5" t="s">
         <v>122</v>
       </c>
@@ -4447,8 +4432,8 @@
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="75"/>
-      <c r="B87" s="78"/>
+      <c r="A87" s="69"/>
+      <c r="B87" s="71"/>
       <c r="C87" s="5" t="s">
         <v>141</v>
       </c>
@@ -4461,8 +4446,8 @@
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="75"/>
-      <c r="B88" s="78"/>
+      <c r="A88" s="69"/>
+      <c r="B88" s="71"/>
       <c r="C88" s="5" t="s">
         <v>155</v>
       </c>
@@ -4475,8 +4460,8 @@
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="75"/>
-      <c r="B89" s="78"/>
+      <c r="A89" s="69"/>
+      <c r="B89" s="71"/>
       <c r="C89" s="5" t="s">
         <v>161</v>
       </c>
@@ -4489,8 +4474,8 @@
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="75"/>
-      <c r="B90" s="78"/>
+      <c r="A90" s="69"/>
+      <c r="B90" s="71"/>
       <c r="C90" s="5" t="s">
         <v>196</v>
       </c>
@@ -4503,8 +4488,8 @@
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="75"/>
-      <c r="B91" s="78"/>
+      <c r="A91" s="69"/>
+      <c r="B91" s="71"/>
       <c r="C91" s="5" t="s">
         <v>167</v>
       </c>
@@ -4517,8 +4502,8 @@
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="75"/>
-      <c r="B92" s="78"/>
+      <c r="A92" s="69"/>
+      <c r="B92" s="71"/>
       <c r="C92" s="5" t="s">
         <v>188</v>
       </c>
@@ -4531,12 +4516,12 @@
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="75"/>
-      <c r="B93" s="79"/>
+      <c r="A93" s="69"/>
+      <c r="B93" s="76"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="75"/>
-      <c r="B94" s="77" t="s">
+      <c r="A94" s="69"/>
+      <c r="B94" s="73" t="s">
         <v>5</v>
       </c>
       <c r="C94" s="12" t="s">
@@ -4551,8 +4536,8 @@
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="75"/>
-      <c r="B95" s="78"/>
+      <c r="A95" s="69"/>
+      <c r="B95" s="71"/>
       <c r="C95" s="5" t="s">
         <v>108</v>
       </c>
@@ -4565,8 +4550,8 @@
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="75"/>
-      <c r="B96" s="78"/>
+      <c r="A96" s="69"/>
+      <c r="B96" s="71"/>
       <c r="C96" s="5" t="s">
         <v>120</v>
       </c>
@@ -4579,8 +4564,8 @@
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="75"/>
-      <c r="B97" s="78"/>
+      <c r="A97" s="69"/>
+      <c r="B97" s="71"/>
       <c r="C97" s="5" t="s">
         <v>141</v>
       </c>
@@ -4593,8 +4578,8 @@
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="75"/>
-      <c r="B98" s="78"/>
+      <c r="A98" s="69"/>
+      <c r="B98" s="71"/>
       <c r="C98" s="5" t="s">
         <v>155</v>
       </c>
@@ -4607,36 +4592,36 @@
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="75"/>
-      <c r="B99" s="78"/>
+      <c r="A99" s="69"/>
+      <c r="B99" s="71"/>
       <c r="C99" s="5" t="s">
         <v>161</v>
       </c>
       <c r="D99" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="E99" s="23"/>
+      <c r="E99" s="21"/>
       <c r="F99" s="5" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="75"/>
-      <c r="B100" s="78"/>
+      <c r="A100" s="69"/>
+      <c r="B100" s="71"/>
       <c r="C100" s="5" t="s">
         <v>196</v>
       </c>
       <c r="D100" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="E100" s="23"/>
+      <c r="E100" s="21"/>
       <c r="F100" s="5" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="75"/>
-      <c r="B101" s="78"/>
+      <c r="A101" s="69"/>
+      <c r="B101" s="71"/>
       <c r="C101" s="5" t="s">
         <v>167</v>
       </c>
@@ -4649,8 +4634,8 @@
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="75"/>
-      <c r="B102" s="78"/>
+      <c r="A102" s="69"/>
+      <c r="B102" s="71"/>
       <c r="C102" s="5" t="s">
         <v>188</v>
       </c>
@@ -4663,14 +4648,14 @@
       </c>
     </row>
     <row r="103" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="76"/>
-      <c r="B103" s="80"/>
+      <c r="A103" s="72"/>
+      <c r="B103" s="77"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="74" t="s">
+      <c r="A104" s="68" t="s">
         <v>76</v>
       </c>
-      <c r="B104" s="71" t="s">
+      <c r="B104" s="70" t="s">
         <v>73</v>
       </c>
       <c r="C104" s="6" t="s">
@@ -4685,8 +4670,8 @@
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="75"/>
-      <c r="B105" s="72"/>
+      <c r="A105" s="69"/>
+      <c r="B105" s="66"/>
       <c r="C105" s="5" t="s">
         <v>228</v>
       </c>
@@ -4699,8 +4684,8 @@
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="75"/>
-      <c r="B106" s="72"/>
+      <c r="A106" s="69"/>
+      <c r="B106" s="66"/>
       <c r="C106" s="5" t="s">
         <v>150</v>
       </c>
@@ -4713,16 +4698,16 @@
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="75"/>
-      <c r="B107" s="73"/>
+      <c r="A107" s="69"/>
+      <c r="B107" s="67"/>
       <c r="C107" s="14"/>
       <c r="D107" s="14"/>
       <c r="E107" s="15"/>
       <c r="F107" s="14"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="75"/>
-      <c r="B108" s="81" t="s">
+      <c r="A108" s="69"/>
+      <c r="B108" s="65" t="s">
         <v>301</v>
       </c>
       <c r="C108" s="5" t="s">
@@ -4737,8 +4722,8 @@
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="75"/>
-      <c r="B109" s="72"/>
+      <c r="A109" s="69"/>
+      <c r="B109" s="66"/>
       <c r="C109" s="5" t="s">
         <v>306</v>
       </c>
@@ -4751,8 +4736,8 @@
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="75"/>
-      <c r="B110" s="72"/>
+      <c r="A110" s="69"/>
+      <c r="B110" s="66"/>
       <c r="C110" s="5" t="s">
         <v>307</v>
       </c>
@@ -4765,13 +4750,13 @@
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="75"/>
-      <c r="B111" s="73"/>
+      <c r="A111" s="69"/>
+      <c r="B111" s="67"/>
       <c r="E111" s="10"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="75"/>
-      <c r="B112" s="81" t="s">
+      <c r="A112" s="69"/>
+      <c r="B112" s="65" t="s">
         <v>79</v>
       </c>
       <c r="C112" s="12" t="s">
@@ -4786,8 +4771,8 @@
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="75"/>
-      <c r="B113" s="72"/>
+      <c r="A113" s="69"/>
+      <c r="B113" s="66"/>
       <c r="C113" s="5" t="s">
         <v>151</v>
       </c>
@@ -4800,16 +4785,16 @@
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="75"/>
-      <c r="B114" s="73"/>
+      <c r="A114" s="69"/>
+      <c r="B114" s="67"/>
       <c r="C114" s="14"/>
       <c r="D114" s="14"/>
       <c r="E114" s="15"/>
       <c r="F114" s="14"/>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="75"/>
-      <c r="B115" s="81" t="s">
+      <c r="A115" s="69"/>
+      <c r="B115" s="65" t="s">
         <v>260</v>
       </c>
       <c r="C115" s="5" t="s">
@@ -4824,8 +4809,8 @@
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="75"/>
-      <c r="B116" s="72"/>
+      <c r="A116" s="69"/>
+      <c r="B116" s="66"/>
       <c r="C116" s="5" t="s">
         <v>261</v>
       </c>
@@ -4838,18 +4823,18 @@
       </c>
     </row>
     <row r="117" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="76"/>
-      <c r="B117" s="84"/>
+      <c r="A117" s="72"/>
+      <c r="B117" s="74"/>
       <c r="C117" s="18"/>
       <c r="D117" s="18"/>
       <c r="E117" s="19"/>
       <c r="F117" s="18"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="74" t="s">
+      <c r="A118" s="68" t="s">
         <v>163</v>
       </c>
-      <c r="B118" s="71" t="s">
+      <c r="B118" s="70" t="s">
         <v>13</v>
       </c>
       <c r="C118" s="6" t="s">
@@ -4864,8 +4849,8 @@
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="83"/>
-      <c r="B119" s="72"/>
+      <c r="A119" s="69"/>
+      <c r="B119" s="66"/>
       <c r="C119" s="5" t="s">
         <v>174</v>
       </c>
@@ -4877,16 +4862,16 @@
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="83"/>
-      <c r="B120" s="73"/>
+      <c r="A120" s="69"/>
+      <c r="B120" s="67"/>
       <c r="C120" s="14"/>
       <c r="D120" s="14"/>
       <c r="E120" s="14"/>
       <c r="F120" s="14"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="83"/>
-      <c r="B121" s="81" t="s">
+      <c r="A121" s="69"/>
+      <c r="B121" s="65" t="s">
         <v>183</v>
       </c>
       <c r="C121" s="5" t="s">
@@ -4900,8 +4885,8 @@
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="83"/>
-      <c r="B122" s="72"/>
+      <c r="A122" s="69"/>
+      <c r="B122" s="66"/>
       <c r="C122" s="5" t="s">
         <v>181</v>
       </c>
@@ -4913,8 +4898,8 @@
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="83"/>
-      <c r="B123" s="72"/>
+      <c r="A123" s="69"/>
+      <c r="B123" s="66"/>
       <c r="C123" s="5" t="s">
         <v>177</v>
       </c>
@@ -4926,8 +4911,8 @@
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="83"/>
-      <c r="B124" s="72"/>
+      <c r="A124" s="69"/>
+      <c r="B124" s="66"/>
       <c r="C124" s="5" t="s">
         <v>179</v>
       </c>
@@ -4939,8 +4924,8 @@
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="83"/>
-      <c r="B125" s="72"/>
+      <c r="A125" s="69"/>
+      <c r="B125" s="66"/>
       <c r="C125" s="5" t="s">
         <v>182</v>
       </c>
@@ -4952,8 +4937,8 @@
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="83"/>
-      <c r="B126" s="72"/>
+      <c r="A126" s="69"/>
+      <c r="B126" s="66"/>
       <c r="C126" s="5" t="s">
         <v>191</v>
       </c>
@@ -4965,12 +4950,12 @@
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="83"/>
-      <c r="B127" s="72"/>
+      <c r="A127" s="69"/>
+      <c r="B127" s="66"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="83"/>
-      <c r="B128" s="81" t="s">
+      <c r="A128" s="69"/>
+      <c r="B128" s="65" t="s">
         <v>206</v>
       </c>
       <c r="C128" s="12" t="s">
@@ -4985,8 +4970,8 @@
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="83"/>
-      <c r="B129" s="72"/>
+      <c r="A129" s="69"/>
+      <c r="B129" s="66"/>
       <c r="C129" s="5" t="s">
         <v>204</v>
       </c>
@@ -4998,8 +4983,8 @@
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="83"/>
-      <c r="B130" s="72"/>
+      <c r="A130" s="69"/>
+      <c r="B130" s="66"/>
       <c r="C130" s="5" t="s">
         <v>215</v>
       </c>
@@ -5011,8 +4996,8 @@
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="83"/>
-      <c r="B131" s="72"/>
+      <c r="A131" s="69"/>
+      <c r="B131" s="66"/>
       <c r="C131" s="5" t="s">
         <v>205</v>
       </c>
@@ -5024,8 +5009,8 @@
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="83"/>
-      <c r="B132" s="72"/>
+      <c r="A132" s="69"/>
+      <c r="B132" s="66"/>
       <c r="C132" s="5" t="s">
         <v>310</v>
       </c>
@@ -5037,8 +5022,8 @@
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="83"/>
-      <c r="B133" s="72"/>
+      <c r="A133" s="69"/>
+      <c r="B133" s="66"/>
       <c r="C133" s="5" t="s">
         <v>334</v>
       </c>
@@ -5050,8 +5035,8 @@
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="83"/>
-      <c r="B134" s="72"/>
+      <c r="A134" s="69"/>
+      <c r="B134" s="66"/>
       <c r="C134" s="5" t="s">
         <v>336</v>
       </c>
@@ -5063,8 +5048,8 @@
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="83"/>
-      <c r="B135" s="72"/>
+      <c r="A135" s="69"/>
+      <c r="B135" s="66"/>
       <c r="C135" s="5" t="s">
         <v>217</v>
       </c>
@@ -5076,8 +5061,8 @@
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="83"/>
-      <c r="B136" s="72"/>
+      <c r="A136" s="69"/>
+      <c r="B136" s="66"/>
       <c r="C136" s="5" t="s">
         <v>221</v>
       </c>
@@ -5089,8 +5074,8 @@
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="83"/>
-      <c r="B137" s="72"/>
+      <c r="A137" s="69"/>
+      <c r="B137" s="66"/>
       <c r="C137" s="5" t="s">
         <v>202</v>
       </c>
@@ -5102,8 +5087,8 @@
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="83"/>
-      <c r="B138" s="72"/>
+      <c r="A138" s="69"/>
+      <c r="B138" s="66"/>
       <c r="C138" s="5" t="s">
         <v>264</v>
       </c>
@@ -5115,8 +5100,8 @@
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="83"/>
-      <c r="B139" s="72"/>
+      <c r="A139" s="69"/>
+      <c r="B139" s="66"/>
       <c r="C139" s="5" t="s">
         <v>266</v>
       </c>
@@ -5128,12 +5113,12 @@
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="83"/>
-      <c r="B140" s="72"/>
+      <c r="A140" s="69"/>
+      <c r="B140" s="66"/>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="83"/>
-      <c r="B141" s="81" t="s">
+      <c r="A141" s="69"/>
+      <c r="B141" s="65" t="s">
         <v>222</v>
       </c>
       <c r="C141" s="12" t="s">
@@ -5148,8 +5133,8 @@
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="83"/>
-      <c r="B142" s="82"/>
+      <c r="A142" s="69"/>
+      <c r="B142" s="66"/>
       <c r="C142" s="5" t="s">
         <v>312</v>
       </c>
@@ -5161,8 +5146,8 @@
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="83"/>
-      <c r="B143" s="82"/>
+      <c r="A143" s="69"/>
+      <c r="B143" s="66"/>
       <c r="C143" s="5" t="s">
         <v>225</v>
       </c>
@@ -5174,8 +5159,8 @@
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="83"/>
-      <c r="B144" s="82"/>
+      <c r="A144" s="69"/>
+      <c r="B144" s="66"/>
       <c r="C144" s="5" t="s">
         <v>267</v>
       </c>
@@ -5187,8 +5172,8 @@
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A145" s="83"/>
-      <c r="B145" s="82"/>
+      <c r="A145" s="69"/>
+      <c r="B145" s="66"/>
       <c r="C145" s="5" t="s">
         <v>269</v>
       </c>
@@ -5200,12 +5185,12 @@
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A146" s="83"/>
-      <c r="B146" s="73"/>
+      <c r="A146" s="69"/>
+      <c r="B146" s="67"/>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A147" s="83"/>
-      <c r="B147" s="81" t="s">
+      <c r="A147" s="69"/>
+      <c r="B147" s="65" t="s">
         <v>380</v>
       </c>
       <c r="C147" s="12" t="s">
@@ -5220,8 +5205,8 @@
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A148" s="83"/>
-      <c r="B148" s="72"/>
+      <c r="A148" s="69"/>
+      <c r="B148" s="66"/>
       <c r="C148" s="5" t="s">
         <v>383</v>
       </c>
@@ -5233,10 +5218,19 @@
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A149" s="83"/>
+      <c r="A149" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="B118:B120"/>
+    <mergeCell ref="A78:A103"/>
+    <mergeCell ref="B84:B93"/>
+    <mergeCell ref="B94:B103"/>
+    <mergeCell ref="A104:A117"/>
+    <mergeCell ref="B112:B114"/>
+    <mergeCell ref="B104:B107"/>
+    <mergeCell ref="B108:B111"/>
+    <mergeCell ref="B78:B80"/>
     <mergeCell ref="B147:B148"/>
     <mergeCell ref="B141:B146"/>
     <mergeCell ref="A118:A149"/>
@@ -5253,15 +5247,6 @@
     <mergeCell ref="B115:B117"/>
     <mergeCell ref="B121:B127"/>
     <mergeCell ref="B128:B140"/>
-    <mergeCell ref="B118:B120"/>
-    <mergeCell ref="A78:A103"/>
-    <mergeCell ref="B84:B93"/>
-    <mergeCell ref="B94:B103"/>
-    <mergeCell ref="A104:A117"/>
-    <mergeCell ref="B112:B114"/>
-    <mergeCell ref="B104:B107"/>
-    <mergeCell ref="B108:B111"/>
-    <mergeCell ref="B78:B80"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Methanol/Methanol_Bio_Brownfield_Memmingen/Datenbank.xlsx
+++ b/Methanol/Methanol_Bio_Brownfield_Memmingen/Datenbank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Methanol\Methanol_Bio_Brownfield_Memmingen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methanol\Methanol_Bio_Brownfield_Memmingen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E10240A4-A514-4B48-A4F3-A3CD58B98EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B7B8C3E-7CC1-4649-93B4-B9A35D0B66BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="23520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -170,7 +170,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="384">
   <si>
     <t>PEM Elektrolyse</t>
   </si>
@@ -855,12 +855,6 @@
     <t>calc_cost_h2</t>
   </si>
   <si>
-    <t>calc_einnahmen_stromverkauf_schattenvariable</t>
-  </si>
-  <si>
-    <t>Schattenvariable Einnahmen Stromverkauf</t>
-  </si>
-  <si>
     <t>Methanolsynthese</t>
   </si>
   <si>
@@ -1086,13 +1080,7 @@
     <t>result_qverkauf_flowsum</t>
   </si>
   <si>
-    <t>calc_einnahmen_qverkauf_schattenvariable</t>
-  </si>
-  <si>
     <t>calc_einnnahmen_qverkauf</t>
-  </si>
-  <si>
-    <t>Schattenvariable Einnahmen Wärmeverkauf</t>
   </si>
   <si>
     <t>Einnahmen aus Wärmeverkauf</t>
@@ -1343,10 +1331,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="0.00000"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.00000"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -1486,69 +1474,69 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1588,7 +1576,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1603,28 +1591,28 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2089,19 +2077,19 @@
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="53"/>
       <c r="B8" s="63" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C8" s="32" t="s">
         <v>84</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E8" s="33">
         <v>1.5</v>
       </c>
       <c r="F8" s="32" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -2111,7 +2099,7 @@
         <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E9" s="28">
         <v>285.39999999999998</v>
@@ -2127,13 +2115,13 @@
         <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E10" s="28">
         <v>5110</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -2143,7 +2131,7 @@
         <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E11" s="30">
         <v>0.05</v>
@@ -2159,29 +2147,29 @@
         <v>86</v>
       </c>
       <c r="D12" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E12" s="28">
         <v>0.189</v>
       </c>
       <c r="F12" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="53"/>
       <c r="B13" s="60"/>
       <c r="C13" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D13" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E13" s="28">
         <v>1.375</v>
       </c>
       <c r="F13" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -2191,7 +2179,7 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E14" s="31">
         <v>25</v>
@@ -2207,7 +2195,7 @@
         <v>15</v>
       </c>
       <c r="D15" s="34" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E15" s="35">
         <v>0.08</v>
@@ -2219,13 +2207,13 @@
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="53"/>
       <c r="B16" s="63" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C16" s="32" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E16" s="36">
         <v>3.7</v>
@@ -2241,13 +2229,13 @@
         <v>84</v>
       </c>
       <c r="D17" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E17" s="30">
         <v>0.27</v>
       </c>
       <c r="F17" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -2257,13 +2245,13 @@
         <v>10</v>
       </c>
       <c r="D18" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E18" s="30">
         <v>700</v>
       </c>
       <c r="F18" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -2273,7 +2261,7 @@
         <v>11</v>
       </c>
       <c r="D19" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E19" s="30">
         <v>0.02</v>
@@ -2289,7 +2277,7 @@
         <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E20" s="30">
         <v>20</v>
@@ -2305,7 +2293,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="34" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E21" s="35">
         <v>0.05</v>
@@ -2317,35 +2305,35 @@
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="53"/>
       <c r="B22" s="56" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C22" t="s">
         <v>84</v>
       </c>
       <c r="D22" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="E22" s="28">
         <v>0.2</v>
       </c>
       <c r="F22" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="53"/>
       <c r="B23" s="56"/>
       <c r="C23" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D23" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E23" s="28">
         <v>0.92800000000000005</v>
       </c>
       <c r="F23" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -2355,23 +2343,23 @@
         <v>10</v>
       </c>
       <c r="D24" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="E24" s="28">
         <v>1640</v>
       </c>
       <c r="F24" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="53"/>
       <c r="B25" s="56"/>
       <c r="C25" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="D25" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="E25" s="30">
         <v>0.04</v>
@@ -2384,48 +2372,48 @@
       <c r="A26" s="53"/>
       <c r="B26" s="56"/>
       <c r="C26" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="D26" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="E26" s="30">
         <v>2.5</v>
       </c>
       <c r="F26" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="53"/>
       <c r="B27" s="56"/>
       <c r="C27" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D27" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="E27" s="30">
         <v>1.5</v>
       </c>
       <c r="F27" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="53"/>
       <c r="B28" s="56"/>
       <c r="C28" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="D28" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="E28" s="30">
         <v>1.5E-3</v>
       </c>
       <c r="F28" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -2435,7 +2423,7 @@
         <v>13</v>
       </c>
       <c r="D29" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="E29" s="31">
         <v>25</v>
@@ -2451,7 +2439,7 @@
         <v>15</v>
       </c>
       <c r="D30" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="E30" s="30">
         <v>0.08</v>
@@ -2595,19 +2583,19 @@
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="53"/>
       <c r="B39" s="58" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C39" s="26" t="s">
         <v>87</v>
       </c>
       <c r="D39" s="26" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E39" s="37">
         <v>2.83</v>
       </c>
       <c r="F39" s="26" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -2617,7 +2605,7 @@
         <v>11</v>
       </c>
       <c r="D40" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="E40" s="30">
         <v>0.03</v>
@@ -2633,7 +2621,7 @@
         <v>13</v>
       </c>
       <c r="D41" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="E41" s="31">
         <v>30</v>
@@ -2649,7 +2637,7 @@
         <v>20</v>
       </c>
       <c r="D42" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="E42" s="30">
         <v>7.3999999999999999E-4</v>
@@ -2665,7 +2653,7 @@
         <v>35</v>
       </c>
       <c r="D43" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E43" s="30">
         <v>0.98</v>
@@ -2681,7 +2669,7 @@
         <v>36</v>
       </c>
       <c r="D44" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="E44" s="30">
         <v>0.98</v>
@@ -2697,7 +2685,7 @@
         <v>15</v>
       </c>
       <c r="D45" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E45" s="30">
         <v>0.05</v>
@@ -2713,7 +2701,7 @@
         <v>88</v>
       </c>
       <c r="D46" s="34" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="E46" s="35">
         <v>0</v>
@@ -2908,13 +2896,13 @@
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="53"/>
       <c r="B58" s="44" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C58" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="D58" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="E58" s="30">
         <v>0</v>
@@ -3165,7 +3153,7 @@
         <v>78</v>
       </c>
       <c r="E73" s="43">
-        <v>-1E-4</v>
+        <v>0</v>
       </c>
       <c r="F73" s="42" t="s">
         <v>19</v>
@@ -3174,19 +3162,19 @@
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="53"/>
       <c r="B74" s="25" t="s">
+        <v>295</v>
+      </c>
+      <c r="C74" t="s">
+        <v>296</v>
+      </c>
+      <c r="D74" t="s">
         <v>297</v>
       </c>
-      <c r="C74" t="s">
-        <v>298</v>
-      </c>
-      <c r="D74" t="s">
-        <v>299</v>
-      </c>
       <c r="E74" s="30">
-        <v>-1E-4</v>
+        <v>0</v>
       </c>
       <c r="F74" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
@@ -3210,19 +3198,19 @@
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="54"/>
       <c r="B76" s="23" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C76" s="39" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D76" s="39" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E76" s="40">
         <v>-0.6</v>
       </c>
       <c r="F76" s="39" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -3249,7 +3237,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AB2E79-6F94-41B5-A552-C40EC4890194}">
-  <dimension ref="A1:F149"/>
+  <dimension ref="A1:F147"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" style="5" customWidth="1"/>
@@ -3285,7 +3273,7 @@
       <c r="A2" s="68" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="70" t="s">
+      <c r="B2" s="65" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="6" t="s">
@@ -3418,14 +3406,14 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="69"/>
-      <c r="B12" s="65" t="s">
-        <v>229</v>
+      <c r="B12" s="75" t="s">
+        <v>227</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>96</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E12" s="13"/>
       <c r="F12" s="12" t="s">
@@ -3436,14 +3424,14 @@
       <c r="A13" s="69"/>
       <c r="B13" s="66"/>
       <c r="C13" s="5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E13" s="8"/>
       <c r="F13" s="5" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -3453,7 +3441,7 @@
         <v>139</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E14" s="8"/>
       <c r="F14" s="8" t="s">
@@ -3464,14 +3452,14 @@
       <c r="A15" s="69"/>
       <c r="B15" s="66"/>
       <c r="C15" s="5" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E15" s="10"/>
       <c r="F15" s="5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -3481,7 +3469,7 @@
         <v>84</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E16" s="8"/>
       <c r="F16" s="5" t="s">
@@ -3495,7 +3483,7 @@
         <v>141</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E17" s="8"/>
       <c r="F17" s="5" t="s">
@@ -3509,7 +3497,7 @@
         <v>155</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E18" s="11"/>
       <c r="F18" s="5" t="s">
@@ -3523,7 +3511,7 @@
         <v>196</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E19" s="11"/>
       <c r="F19" s="5" t="s">
@@ -3537,7 +3525,7 @@
         <v>167</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E20" s="11"/>
       <c r="F20" s="5" t="s">
@@ -3551,7 +3539,7 @@
         <v>188</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E21" s="11"/>
       <c r="F21" s="5" t="s">
@@ -3568,18 +3556,18 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="69"/>
-      <c r="B23" s="65" t="s">
-        <v>271</v>
+      <c r="B23" s="75" t="s">
+        <v>269</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>96</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E23" s="8"/>
       <c r="F23" s="5" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -3589,7 +3577,7 @@
         <v>107</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E24" s="8"/>
       <c r="F24" s="5" t="s">
@@ -3603,25 +3591,25 @@
         <v>84</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E25" s="10"/>
       <c r="F25" s="5" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="69"/>
       <c r="B26" s="66"/>
       <c r="C26" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E26" s="11"/>
       <c r="F26" s="5" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -3631,7 +3619,7 @@
         <v>141</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E27" s="11"/>
       <c r="F27" s="5" t="s">
@@ -3645,7 +3633,7 @@
         <v>155</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E28" s="11"/>
       <c r="F28" s="5" t="s">
@@ -3659,7 +3647,7 @@
         <v>196</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E29" s="11"/>
       <c r="F29" s="5" t="s">
@@ -3673,7 +3661,7 @@
         <v>167</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E30" s="10"/>
       <c r="F30" s="5" t="s">
@@ -3687,7 +3675,7 @@
         <v>188</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E31" s="10"/>
       <c r="F31" s="5" t="s">
@@ -3704,14 +3692,14 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="69"/>
-      <c r="B33" s="71" t="s">
-        <v>358</v>
+      <c r="B33" s="72" t="s">
+        <v>354</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>96</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="E33" s="8"/>
       <c r="F33" s="5" t="s">
@@ -3720,12 +3708,12 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="69"/>
-      <c r="B34" s="71"/>
+      <c r="B34" s="72"/>
       <c r="C34" s="5" t="s">
         <v>107</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E34" s="8"/>
       <c r="F34" s="5" t="s">
@@ -3734,12 +3722,12 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="69"/>
-      <c r="B35" s="71"/>
+      <c r="B35" s="72"/>
       <c r="C35" s="5" t="s">
         <v>84</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="E35" s="10"/>
       <c r="F35" s="5" t="s">
@@ -3748,54 +3736,54 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="69"/>
-      <c r="B36" s="71"/>
+      <c r="B36" s="72"/>
       <c r="C36" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E36" s="10"/>
       <c r="F36" s="5" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="69"/>
-      <c r="B37" s="71"/>
+      <c r="B37" s="72"/>
       <c r="C37" s="5" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="E37" s="10"/>
       <c r="F37" s="5" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="69"/>
-      <c r="B38" s="71"/>
+      <c r="B38" s="72"/>
       <c r="C38" s="5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="E38" s="11"/>
       <c r="F38" s="5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="69"/>
-      <c r="B39" s="71"/>
+      <c r="B39" s="72"/>
       <c r="C39" s="5" t="s">
         <v>141</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E39" s="11"/>
       <c r="F39" s="5" t="s">
@@ -3804,12 +3792,12 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="69"/>
-      <c r="B40" s="71"/>
+      <c r="B40" s="72"/>
       <c r="C40" s="5" t="s">
         <v>155</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E40" s="11"/>
       <c r="F40" s="5" t="s">
@@ -3818,12 +3806,12 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="69"/>
-      <c r="B41" s="71"/>
+      <c r="B41" s="72"/>
       <c r="C41" s="5" t="s">
         <v>161</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E41" s="11"/>
       <c r="F41" s="5" t="s">
@@ -3832,12 +3820,12 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="69"/>
-      <c r="B42" s="71"/>
+      <c r="B42" s="72"/>
       <c r="C42" s="5" t="s">
         <v>196</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="E42" s="11"/>
       <c r="F42" s="5" t="s">
@@ -3846,12 +3834,12 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="69"/>
-      <c r="B43" s="71"/>
+      <c r="B43" s="72"/>
       <c r="C43" s="5" t="s">
         <v>167</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="E43" s="10"/>
       <c r="F43" s="5" t="s">
@@ -3860,12 +3848,12 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="69"/>
-      <c r="B44" s="71"/>
+      <c r="B44" s="72"/>
       <c r="C44" s="5" t="s">
         <v>188</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="E44" s="10"/>
       <c r="F44" s="5" t="s">
@@ -3874,14 +3862,14 @@
     </row>
     <row r="45" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="69"/>
-      <c r="B45" s="71"/>
+      <c r="B45" s="72"/>
       <c r="E45" s="10"/>
     </row>
     <row r="46" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="68" t="s">
         <v>71</v>
       </c>
-      <c r="B46" s="75" t="s">
+      <c r="B46" s="77" t="s">
         <v>3</v>
       </c>
       <c r="C46" s="6" t="s">
@@ -3892,12 +3880,12 @@
       </c>
       <c r="E46" s="16"/>
       <c r="F46" s="6" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="69"/>
-      <c r="B47" s="71"/>
+      <c r="B47" s="72"/>
       <c r="C47" s="5" t="s">
         <v>111</v>
       </c>
@@ -3906,12 +3894,12 @@
       </c>
       <c r="E47" s="10"/>
       <c r="F47" s="5" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="69"/>
-      <c r="B48" s="71"/>
+      <c r="B48" s="72"/>
       <c r="C48" s="5" t="s">
         <v>135</v>
       </c>
@@ -3925,7 +3913,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="69"/>
-      <c r="B49" s="71"/>
+      <c r="B49" s="72"/>
       <c r="C49" s="5" t="s">
         <v>136</v>
       </c>
@@ -3939,7 +3927,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="69"/>
-      <c r="B50" s="71"/>
+      <c r="B50" s="72"/>
       <c r="C50" s="5" t="s">
         <v>141</v>
       </c>
@@ -3953,7 +3941,7 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="69"/>
-      <c r="B51" s="71"/>
+      <c r="B51" s="72"/>
       <c r="C51" s="5" t="s">
         <v>155</v>
       </c>
@@ -3967,7 +3955,7 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="69"/>
-      <c r="B52" s="71"/>
+      <c r="B52" s="72"/>
       <c r="C52" s="5" t="s">
         <v>196</v>
       </c>
@@ -3981,7 +3969,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="69"/>
-      <c r="B53" s="71"/>
+      <c r="B53" s="72"/>
       <c r="C53" s="5" t="s">
         <v>167</v>
       </c>
@@ -3995,7 +3983,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="69"/>
-      <c r="B54" s="71"/>
+      <c r="B54" s="72"/>
       <c r="C54" s="5" t="s">
         <v>188</v>
       </c>
@@ -4009,7 +3997,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="69"/>
-      <c r="B55" s="76"/>
+      <c r="B55" s="73"/>
       <c r="C55" s="14"/>
       <c r="D55" s="14"/>
       <c r="E55" s="15"/>
@@ -4017,70 +4005,70 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="69"/>
-      <c r="B56" s="71" t="s">
-        <v>315</v>
+      <c r="B56" s="72" t="s">
+        <v>311</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E56" s="8"/>
       <c r="F56" s="5" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="69"/>
-      <c r="B57" s="71"/>
+      <c r="B57" s="72"/>
       <c r="C57" s="5" t="s">
         <v>111</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E57" s="10"/>
       <c r="F57" s="5" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="69"/>
-      <c r="B58" s="71"/>
+      <c r="B58" s="72"/>
       <c r="C58" s="5" t="s">
         <v>135</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="E58" s="11"/>
       <c r="F58" s="5" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="69"/>
-      <c r="B59" s="71"/>
+      <c r="B59" s="72"/>
       <c r="C59" s="5" t="s">
         <v>136</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="E59" s="10"/>
       <c r="F59" s="5" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="69"/>
-      <c r="B60" s="71"/>
+      <c r="B60" s="72"/>
       <c r="C60" s="5" t="s">
         <v>141</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E60" s="10"/>
       <c r="F60" s="5" t="s">
@@ -4089,12 +4077,12 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="69"/>
-      <c r="B61" s="71"/>
+      <c r="B61" s="72"/>
       <c r="C61" s="5" t="s">
         <v>155</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="E61" s="10"/>
       <c r="F61" s="5" t="s">
@@ -4103,12 +4091,12 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="69"/>
-      <c r="B62" s="71"/>
+      <c r="B62" s="72"/>
       <c r="C62" s="5" t="s">
         <v>196</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="E62" s="10"/>
       <c r="F62" s="5" t="s">
@@ -4117,12 +4105,12 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="69"/>
-      <c r="B63" s="71"/>
+      <c r="B63" s="72"/>
       <c r="C63" s="5" t="s">
         <v>167</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E63" s="10"/>
       <c r="F63" s="5" t="s">
@@ -4131,12 +4119,12 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="69"/>
-      <c r="B64" s="71"/>
+      <c r="B64" s="72"/>
       <c r="C64" s="5" t="s">
         <v>188</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E64" s="10"/>
       <c r="F64" s="5" t="s">
@@ -4145,12 +4133,12 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="69"/>
-      <c r="B65" s="76"/>
+      <c r="B65" s="73"/>
       <c r="E65" s="10"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="69"/>
-      <c r="B66" s="73" t="s">
+      <c r="B66" s="71" t="s">
         <v>6</v>
       </c>
       <c r="C66" s="12" t="s">
@@ -4166,7 +4154,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="69"/>
-      <c r="B67" s="71"/>
+      <c r="B67" s="72"/>
       <c r="C67" s="5" t="s">
         <v>113</v>
       </c>
@@ -4305,8 +4293,8 @@
       </c>
     </row>
     <row r="77" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="72"/>
-      <c r="B77" s="74"/>
+      <c r="A77" s="70"/>
+      <c r="B77" s="76"/>
       <c r="C77" s="18"/>
       <c r="D77" s="18"/>
       <c r="E77" s="19"/>
@@ -4316,7 +4304,7 @@
       <c r="A78" s="68" t="s">
         <v>72</v>
       </c>
-      <c r="B78" s="70" t="s">
+      <c r="B78" s="65" t="s">
         <v>73</v>
       </c>
       <c r="C78" s="6" t="s">
@@ -4355,27 +4343,27 @@
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="69"/>
       <c r="B81" s="66" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="E81" s="8"/>
       <c r="F81" s="5" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="69"/>
       <c r="B82" s="66"/>
       <c r="C82" s="5" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="E82" s="8"/>
       <c r="F82" s="5" t="s">
@@ -4389,7 +4377,7 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="69"/>
-      <c r="B84" s="73" t="s">
+      <c r="B84" s="71" t="s">
         <v>4</v>
       </c>
       <c r="C84" s="12" t="s">
@@ -4405,7 +4393,7 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="69"/>
-      <c r="B85" s="71"/>
+      <c r="B85" s="72"/>
       <c r="C85" s="5" t="s">
         <v>107</v>
       </c>
@@ -4419,7 +4407,7 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="69"/>
-      <c r="B86" s="71"/>
+      <c r="B86" s="72"/>
       <c r="C86" s="5" t="s">
         <v>122</v>
       </c>
@@ -4433,7 +4421,7 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="69"/>
-      <c r="B87" s="71"/>
+      <c r="B87" s="72"/>
       <c r="C87" s="5" t="s">
         <v>141</v>
       </c>
@@ -4447,7 +4435,7 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="69"/>
-      <c r="B88" s="71"/>
+      <c r="B88" s="72"/>
       <c r="C88" s="5" t="s">
         <v>155</v>
       </c>
@@ -4461,7 +4449,7 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="69"/>
-      <c r="B89" s="71"/>
+      <c r="B89" s="72"/>
       <c r="C89" s="5" t="s">
         <v>161</v>
       </c>
@@ -4475,7 +4463,7 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="69"/>
-      <c r="B90" s="71"/>
+      <c r="B90" s="72"/>
       <c r="C90" s="5" t="s">
         <v>196</v>
       </c>
@@ -4489,7 +4477,7 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="69"/>
-      <c r="B91" s="71"/>
+      <c r="B91" s="72"/>
       <c r="C91" s="5" t="s">
         <v>167</v>
       </c>
@@ -4503,7 +4491,7 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="69"/>
-      <c r="B92" s="71"/>
+      <c r="B92" s="72"/>
       <c r="C92" s="5" t="s">
         <v>188</v>
       </c>
@@ -4517,11 +4505,11 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="69"/>
-      <c r="B93" s="76"/>
+      <c r="B93" s="73"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="69"/>
-      <c r="B94" s="73" t="s">
+      <c r="B94" s="71" t="s">
         <v>5</v>
       </c>
       <c r="C94" s="12" t="s">
@@ -4537,7 +4525,7 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="69"/>
-      <c r="B95" s="71"/>
+      <c r="B95" s="72"/>
       <c r="C95" s="5" t="s">
         <v>108</v>
       </c>
@@ -4551,7 +4539,7 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="69"/>
-      <c r="B96" s="71"/>
+      <c r="B96" s="72"/>
       <c r="C96" s="5" t="s">
         <v>120</v>
       </c>
@@ -4565,7 +4553,7 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="69"/>
-      <c r="B97" s="71"/>
+      <c r="B97" s="72"/>
       <c r="C97" s="5" t="s">
         <v>141</v>
       </c>
@@ -4579,7 +4567,7 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="69"/>
-      <c r="B98" s="71"/>
+      <c r="B98" s="72"/>
       <c r="C98" s="5" t="s">
         <v>155</v>
       </c>
@@ -4593,7 +4581,7 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="69"/>
-      <c r="B99" s="71"/>
+      <c r="B99" s="72"/>
       <c r="C99" s="5" t="s">
         <v>161</v>
       </c>
@@ -4607,7 +4595,7 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="69"/>
-      <c r="B100" s="71"/>
+      <c r="B100" s="72"/>
       <c r="C100" s="5" t="s">
         <v>196</v>
       </c>
@@ -4621,7 +4609,7 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="69"/>
-      <c r="B101" s="71"/>
+      <c r="B101" s="72"/>
       <c r="C101" s="5" t="s">
         <v>167</v>
       </c>
@@ -4635,7 +4623,7 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="69"/>
-      <c r="B102" s="71"/>
+      <c r="B102" s="72"/>
       <c r="C102" s="5" t="s">
         <v>188</v>
       </c>
@@ -4648,14 +4636,14 @@
       </c>
     </row>
     <row r="103" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="72"/>
-      <c r="B103" s="77"/>
+      <c r="A103" s="70"/>
+      <c r="B103" s="74"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="68" t="s">
         <v>76</v>
       </c>
-      <c r="B104" s="70" t="s">
+      <c r="B104" s="65" t="s">
         <v>73</v>
       </c>
       <c r="C104" s="6" t="s">
@@ -4673,10 +4661,10 @@
       <c r="A105" s="69"/>
       <c r="B105" s="66"/>
       <c r="C105" s="5" t="s">
-        <v>228</v>
+        <v>150</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>227</v>
+        <v>147</v>
       </c>
       <c r="E105" s="10"/>
       <c r="F105" s="5" t="s">
@@ -4685,200 +4673,198 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="69"/>
-      <c r="B106" s="66"/>
-      <c r="C106" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="D106" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="E106" s="10"/>
-      <c r="F106" s="5" t="s">
-        <v>149</v>
-      </c>
+      <c r="B106" s="67"/>
+      <c r="C106" s="14"/>
+      <c r="D106" s="14"/>
+      <c r="E106" s="15"/>
+      <c r="F106" s="14"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="69"/>
-      <c r="B107" s="67"/>
-      <c r="C107" s="14"/>
-      <c r="D107" s="14"/>
-      <c r="E107" s="15"/>
-      <c r="F107" s="14"/>
+      <c r="B107" s="75" t="s">
+        <v>299</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="D107" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="E107" s="10"/>
+      <c r="F107" s="5" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="69"/>
-      <c r="B108" s="65" t="s">
-        <v>301</v>
-      </c>
+      <c r="B108" s="66"/>
       <c r="C108" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="D108" s="5" t="s">
         <v>302</v>
-      </c>
-      <c r="D108" s="5" t="s">
-        <v>303</v>
       </c>
       <c r="E108" s="10"/>
       <c r="F108" s="5" t="s">
-        <v>292</v>
+        <v>149</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="69"/>
-      <c r="B109" s="66"/>
-      <c r="C109" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="D109" s="5" t="s">
-        <v>304</v>
-      </c>
+      <c r="B109" s="67"/>
       <c r="E109" s="10"/>
-      <c r="F109" s="5" t="s">
-        <v>149</v>
-      </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="69"/>
-      <c r="B110" s="66"/>
-      <c r="C110" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="D110" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="E110" s="10"/>
-      <c r="F110" s="5" t="s">
-        <v>149</v>
+      <c r="B110" s="75" t="s">
+        <v>79</v>
+      </c>
+      <c r="C110" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D110" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="E110" s="17"/>
+      <c r="F110" s="12" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="69"/>
-      <c r="B111" s="67"/>
+      <c r="B111" s="66"/>
+      <c r="C111" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D111" s="5" t="s">
+        <v>148</v>
+      </c>
       <c r="E111" s="10"/>
+      <c r="F111" s="5" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="69"/>
-      <c r="B112" s="65" t="s">
-        <v>79</v>
-      </c>
-      <c r="C112" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="D112" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="E112" s="17"/>
-      <c r="F112" s="12" t="s">
-        <v>132</v>
-      </c>
+      <c r="B112" s="67"/>
+      <c r="C112" s="14"/>
+      <c r="D112" s="14"/>
+      <c r="E112" s="15"/>
+      <c r="F112" s="14"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" s="69"/>
-      <c r="B113" s="66"/>
+      <c r="B113" s="75" t="s">
+        <v>258</v>
+      </c>
       <c r="C113" s="5" t="s">
-        <v>151</v>
+        <v>257</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>148</v>
+        <v>260</v>
       </c>
       <c r="E113" s="10"/>
       <c r="F113" s="5" t="s">
-        <v>149</v>
+        <v>254</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="69"/>
-      <c r="B114" s="67"/>
-      <c r="C114" s="14"/>
-      <c r="D114" s="14"/>
-      <c r="E114" s="15"/>
-      <c r="F114" s="14"/>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="69"/>
-      <c r="B115" s="65" t="s">
-        <v>260</v>
-      </c>
-      <c r="C115" s="5" t="s">
+      <c r="B114" s="66"/>
+      <c r="C114" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="D115" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="E115" s="10"/>
-      <c r="F115" s="5" t="s">
-        <v>256</v>
-      </c>
+      <c r="D114" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="E114" s="10"/>
+      <c r="F114" s="5" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A115" s="70"/>
+      <c r="B115" s="76"/>
+      <c r="C115" s="18"/>
+      <c r="D115" s="18"/>
+      <c r="E115" s="19"/>
+      <c r="F115" s="18"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="69"/>
-      <c r="B116" s="66"/>
-      <c r="C116" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="D116" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="E116" s="10"/>
-      <c r="F116" s="5" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="72"/>
-      <c r="B117" s="74"/>
-      <c r="C117" s="18"/>
-      <c r="D117" s="18"/>
-      <c r="E117" s="19"/>
-      <c r="F117" s="18"/>
+      <c r="A116" s="68" t="s">
+        <v>163</v>
+      </c>
+      <c r="B116" s="65" t="s">
+        <v>13</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="D116" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="E116" s="6"/>
+      <c r="F116" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A117" s="69"/>
+      <c r="B117" s="66"/>
+      <c r="C117" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D117" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="F117" s="5" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="68" t="s">
-        <v>163</v>
-      </c>
-      <c r="B118" s="70" t="s">
-        <v>13</v>
-      </c>
-      <c r="C118" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="D118" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="E118" s="6"/>
-      <c r="F118" s="6" t="s">
-        <v>140</v>
-      </c>
+      <c r="A118" s="69"/>
+      <c r="B118" s="67"/>
+      <c r="C118" s="14"/>
+      <c r="D118" s="14"/>
+      <c r="E118" s="14"/>
+      <c r="F118" s="14"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" s="69"/>
-      <c r="B119" s="66"/>
+      <c r="B119" s="75" t="s">
+        <v>183</v>
+      </c>
       <c r="C119" s="5" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" s="69"/>
-      <c r="B120" s="67"/>
-      <c r="C120" s="14"/>
-      <c r="D120" s="14"/>
-      <c r="E120" s="14"/>
-      <c r="F120" s="14"/>
+      <c r="B120" s="66"/>
+      <c r="C120" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D120" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="F120" s="5" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="69"/>
-      <c r="B121" s="65" t="s">
-        <v>183</v>
-      </c>
+      <c r="B121" s="66"/>
       <c r="C121" s="5" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="F121" s="5" t="s">
         <v>149</v>
@@ -4888,10 +4874,10 @@
       <c r="A122" s="69"/>
       <c r="B122" s="66"/>
       <c r="C122" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>309</v>
+        <v>178</v>
       </c>
       <c r="F122" s="5" t="s">
         <v>149</v>
@@ -4901,10 +4887,10 @@
       <c r="A123" s="69"/>
       <c r="B123" s="66"/>
       <c r="C123" s="5" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F123" s="5" t="s">
         <v>149</v>
@@ -4914,10 +4900,10 @@
       <c r="A124" s="69"/>
       <c r="B124" s="66"/>
       <c r="C124" s="5" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="F124" s="5" t="s">
         <v>149</v>
@@ -4926,57 +4912,57 @@
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" s="69"/>
       <c r="B125" s="66"/>
-      <c r="C125" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="D125" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="F125" s="5" t="s">
-        <v>149</v>
-      </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" s="69"/>
-      <c r="B126" s="66"/>
-      <c r="C126" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="D126" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="F126" s="5" t="s">
-        <v>149</v>
+      <c r="B126" s="75" t="s">
+        <v>206</v>
+      </c>
+      <c r="C126" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="D126" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="E126" s="12"/>
+      <c r="F126" s="12" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="69"/>
       <c r="B127" s="66"/>
+      <c r="C127" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="D127" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="F127" s="5" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" s="69"/>
-      <c r="B128" s="65" t="s">
-        <v>206</v>
-      </c>
-      <c r="C128" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="D128" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="E128" s="12"/>
-      <c r="F128" s="12" t="s">
-        <v>208</v>
+      <c r="B128" s="66"/>
+      <c r="C128" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="D128" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="F128" s="5" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" s="69"/>
       <c r="B129" s="66"/>
       <c r="C129" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F129" s="5" t="s">
         <v>208</v>
@@ -4986,88 +4972,88 @@
       <c r="A130" s="69"/>
       <c r="B130" s="66"/>
       <c r="C130" s="5" t="s">
-        <v>215</v>
+        <v>306</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>214</v>
+        <v>307</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>219</v>
+        <v>310</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" s="69"/>
       <c r="B131" s="66"/>
       <c r="C131" s="5" t="s">
-        <v>205</v>
+        <v>330</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>209</v>
+        <v>331</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>208</v>
+        <v>310</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" s="69"/>
       <c r="B132" s="66"/>
       <c r="C132" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="D132" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="F132" s="5" t="s">
         <v>310</v>
-      </c>
-      <c r="D132" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="F132" s="5" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" s="69"/>
       <c r="B133" s="66"/>
       <c r="C133" s="5" t="s">
-        <v>334</v>
+        <v>217</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>335</v>
+        <v>216</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>314</v>
+        <v>218</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" s="69"/>
       <c r="B134" s="66"/>
       <c r="C134" s="5" t="s">
-        <v>336</v>
+        <v>221</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>337</v>
+        <v>211</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>314</v>
+        <v>212</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" s="69"/>
       <c r="B135" s="66"/>
       <c r="C135" s="5" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" s="69"/>
       <c r="B136" s="66"/>
       <c r="C136" s="5" t="s">
-        <v>221</v>
+        <v>262</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>211</v>
+        <v>365</v>
       </c>
       <c r="F136" s="5" t="s">
         <v>212</v>
@@ -5077,163 +5063,128 @@
       <c r="A137" s="69"/>
       <c r="B137" s="66"/>
       <c r="C137" s="5" t="s">
-        <v>202</v>
+        <v>264</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>220</v>
+        <v>263</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" s="69"/>
       <c r="B138" s="66"/>
-      <c r="C138" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="D138" s="5" t="s">
-        <v>369</v>
-      </c>
-      <c r="F138" s="5" t="s">
-        <v>212</v>
-      </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" s="69"/>
-      <c r="B139" s="66"/>
-      <c r="C139" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="D139" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="F139" s="5" t="s">
-        <v>213</v>
+      <c r="B139" s="75" t="s">
+        <v>222</v>
+      </c>
+      <c r="C139" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="D139" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="E139" s="12"/>
+      <c r="F139" s="12" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="69"/>
       <c r="B140" s="66"/>
+      <c r="C140" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D140" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="F140" s="5" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" s="69"/>
-      <c r="B141" s="65" t="s">
-        <v>222</v>
-      </c>
-      <c r="C141" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="D141" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="E141" s="12"/>
-      <c r="F141" s="12" t="s">
-        <v>208</v>
+      <c r="B141" s="66"/>
+      <c r="C141" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="D141" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F141" s="5" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" s="69"/>
       <c r="B142" s="66"/>
       <c r="C142" s="5" t="s">
-        <v>312</v>
+        <v>265</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>313</v>
+        <v>266</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>314</v>
+        <v>212</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" s="69"/>
       <c r="B143" s="66"/>
       <c r="C143" s="5" t="s">
-        <v>225</v>
+        <v>267</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>226</v>
+        <v>304</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" s="69"/>
-      <c r="B144" s="66"/>
-      <c r="C144" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="D144" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="F144" s="5" t="s">
-        <v>212</v>
-      </c>
+      <c r="B144" s="67"/>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" s="69"/>
-      <c r="B145" s="66"/>
-      <c r="C145" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="D145" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="F145" s="5" t="s">
-        <v>213</v>
+      <c r="B145" s="75" t="s">
+        <v>376</v>
+      </c>
+      <c r="C145" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="D145" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="E145" s="12"/>
+      <c r="F145" s="12" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" s="69"/>
-      <c r="B146" s="67"/>
+      <c r="B146" s="66"/>
+      <c r="C146" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="D146" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="F146" s="5" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" s="69"/>
-      <c r="B147" s="65" t="s">
-        <v>380</v>
-      </c>
-      <c r="C147" s="12" t="s">
-        <v>381</v>
-      </c>
-      <c r="D147" s="12" t="s">
-        <v>382</v>
-      </c>
-      <c r="E147" s="12"/>
-      <c r="F147" s="12" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A148" s="69"/>
-      <c r="B148" s="66"/>
-      <c r="C148" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="D148" s="5" t="s">
-        <v>384</v>
-      </c>
-      <c r="F148" s="5" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A149" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="B118:B120"/>
-    <mergeCell ref="A78:A103"/>
-    <mergeCell ref="B84:B93"/>
-    <mergeCell ref="B94:B103"/>
-    <mergeCell ref="A104:A117"/>
-    <mergeCell ref="B112:B114"/>
-    <mergeCell ref="B104:B107"/>
-    <mergeCell ref="B108:B111"/>
-    <mergeCell ref="B78:B80"/>
-    <mergeCell ref="B147:B148"/>
-    <mergeCell ref="B141:B146"/>
-    <mergeCell ref="A118:A149"/>
+    <mergeCell ref="B145:B146"/>
+    <mergeCell ref="B139:B144"/>
+    <mergeCell ref="A116:A147"/>
     <mergeCell ref="A2:A45"/>
     <mergeCell ref="B2:B11"/>
     <mergeCell ref="B12:B22"/>
@@ -5244,9 +5195,18 @@
     <mergeCell ref="B46:B55"/>
     <mergeCell ref="B56:B65"/>
     <mergeCell ref="B81:B83"/>
-    <mergeCell ref="B115:B117"/>
-    <mergeCell ref="B121:B127"/>
-    <mergeCell ref="B128:B140"/>
+    <mergeCell ref="B113:B115"/>
+    <mergeCell ref="B119:B125"/>
+    <mergeCell ref="B126:B138"/>
+    <mergeCell ref="B116:B118"/>
+    <mergeCell ref="A78:A103"/>
+    <mergeCell ref="B84:B93"/>
+    <mergeCell ref="B94:B103"/>
+    <mergeCell ref="A104:A115"/>
+    <mergeCell ref="B110:B112"/>
+    <mergeCell ref="B104:B106"/>
+    <mergeCell ref="B107:B109"/>
+    <mergeCell ref="B78:B80"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
